--- a/grilla.xlsx
+++ b/grilla.xlsx
@@ -5,12 +5,12 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aetch\Desktop\proyecto_datero\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aetch\Desktop\proyecto_aamas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9A9B9EF5-A466-451C-A3FB-6FB1A96C537A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B5244439-1DB5-4020-8CE0-DBBD7AB73783}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1770" yWindow="2220" windowWidth="15825" windowHeight="11385" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Grilla" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="545" uniqueCount="448">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="654" uniqueCount="462">
   <si>
     <t>Cuotas12</t>
   </si>
@@ -1378,6 +1378,48 @@
   </si>
   <si>
     <t>Cuotas6</t>
+  </si>
+  <si>
+    <t>Cuotas9</t>
+  </si>
+  <si>
+    <t>15036.66</t>
+  </si>
+  <si>
+    <t>22554.99</t>
+  </si>
+  <si>
+    <t>30073.31</t>
+  </si>
+  <si>
+    <t>37591.64</t>
+  </si>
+  <si>
+    <t>45109.97</t>
+  </si>
+  <si>
+    <t>52628.30</t>
+  </si>
+  <si>
+    <t>60146.63</t>
+  </si>
+  <si>
+    <t>67664.96</t>
+  </si>
+  <si>
+    <t>75183.29</t>
+  </si>
+  <si>
+    <t>82701.61</t>
+  </si>
+  <si>
+    <t>114584.69</t>
+  </si>
+  <si>
+    <t>125001.48</t>
+  </si>
+  <si>
+    <t>90219.94</t>
   </si>
 </sst>
 </file>
@@ -1756,15 +1798,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E109"/>
+  <dimension ref="A1:F109"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="13.875" customWidth="1"/>
-    <col min="2" max="2" width="11.25" style="2" customWidth="1"/>
-    <col min="3" max="5" width="12.5" customWidth="1"/>
+    <col min="2" max="3" width="11.25" style="2" customWidth="1"/>
+    <col min="4" max="6" width="12.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>435</v>
       </c>
@@ -1772,16 +1814,19 @@
         <v>447</v>
       </c>
       <c r="C1" t="s">
+        <v>448</v>
+      </c>
+      <c r="D1" t="s">
         <v>0</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>1</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -1789,16 +1834,19 @@
         <v>436</v>
       </c>
       <c r="C2" t="s">
+        <v>436</v>
+      </c>
+      <c r="D2" t="s">
         <v>4</v>
       </c>
-      <c r="D2" t="s">
+      <c r="E2" t="s">
         <v>5</v>
       </c>
-      <c r="E2" t="s">
+      <c r="F2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>7</v>
       </c>
@@ -1806,16 +1854,19 @@
         <v>436</v>
       </c>
       <c r="C3" t="s">
+        <v>436</v>
+      </c>
+      <c r="D3" t="s">
         <v>8</v>
       </c>
-      <c r="D3" t="s">
+      <c r="E3" t="s">
         <v>9</v>
       </c>
-      <c r="E3" t="s">
+      <c r="F3" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>11</v>
       </c>
@@ -1823,16 +1874,19 @@
         <v>436</v>
       </c>
       <c r="C4" t="s">
+        <v>436</v>
+      </c>
+      <c r="D4" t="s">
         <v>12</v>
       </c>
-      <c r="D4" t="s">
+      <c r="E4" t="s">
         <v>13</v>
       </c>
-      <c r="E4" t="s">
+      <c r="F4" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>15</v>
       </c>
@@ -1840,16 +1894,19 @@
         <v>436</v>
       </c>
       <c r="C5" t="s">
+        <v>436</v>
+      </c>
+      <c r="D5" t="s">
         <v>16</v>
       </c>
-      <c r="D5" t="s">
+      <c r="E5" t="s">
         <v>17</v>
       </c>
-      <c r="E5" t="s">
+      <c r="F5" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>19</v>
       </c>
@@ -1857,16 +1914,19 @@
         <v>436</v>
       </c>
       <c r="C6" t="s">
+        <v>436</v>
+      </c>
+      <c r="D6" t="s">
         <v>20</v>
       </c>
-      <c r="D6" t="s">
+      <c r="E6" t="s">
         <v>21</v>
       </c>
-      <c r="E6" t="s">
+      <c r="F6" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>23</v>
       </c>
@@ -1874,16 +1934,19 @@
         <v>436</v>
       </c>
       <c r="C7" t="s">
+        <v>436</v>
+      </c>
+      <c r="D7" t="s">
         <v>24</v>
       </c>
-      <c r="D7" s="1" t="s">
+      <c r="E7" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="E7" t="s">
+      <c r="F7" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>27</v>
       </c>
@@ -1891,16 +1954,19 @@
         <v>436</v>
       </c>
       <c r="C8" t="s">
+        <v>436</v>
+      </c>
+      <c r="D8" t="s">
         <v>28</v>
       </c>
-      <c r="D8" t="s">
+      <c r="E8" t="s">
         <v>29</v>
       </c>
-      <c r="E8" t="s">
+      <c r="F8" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>31</v>
       </c>
@@ -1908,16 +1974,19 @@
         <v>438</v>
       </c>
       <c r="C9" t="s">
+        <v>449</v>
+      </c>
+      <c r="D9" t="s">
         <v>32</v>
       </c>
-      <c r="D9" t="s">
+      <c r="E9" t="s">
         <v>33</v>
       </c>
-      <c r="E9" t="s">
+      <c r="F9" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>35</v>
       </c>
@@ -1925,16 +1994,19 @@
         <v>439</v>
       </c>
       <c r="C10" t="s">
+        <v>436</v>
+      </c>
+      <c r="D10" t="s">
         <v>36</v>
       </c>
-      <c r="D10" t="s">
+      <c r="E10" t="s">
         <v>37</v>
       </c>
-      <c r="E10" t="s">
+      <c r="F10" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>39</v>
       </c>
@@ -1942,16 +2014,19 @@
         <v>436</v>
       </c>
       <c r="C11" t="s">
+        <v>436</v>
+      </c>
+      <c r="D11" t="s">
         <v>40</v>
       </c>
-      <c r="D11" t="s">
+      <c r="E11" t="s">
         <v>41</v>
       </c>
-      <c r="E11" t="s">
+      <c r="F11" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>43</v>
       </c>
@@ -1959,16 +2034,19 @@
         <v>436</v>
       </c>
       <c r="C12" t="s">
+        <v>436</v>
+      </c>
+      <c r="D12" t="s">
         <v>44</v>
       </c>
-      <c r="D12" t="s">
+      <c r="E12" t="s">
         <v>45</v>
       </c>
-      <c r="E12" t="s">
+      <c r="F12" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>47</v>
       </c>
@@ -1976,16 +2054,19 @@
         <v>436</v>
       </c>
       <c r="C13" t="s">
+        <v>436</v>
+      </c>
+      <c r="D13" t="s">
         <v>48</v>
       </c>
-      <c r="D13" t="s">
+      <c r="E13" t="s">
         <v>49</v>
       </c>
-      <c r="E13" t="s">
+      <c r="F13" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>51</v>
       </c>
@@ -1993,16 +2074,19 @@
         <v>440</v>
       </c>
       <c r="C14" t="s">
+        <v>450</v>
+      </c>
+      <c r="D14" t="s">
         <v>52</v>
       </c>
-      <c r="D14" t="s">
+      <c r="E14" t="s">
         <v>53</v>
       </c>
-      <c r="E14" t="s">
+      <c r="F14" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>55</v>
       </c>
@@ -2010,16 +2094,19 @@
         <v>436</v>
       </c>
       <c r="C15" t="s">
+        <v>436</v>
+      </c>
+      <c r="D15" t="s">
         <v>56</v>
       </c>
-      <c r="D15" t="s">
+      <c r="E15" t="s">
         <v>57</v>
       </c>
-      <c r="E15" t="s">
+      <c r="F15" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>59</v>
       </c>
@@ -2027,16 +2114,19 @@
         <v>436</v>
       </c>
       <c r="C16" t="s">
+        <v>436</v>
+      </c>
+      <c r="D16" t="s">
         <v>60</v>
       </c>
-      <c r="D16" t="s">
+      <c r="E16" t="s">
         <v>61</v>
       </c>
-      <c r="E16" t="s">
+      <c r="F16" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>63</v>
       </c>
@@ -2044,16 +2134,19 @@
         <v>436</v>
       </c>
       <c r="C17" t="s">
+        <v>436</v>
+      </c>
+      <c r="D17" t="s">
         <v>64</v>
       </c>
-      <c r="D17" t="s">
+      <c r="E17" t="s">
         <v>65</v>
       </c>
-      <c r="E17" t="s">
+      <c r="F17" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>67</v>
       </c>
@@ -2061,16 +2154,19 @@
         <v>436</v>
       </c>
       <c r="C18" t="s">
+        <v>436</v>
+      </c>
+      <c r="D18" t="s">
         <v>68</v>
       </c>
-      <c r="D18" t="s">
+      <c r="E18" t="s">
         <v>69</v>
       </c>
-      <c r="E18" t="s">
+      <c r="F18" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>71</v>
       </c>
@@ -2078,16 +2174,19 @@
         <v>437</v>
       </c>
       <c r="C19" t="s">
+        <v>451</v>
+      </c>
+      <c r="D19" t="s">
         <v>72</v>
       </c>
-      <c r="D19" t="s">
+      <c r="E19" t="s">
         <v>73</v>
       </c>
-      <c r="E19" t="s">
+      <c r="F19" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>75</v>
       </c>
@@ -2095,16 +2194,19 @@
         <v>436</v>
       </c>
       <c r="C20" t="s">
+        <v>436</v>
+      </c>
+      <c r="D20" t="s">
         <v>76</v>
       </c>
-      <c r="D20" t="s">
+      <c r="E20" t="s">
         <v>77</v>
       </c>
-      <c r="E20" t="s">
+      <c r="F20" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>79</v>
       </c>
@@ -2112,16 +2214,19 @@
         <v>436</v>
       </c>
       <c r="C21" t="s">
+        <v>436</v>
+      </c>
+      <c r="D21" t="s">
         <v>80</v>
       </c>
-      <c r="D21" t="s">
+      <c r="E21" t="s">
         <v>81</v>
       </c>
-      <c r="E21" t="s">
+      <c r="F21" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>83</v>
       </c>
@@ -2129,16 +2234,19 @@
         <v>436</v>
       </c>
       <c r="C22" t="s">
+        <v>436</v>
+      </c>
+      <c r="D22" t="s">
         <v>84</v>
       </c>
-      <c r="D22" t="s">
+      <c r="E22" t="s">
         <v>85</v>
       </c>
-      <c r="E22" t="s">
+      <c r="F22" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>87</v>
       </c>
@@ -2146,16 +2254,19 @@
         <v>436</v>
       </c>
       <c r="C23" t="s">
+        <v>436</v>
+      </c>
+      <c r="D23" t="s">
         <v>88</v>
       </c>
-      <c r="D23" t="s">
+      <c r="E23" t="s">
         <v>89</v>
       </c>
-      <c r="E23" t="s">
+      <c r="F23" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>91</v>
       </c>
@@ -2163,16 +2274,19 @@
         <v>441</v>
       </c>
       <c r="C24" t="s">
+        <v>452</v>
+      </c>
+      <c r="D24" t="s">
         <v>92</v>
       </c>
-      <c r="D24" t="s">
+      <c r="E24" t="s">
         <v>93</v>
       </c>
-      <c r="E24" t="s">
+      <c r="F24" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>95</v>
       </c>
@@ -2180,16 +2294,19 @@
         <v>436</v>
       </c>
       <c r="C25" t="s">
+        <v>436</v>
+      </c>
+      <c r="D25" t="s">
         <v>96</v>
       </c>
-      <c r="D25" t="s">
+      <c r="E25" t="s">
         <v>97</v>
       </c>
-      <c r="E25" t="s">
+      <c r="F25" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>99</v>
       </c>
@@ -2197,16 +2314,19 @@
         <v>436</v>
       </c>
       <c r="C26" t="s">
+        <v>436</v>
+      </c>
+      <c r="D26" t="s">
         <v>100</v>
       </c>
-      <c r="D26" t="s">
+      <c r="E26" t="s">
         <v>101</v>
       </c>
-      <c r="E26" t="s">
+      <c r="F26" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>103</v>
       </c>
@@ -2214,16 +2334,19 @@
         <v>436</v>
       </c>
       <c r="C27" t="s">
+        <v>436</v>
+      </c>
+      <c r="D27" t="s">
         <v>104</v>
       </c>
-      <c r="D27" t="s">
+      <c r="E27" t="s">
         <v>105</v>
       </c>
-      <c r="E27" t="s">
+      <c r="F27" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>107</v>
       </c>
@@ -2231,16 +2354,19 @@
         <v>436</v>
       </c>
       <c r="C28" t="s">
+        <v>436</v>
+      </c>
+      <c r="D28" t="s">
         <v>108</v>
       </c>
-      <c r="D28" t="s">
+      <c r="E28" t="s">
         <v>109</v>
       </c>
-      <c r="E28" t="s">
+      <c r="F28" t="s">
         <v>110</v>
       </c>
     </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>111</v>
       </c>
@@ -2248,16 +2374,19 @@
         <v>442</v>
       </c>
       <c r="C29" t="s">
+        <v>453</v>
+      </c>
+      <c r="D29" t="s">
         <v>112</v>
       </c>
-      <c r="D29" t="s">
+      <c r="E29" t="s">
         <v>113</v>
       </c>
-      <c r="E29" t="s">
+      <c r="F29" t="s">
         <v>114</v>
       </c>
     </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>115</v>
       </c>
@@ -2265,16 +2394,19 @@
         <v>436</v>
       </c>
       <c r="C30" t="s">
+        <v>436</v>
+      </c>
+      <c r="D30" t="s">
         <v>116</v>
       </c>
-      <c r="D30" t="s">
+      <c r="E30" t="s">
         <v>117</v>
       </c>
-      <c r="E30" t="s">
+      <c r="F30" t="s">
         <v>118</v>
       </c>
     </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>119</v>
       </c>
@@ -2282,16 +2414,19 @@
         <v>436</v>
       </c>
       <c r="C31" t="s">
+        <v>436</v>
+      </c>
+      <c r="D31" t="s">
         <v>120</v>
       </c>
-      <c r="D31" t="s">
+      <c r="E31" t="s">
         <v>121</v>
       </c>
-      <c r="E31" t="s">
+      <c r="F31" t="s">
         <v>122</v>
       </c>
     </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>123</v>
       </c>
@@ -2299,16 +2434,19 @@
         <v>436</v>
       </c>
       <c r="C32" t="s">
+        <v>436</v>
+      </c>
+      <c r="D32" t="s">
         <v>124</v>
       </c>
-      <c r="D32" t="s">
+      <c r="E32" t="s">
         <v>125</v>
       </c>
-      <c r="E32" t="s">
+      <c r="F32" t="s">
         <v>126</v>
       </c>
     </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>127</v>
       </c>
@@ -2316,16 +2454,19 @@
         <v>436</v>
       </c>
       <c r="C33" t="s">
+        <v>436</v>
+      </c>
+      <c r="D33" t="s">
         <v>128</v>
       </c>
-      <c r="D33" t="s">
+      <c r="E33" t="s">
         <v>129</v>
       </c>
-      <c r="E33" t="s">
+      <c r="F33" t="s">
         <v>130</v>
       </c>
     </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>131</v>
       </c>
@@ -2333,16 +2474,19 @@
         <v>443</v>
       </c>
       <c r="C34" t="s">
+        <v>454</v>
+      </c>
+      <c r="D34" t="s">
         <v>132</v>
       </c>
-      <c r="D34" t="s">
+      <c r="E34" t="s">
         <v>133</v>
       </c>
-      <c r="E34" t="s">
+      <c r="F34" t="s">
         <v>134</v>
       </c>
     </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>135</v>
       </c>
@@ -2350,16 +2494,19 @@
         <v>436</v>
       </c>
       <c r="C35" t="s">
+        <v>436</v>
+      </c>
+      <c r="D35" t="s">
         <v>136</v>
       </c>
-      <c r="D35" t="s">
+      <c r="E35" t="s">
         <v>137</v>
       </c>
-      <c r="E35" t="s">
+      <c r="F35" t="s">
         <v>138</v>
       </c>
     </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>139</v>
       </c>
@@ -2367,16 +2514,19 @@
         <v>436</v>
       </c>
       <c r="C36" t="s">
+        <v>436</v>
+      </c>
+      <c r="D36" t="s">
         <v>140</v>
       </c>
-      <c r="D36" t="s">
+      <c r="E36" t="s">
         <v>141</v>
       </c>
-      <c r="E36" t="s">
+      <c r="F36" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>143</v>
       </c>
@@ -2384,16 +2534,19 @@
         <v>436</v>
       </c>
       <c r="C37" t="s">
+        <v>436</v>
+      </c>
+      <c r="D37" t="s">
         <v>144</v>
       </c>
-      <c r="D37" t="s">
+      <c r="E37" t="s">
         <v>145</v>
       </c>
-      <c r="E37" t="s">
+      <c r="F37" t="s">
         <v>146</v>
       </c>
     </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>147</v>
       </c>
@@ -2401,16 +2554,19 @@
         <v>436</v>
       </c>
       <c r="C38" t="s">
+        <v>436</v>
+      </c>
+      <c r="D38" t="s">
         <v>148</v>
       </c>
-      <c r="D38" t="s">
+      <c r="E38" t="s">
         <v>149</v>
       </c>
-      <c r="E38" t="s">
+      <c r="F38" t="s">
         <v>150</v>
       </c>
     </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>151</v>
       </c>
@@ -2418,16 +2574,19 @@
         <v>444</v>
       </c>
       <c r="C39" t="s">
+        <v>455</v>
+      </c>
+      <c r="D39" t="s">
         <v>152</v>
       </c>
-      <c r="D39" t="s">
+      <c r="E39" t="s">
         <v>153</v>
       </c>
-      <c r="E39" t="s">
+      <c r="F39" t="s">
         <v>154</v>
       </c>
     </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>155</v>
       </c>
@@ -2435,16 +2594,19 @@
         <v>436</v>
       </c>
       <c r="C40" t="s">
+        <v>436</v>
+      </c>
+      <c r="D40" t="s">
         <v>156</v>
       </c>
-      <c r="D40" t="s">
+      <c r="E40" t="s">
         <v>157</v>
       </c>
-      <c r="E40" t="s">
+      <c r="F40" t="s">
         <v>158</v>
       </c>
     </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>159</v>
       </c>
@@ -2452,16 +2614,19 @@
         <v>436</v>
       </c>
       <c r="C41" t="s">
+        <v>436</v>
+      </c>
+      <c r="D41" t="s">
         <v>160</v>
       </c>
-      <c r="D41" t="s">
+      <c r="E41" t="s">
         <v>161</v>
       </c>
-      <c r="E41" t="s">
+      <c r="F41" t="s">
         <v>162</v>
       </c>
     </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>163</v>
       </c>
@@ -2469,16 +2634,19 @@
         <v>436</v>
       </c>
       <c r="C42" t="s">
+        <v>436</v>
+      </c>
+      <c r="D42" t="s">
         <v>164</v>
       </c>
-      <c r="D42" t="s">
+      <c r="E42" t="s">
         <v>165</v>
       </c>
-      <c r="E42" t="s">
+      <c r="F42" t="s">
         <v>166</v>
       </c>
     </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>167</v>
       </c>
@@ -2486,16 +2654,19 @@
         <v>436</v>
       </c>
       <c r="C43" t="s">
+        <v>436</v>
+      </c>
+      <c r="D43" t="s">
         <v>168</v>
       </c>
-      <c r="D43" t="s">
+      <c r="E43" t="s">
         <v>169</v>
       </c>
-      <c r="E43" t="s">
+      <c r="F43" t="s">
         <v>170</v>
       </c>
     </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>171</v>
       </c>
@@ -2503,16 +2674,19 @@
         <v>445</v>
       </c>
       <c r="C44" t="s">
+        <v>456</v>
+      </c>
+      <c r="D44" t="s">
         <v>172</v>
       </c>
-      <c r="D44" t="s">
+      <c r="E44" t="s">
         <v>173</v>
       </c>
-      <c r="E44" t="s">
+      <c r="F44" t="s">
         <v>174</v>
       </c>
     </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>175</v>
       </c>
@@ -2520,16 +2694,19 @@
         <v>436</v>
       </c>
       <c r="C45" t="s">
+        <v>436</v>
+      </c>
+      <c r="D45" t="s">
         <v>176</v>
       </c>
-      <c r="D45" t="s">
+      <c r="E45" t="s">
         <v>177</v>
       </c>
-      <c r="E45" t="s">
+      <c r="F45" t="s">
         <v>178</v>
       </c>
     </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>179</v>
       </c>
@@ -2537,16 +2714,19 @@
         <v>436</v>
       </c>
       <c r="C46" t="s">
+        <v>436</v>
+      </c>
+      <c r="D46" t="s">
         <v>180</v>
       </c>
-      <c r="D46" t="s">
+      <c r="E46" t="s">
         <v>181</v>
       </c>
-      <c r="E46" t="s">
+      <c r="F46" t="s">
         <v>182</v>
       </c>
     </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>183</v>
       </c>
@@ -2554,16 +2734,19 @@
         <v>436</v>
       </c>
       <c r="C47" t="s">
+        <v>436</v>
+      </c>
+      <c r="D47" t="s">
         <v>184</v>
       </c>
-      <c r="D47" t="s">
+      <c r="E47" t="s">
         <v>185</v>
       </c>
-      <c r="E47" t="s">
+      <c r="F47" t="s">
         <v>186</v>
       </c>
     </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>187</v>
       </c>
@@ -2571,16 +2754,19 @@
         <v>436</v>
       </c>
       <c r="C48" t="s">
+        <v>436</v>
+      </c>
+      <c r="D48" t="s">
         <v>188</v>
       </c>
-      <c r="D48" t="s">
+      <c r="E48" t="s">
         <v>189</v>
       </c>
-      <c r="E48" t="s">
+      <c r="F48" t="s">
         <v>190</v>
       </c>
     </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>191</v>
       </c>
@@ -2588,16 +2774,19 @@
         <v>446</v>
       </c>
       <c r="C49" t="s">
+        <v>457</v>
+      </c>
+      <c r="D49" t="s">
         <v>192</v>
       </c>
-      <c r="D49" t="s">
+      <c r="E49" t="s">
         <v>193</v>
       </c>
-      <c r="E49" t="s">
+      <c r="F49" t="s">
         <v>194</v>
       </c>
     </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>195</v>
       </c>
@@ -2605,16 +2794,19 @@
         <v>436</v>
       </c>
       <c r="C50" t="s">
+        <v>436</v>
+      </c>
+      <c r="D50" t="s">
         <v>196</v>
       </c>
-      <c r="D50" t="s">
+      <c r="E50" t="s">
         <v>197</v>
       </c>
-      <c r="E50" t="s">
+      <c r="F50" t="s">
         <v>198</v>
       </c>
     </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>199</v>
       </c>
@@ -2622,16 +2814,19 @@
         <v>436</v>
       </c>
       <c r="C51" t="s">
+        <v>436</v>
+      </c>
+      <c r="D51" t="s">
         <v>200</v>
       </c>
-      <c r="D51" t="s">
+      <c r="E51" t="s">
         <v>201</v>
       </c>
-      <c r="E51" t="s">
+      <c r="F51" t="s">
         <v>202</v>
       </c>
     </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>203</v>
       </c>
@@ -2639,16 +2834,19 @@
         <v>436</v>
       </c>
       <c r="C52" t="s">
+        <v>436</v>
+      </c>
+      <c r="D52" t="s">
         <v>204</v>
       </c>
-      <c r="D52" t="s">
+      <c r="E52" t="s">
         <v>205</v>
       </c>
-      <c r="E52" t="s">
+      <c r="F52" t="s">
         <v>206</v>
       </c>
     </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>207</v>
       </c>
@@ -2656,33 +2854,39 @@
         <v>436</v>
       </c>
       <c r="C53" t="s">
+        <v>436</v>
+      </c>
+      <c r="D53" t="s">
         <v>208</v>
       </c>
-      <c r="D53" t="s">
+      <c r="E53" t="s">
         <v>209</v>
       </c>
-      <c r="E53" t="s">
+      <c r="F53" t="s">
         <v>210</v>
       </c>
     </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>211</v>
       </c>
       <c r="B54" t="s">
-        <v>436</v>
+        <v>459</v>
       </c>
       <c r="C54" t="s">
+        <v>458</v>
+      </c>
+      <c r="D54" t="s">
         <v>212</v>
       </c>
-      <c r="D54" t="s">
+      <c r="E54" t="s">
         <v>213</v>
       </c>
-      <c r="E54" t="s">
+      <c r="F54" t="s">
         <v>214</v>
       </c>
     </row>
-    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>215</v>
       </c>
@@ -2690,16 +2894,19 @@
         <v>436</v>
       </c>
       <c r="C55" t="s">
+        <v>436</v>
+      </c>
+      <c r="D55" t="s">
         <v>216</v>
       </c>
-      <c r="D55" t="s">
+      <c r="E55" t="s">
         <v>217</v>
       </c>
-      <c r="E55" t="s">
+      <c r="F55" t="s">
         <v>218</v>
       </c>
     </row>
-    <row r="56" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>219</v>
       </c>
@@ -2707,16 +2914,19 @@
         <v>436</v>
       </c>
       <c r="C56" t="s">
+        <v>436</v>
+      </c>
+      <c r="D56" t="s">
         <v>220</v>
       </c>
-      <c r="D56" t="s">
+      <c r="E56" t="s">
         <v>221</v>
       </c>
-      <c r="E56" t="s">
+      <c r="F56" t="s">
         <v>222</v>
       </c>
     </row>
-    <row r="57" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>223</v>
       </c>
@@ -2724,16 +2934,19 @@
         <v>436</v>
       </c>
       <c r="C57" t="s">
+        <v>436</v>
+      </c>
+      <c r="D57" t="s">
         <v>224</v>
       </c>
-      <c r="D57" t="s">
+      <c r="E57" t="s">
         <v>225</v>
       </c>
-      <c r="E57" t="s">
+      <c r="F57" t="s">
         <v>226</v>
       </c>
     </row>
-    <row r="58" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>227</v>
       </c>
@@ -2741,33 +2954,39 @@
         <v>436</v>
       </c>
       <c r="C58" t="s">
+        <v>436</v>
+      </c>
+      <c r="D58" t="s">
         <v>228</v>
       </c>
-      <c r="D58" t="s">
+      <c r="E58" t="s">
         <v>229</v>
       </c>
-      <c r="E58" t="s">
+      <c r="F58" t="s">
         <v>230</v>
       </c>
     </row>
-    <row r="59" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>231</v>
       </c>
       <c r="B59" t="s">
-        <v>436</v>
+        <v>460</v>
       </c>
       <c r="C59" t="s">
+        <v>461</v>
+      </c>
+      <c r="D59" t="s">
         <v>232</v>
       </c>
-      <c r="D59" t="s">
+      <c r="E59" t="s">
         <v>233</v>
       </c>
-      <c r="E59" t="s">
+      <c r="F59" t="s">
         <v>234</v>
       </c>
     </row>
-    <row r="60" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>235</v>
       </c>
@@ -2775,16 +2994,19 @@
         <v>436</v>
       </c>
       <c r="C60" t="s">
+        <v>436</v>
+      </c>
+      <c r="D60" t="s">
         <v>236</v>
       </c>
-      <c r="D60" t="s">
+      <c r="E60" t="s">
         <v>237</v>
       </c>
-      <c r="E60" t="s">
+      <c r="F60" t="s">
         <v>238</v>
       </c>
     </row>
-    <row r="61" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>239</v>
       </c>
@@ -2792,16 +3014,19 @@
         <v>436</v>
       </c>
       <c r="C61" t="s">
+        <v>436</v>
+      </c>
+      <c r="D61" t="s">
         <v>240</v>
       </c>
-      <c r="D61" t="s">
+      <c r="E61" t="s">
         <v>241</v>
       </c>
-      <c r="E61" t="s">
+      <c r="F61" t="s">
         <v>242</v>
       </c>
     </row>
-    <row r="62" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>243</v>
       </c>
@@ -2809,16 +3034,19 @@
         <v>436</v>
       </c>
       <c r="C62" t="s">
+        <v>436</v>
+      </c>
+      <c r="D62" t="s">
         <v>244</v>
       </c>
-      <c r="D62" t="s">
+      <c r="E62" t="s">
         <v>245</v>
       </c>
-      <c r="E62" t="s">
+      <c r="F62" t="s">
         <v>246</v>
       </c>
     </row>
-    <row r="63" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>247</v>
       </c>
@@ -2826,16 +3054,19 @@
         <v>436</v>
       </c>
       <c r="C63" t="s">
+        <v>436</v>
+      </c>
+      <c r="D63" t="s">
         <v>248</v>
       </c>
-      <c r="D63" t="s">
+      <c r="E63" t="s">
         <v>249</v>
       </c>
-      <c r="E63" t="s">
+      <c r="F63" t="s">
         <v>250</v>
       </c>
     </row>
-    <row r="64" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>251</v>
       </c>
@@ -2843,16 +3074,19 @@
         <v>436</v>
       </c>
       <c r="C64" t="s">
+        <v>436</v>
+      </c>
+      <c r="D64" t="s">
         <v>252</v>
       </c>
-      <c r="D64" t="s">
+      <c r="E64" t="s">
         <v>253</v>
       </c>
-      <c r="E64" t="s">
+      <c r="F64" t="s">
         <v>254</v>
       </c>
     </row>
-    <row r="65" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>255</v>
       </c>
@@ -2860,16 +3094,19 @@
         <v>436</v>
       </c>
       <c r="C65" t="s">
+        <v>436</v>
+      </c>
+      <c r="D65" t="s">
         <v>256</v>
       </c>
-      <c r="D65" t="s">
+      <c r="E65" t="s">
         <v>257</v>
       </c>
-      <c r="E65" t="s">
+      <c r="F65" t="s">
         <v>258</v>
       </c>
     </row>
-    <row r="66" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>259</v>
       </c>
@@ -2877,16 +3114,19 @@
         <v>436</v>
       </c>
       <c r="C66" t="s">
+        <v>436</v>
+      </c>
+      <c r="D66" t="s">
         <v>260</v>
       </c>
-      <c r="D66" t="s">
+      <c r="E66" t="s">
         <v>261</v>
       </c>
-      <c r="E66" t="s">
+      <c r="F66" t="s">
         <v>262</v>
       </c>
     </row>
-    <row r="67" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>263</v>
       </c>
@@ -2894,16 +3134,19 @@
         <v>436</v>
       </c>
       <c r="C67" t="s">
+        <v>436</v>
+      </c>
+      <c r="D67" t="s">
         <v>264</v>
       </c>
-      <c r="D67" t="s">
+      <c r="E67" t="s">
         <v>265</v>
       </c>
-      <c r="E67" t="s">
+      <c r="F67" t="s">
         <v>266</v>
       </c>
     </row>
-    <row r="68" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
         <v>267</v>
       </c>
@@ -2911,16 +3154,19 @@
         <v>436</v>
       </c>
       <c r="C68" t="s">
+        <v>436</v>
+      </c>
+      <c r="D68" t="s">
         <v>268</v>
       </c>
-      <c r="D68" t="s">
+      <c r="E68" t="s">
         <v>269</v>
       </c>
-      <c r="E68" t="s">
+      <c r="F68" t="s">
         <v>270</v>
       </c>
     </row>
-    <row r="69" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
         <v>271</v>
       </c>
@@ -2928,16 +3174,19 @@
         <v>436</v>
       </c>
       <c r="C69" t="s">
+        <v>436</v>
+      </c>
+      <c r="D69" t="s">
         <v>272</v>
       </c>
-      <c r="D69" t="s">
+      <c r="E69" t="s">
         <v>273</v>
       </c>
-      <c r="E69" t="s">
+      <c r="F69" t="s">
         <v>274</v>
       </c>
     </row>
-    <row r="70" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
         <v>275</v>
       </c>
@@ -2945,16 +3194,19 @@
         <v>436</v>
       </c>
       <c r="C70" t="s">
+        <v>436</v>
+      </c>
+      <c r="D70" t="s">
         <v>276</v>
       </c>
-      <c r="D70" t="s">
+      <c r="E70" t="s">
         <v>277</v>
       </c>
-      <c r="E70" t="s">
+      <c r="F70" t="s">
         <v>278</v>
       </c>
     </row>
-    <row r="71" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
         <v>279</v>
       </c>
@@ -2962,16 +3214,19 @@
         <v>436</v>
       </c>
       <c r="C71" t="s">
+        <v>436</v>
+      </c>
+      <c r="D71" t="s">
         <v>280</v>
       </c>
-      <c r="D71" t="s">
+      <c r="E71" t="s">
         <v>281</v>
       </c>
-      <c r="E71" t="s">
+      <c r="F71" t="s">
         <v>282</v>
       </c>
     </row>
-    <row r="72" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
         <v>283</v>
       </c>
@@ -2979,16 +3234,19 @@
         <v>436</v>
       </c>
       <c r="C72" t="s">
+        <v>436</v>
+      </c>
+      <c r="D72" t="s">
         <v>284</v>
       </c>
-      <c r="D72" t="s">
+      <c r="E72" t="s">
         <v>285</v>
       </c>
-      <c r="E72" t="s">
+      <c r="F72" t="s">
         <v>286</v>
       </c>
     </row>
-    <row r="73" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
         <v>287</v>
       </c>
@@ -2996,16 +3254,19 @@
         <v>436</v>
       </c>
       <c r="C73" t="s">
+        <v>436</v>
+      </c>
+      <c r="D73" t="s">
         <v>288</v>
       </c>
-      <c r="D73" t="s">
+      <c r="E73" t="s">
         <v>289</v>
       </c>
-      <c r="E73" t="s">
+      <c r="F73" t="s">
         <v>290</v>
       </c>
     </row>
-    <row r="74" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
         <v>291</v>
       </c>
@@ -3013,16 +3274,19 @@
         <v>436</v>
       </c>
       <c r="C74" t="s">
+        <v>436</v>
+      </c>
+      <c r="D74" t="s">
         <v>292</v>
       </c>
-      <c r="D74" t="s">
+      <c r="E74" t="s">
         <v>293</v>
       </c>
-      <c r="E74" t="s">
+      <c r="F74" t="s">
         <v>294</v>
       </c>
     </row>
-    <row r="75" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
         <v>295</v>
       </c>
@@ -3030,16 +3294,19 @@
         <v>436</v>
       </c>
       <c r="C75" t="s">
+        <v>436</v>
+      </c>
+      <c r="D75" t="s">
         <v>296</v>
       </c>
-      <c r="D75" t="s">
+      <c r="E75" t="s">
         <v>297</v>
       </c>
-      <c r="E75" t="s">
+      <c r="F75" t="s">
         <v>298</v>
       </c>
     </row>
-    <row r="76" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
         <v>299</v>
       </c>
@@ -3047,16 +3314,19 @@
         <v>436</v>
       </c>
       <c r="C76" t="s">
+        <v>436</v>
+      </c>
+      <c r="D76" t="s">
         <v>300</v>
       </c>
-      <c r="D76" t="s">
+      <c r="E76" t="s">
         <v>301</v>
       </c>
-      <c r="E76" t="s">
+      <c r="F76" t="s">
         <v>302</v>
       </c>
     </row>
-    <row r="77" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
         <v>303</v>
       </c>
@@ -3064,16 +3334,19 @@
         <v>436</v>
       </c>
       <c r="C77" t="s">
+        <v>436</v>
+      </c>
+      <c r="D77" t="s">
         <v>304</v>
       </c>
-      <c r="D77" t="s">
+      <c r="E77" t="s">
         <v>305</v>
       </c>
-      <c r="E77" t="s">
+      <c r="F77" t="s">
         <v>306</v>
       </c>
     </row>
-    <row r="78" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
         <v>307</v>
       </c>
@@ -3081,16 +3354,19 @@
         <v>436</v>
       </c>
       <c r="C78" t="s">
+        <v>436</v>
+      </c>
+      <c r="D78" t="s">
         <v>308</v>
       </c>
-      <c r="D78" t="s">
+      <c r="E78" t="s">
         <v>309</v>
       </c>
-      <c r="E78" t="s">
+      <c r="F78" t="s">
         <v>310</v>
       </c>
     </row>
-    <row r="79" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
         <v>311</v>
       </c>
@@ -3098,16 +3374,19 @@
         <v>436</v>
       </c>
       <c r="C79" t="s">
+        <v>436</v>
+      </c>
+      <c r="D79" t="s">
         <v>312</v>
       </c>
-      <c r="D79" t="s">
+      <c r="E79" t="s">
         <v>313</v>
       </c>
-      <c r="E79" t="s">
+      <c r="F79" t="s">
         <v>314</v>
       </c>
     </row>
-    <row r="80" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
         <v>315</v>
       </c>
@@ -3115,16 +3394,19 @@
         <v>436</v>
       </c>
       <c r="C80" t="s">
+        <v>436</v>
+      </c>
+      <c r="D80" t="s">
         <v>316</v>
       </c>
-      <c r="D80" t="s">
+      <c r="E80" t="s">
         <v>317</v>
       </c>
-      <c r="E80" t="s">
+      <c r="F80" t="s">
         <v>318</v>
       </c>
     </row>
-    <row r="81" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
         <v>319</v>
       </c>
@@ -3132,16 +3414,19 @@
         <v>436</v>
       </c>
       <c r="C81" t="s">
+        <v>436</v>
+      </c>
+      <c r="D81" t="s">
         <v>320</v>
       </c>
-      <c r="D81" t="s">
+      <c r="E81" t="s">
         <v>321</v>
       </c>
-      <c r="E81" t="s">
+      <c r="F81" t="s">
         <v>322</v>
       </c>
     </row>
-    <row r="82" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
         <v>323</v>
       </c>
@@ -3149,16 +3434,19 @@
         <v>436</v>
       </c>
       <c r="C82" t="s">
+        <v>436</v>
+      </c>
+      <c r="D82" t="s">
         <v>324</v>
       </c>
-      <c r="D82" t="s">
+      <c r="E82" t="s">
         <v>325</v>
       </c>
-      <c r="E82" t="s">
+      <c r="F82" t="s">
         <v>326</v>
       </c>
     </row>
-    <row r="83" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
         <v>327</v>
       </c>
@@ -3166,16 +3454,19 @@
         <v>436</v>
       </c>
       <c r="C83" t="s">
+        <v>436</v>
+      </c>
+      <c r="D83" t="s">
         <v>328</v>
       </c>
-      <c r="D83" t="s">
+      <c r="E83" t="s">
         <v>329</v>
       </c>
-      <c r="E83" t="s">
+      <c r="F83" t="s">
         <v>330</v>
       </c>
     </row>
-    <row r="84" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
         <v>331</v>
       </c>
@@ -3183,16 +3474,19 @@
         <v>436</v>
       </c>
       <c r="C84" t="s">
+        <v>436</v>
+      </c>
+      <c r="D84" t="s">
         <v>332</v>
       </c>
-      <c r="D84" t="s">
+      <c r="E84" t="s">
         <v>333</v>
       </c>
-      <c r="E84" t="s">
+      <c r="F84" t="s">
         <v>334</v>
       </c>
     </row>
-    <row r="85" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
         <v>335</v>
       </c>
@@ -3200,16 +3494,19 @@
         <v>436</v>
       </c>
       <c r="C85" t="s">
+        <v>436</v>
+      </c>
+      <c r="D85" t="s">
         <v>336</v>
       </c>
-      <c r="D85" t="s">
+      <c r="E85" t="s">
         <v>337</v>
       </c>
-      <c r="E85" t="s">
+      <c r="F85" t="s">
         <v>338</v>
       </c>
     </row>
-    <row r="86" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
         <v>339</v>
       </c>
@@ -3217,16 +3514,19 @@
         <v>436</v>
       </c>
       <c r="C86" t="s">
+        <v>436</v>
+      </c>
+      <c r="D86" t="s">
         <v>340</v>
       </c>
-      <c r="D86" t="s">
+      <c r="E86" t="s">
         <v>341</v>
       </c>
-      <c r="E86" t="s">
+      <c r="F86" t="s">
         <v>342</v>
       </c>
     </row>
-    <row r="87" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
         <v>343</v>
       </c>
@@ -3234,16 +3534,19 @@
         <v>436</v>
       </c>
       <c r="C87" t="s">
+        <v>436</v>
+      </c>
+      <c r="D87" t="s">
         <v>344</v>
       </c>
-      <c r="D87" t="s">
+      <c r="E87" t="s">
         <v>345</v>
       </c>
-      <c r="E87" t="s">
+      <c r="F87" t="s">
         <v>346</v>
       </c>
     </row>
-    <row r="88" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
         <v>347</v>
       </c>
@@ -3251,16 +3554,19 @@
         <v>436</v>
       </c>
       <c r="C88" t="s">
+        <v>436</v>
+      </c>
+      <c r="D88" t="s">
         <v>348</v>
       </c>
-      <c r="D88" t="s">
+      <c r="E88" t="s">
         <v>349</v>
       </c>
-      <c r="E88" t="s">
+      <c r="F88" t="s">
         <v>350</v>
       </c>
     </row>
-    <row r="89" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
         <v>351</v>
       </c>
@@ -3268,16 +3574,19 @@
         <v>436</v>
       </c>
       <c r="C89" t="s">
+        <v>436</v>
+      </c>
+      <c r="D89" t="s">
         <v>352</v>
       </c>
-      <c r="D89" t="s">
+      <c r="E89" t="s">
         <v>353</v>
       </c>
-      <c r="E89" t="s">
+      <c r="F89" t="s">
         <v>354</v>
       </c>
     </row>
-    <row r="90" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
         <v>355</v>
       </c>
@@ -3285,16 +3594,19 @@
         <v>436</v>
       </c>
       <c r="C90" t="s">
+        <v>436</v>
+      </c>
+      <c r="D90" t="s">
         <v>356</v>
       </c>
-      <c r="D90" t="s">
+      <c r="E90" t="s">
         <v>357</v>
       </c>
-      <c r="E90" t="s">
+      <c r="F90" t="s">
         <v>358</v>
       </c>
     </row>
-    <row r="91" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
         <v>359</v>
       </c>
@@ -3302,16 +3614,19 @@
         <v>436</v>
       </c>
       <c r="C91" t="s">
+        <v>436</v>
+      </c>
+      <c r="D91" t="s">
         <v>360</v>
       </c>
-      <c r="D91" t="s">
+      <c r="E91" t="s">
         <v>361</v>
       </c>
-      <c r="E91" t="s">
+      <c r="F91" t="s">
         <v>362</v>
       </c>
     </row>
-    <row r="92" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
         <v>363</v>
       </c>
@@ -3319,16 +3634,19 @@
         <v>436</v>
       </c>
       <c r="C92" t="s">
+        <v>436</v>
+      </c>
+      <c r="D92" t="s">
         <v>364</v>
       </c>
-      <c r="D92" t="s">
+      <c r="E92" t="s">
         <v>365</v>
       </c>
-      <c r="E92" t="s">
+      <c r="F92" t="s">
         <v>366</v>
       </c>
     </row>
-    <row r="93" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
         <v>367</v>
       </c>
@@ -3336,16 +3654,19 @@
         <v>436</v>
       </c>
       <c r="C93" t="s">
+        <v>436</v>
+      </c>
+      <c r="D93" t="s">
         <v>368</v>
       </c>
-      <c r="D93" t="s">
+      <c r="E93" t="s">
         <v>369</v>
       </c>
-      <c r="E93" t="s">
+      <c r="F93" t="s">
         <v>370</v>
       </c>
     </row>
-    <row r="94" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
         <v>371</v>
       </c>
@@ -3353,16 +3674,19 @@
         <v>436</v>
       </c>
       <c r="C94" t="s">
+        <v>436</v>
+      </c>
+      <c r="D94" t="s">
         <v>372</v>
       </c>
-      <c r="D94" t="s">
+      <c r="E94" t="s">
         <v>373</v>
       </c>
-      <c r="E94" t="s">
+      <c r="F94" t="s">
         <v>374</v>
       </c>
     </row>
-    <row r="95" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
         <v>375</v>
       </c>
@@ -3370,16 +3694,19 @@
         <v>436</v>
       </c>
       <c r="C95" t="s">
+        <v>436</v>
+      </c>
+      <c r="D95" t="s">
         <v>376</v>
       </c>
-      <c r="D95" t="s">
+      <c r="E95" t="s">
         <v>377</v>
       </c>
-      <c r="E95" t="s">
+      <c r="F95" t="s">
         <v>378</v>
       </c>
     </row>
-    <row r="96" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
         <v>379</v>
       </c>
@@ -3387,16 +3714,19 @@
         <v>436</v>
       </c>
       <c r="C96" t="s">
+        <v>436</v>
+      </c>
+      <c r="D96" t="s">
         <v>380</v>
       </c>
-      <c r="D96" t="s">
+      <c r="E96" t="s">
         <v>381</v>
       </c>
-      <c r="E96" t="s">
+      <c r="F96" t="s">
         <v>382</v>
       </c>
     </row>
-    <row r="97" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
         <v>383</v>
       </c>
@@ -3404,16 +3734,19 @@
         <v>436</v>
       </c>
       <c r="C97" t="s">
+        <v>436</v>
+      </c>
+      <c r="D97" t="s">
         <v>384</v>
       </c>
-      <c r="D97" t="s">
+      <c r="E97" t="s">
         <v>385</v>
       </c>
-      <c r="E97" t="s">
+      <c r="F97" t="s">
         <v>386</v>
       </c>
     </row>
-    <row r="98" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
         <v>387</v>
       </c>
@@ -3421,16 +3754,19 @@
         <v>436</v>
       </c>
       <c r="C98" t="s">
+        <v>436</v>
+      </c>
+      <c r="D98" t="s">
         <v>388</v>
       </c>
-      <c r="D98" t="s">
+      <c r="E98" t="s">
         <v>389</v>
       </c>
-      <c r="E98" t="s">
+      <c r="F98" t="s">
         <v>390</v>
       </c>
     </row>
-    <row r="99" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
         <v>391</v>
       </c>
@@ -3438,16 +3774,19 @@
         <v>436</v>
       </c>
       <c r="C99" t="s">
+        <v>436</v>
+      </c>
+      <c r="D99" t="s">
         <v>392</v>
       </c>
-      <c r="D99" t="s">
+      <c r="E99" t="s">
         <v>393</v>
       </c>
-      <c r="E99" t="s">
+      <c r="F99" t="s">
         <v>394</v>
       </c>
     </row>
-    <row r="100" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
         <v>395</v>
       </c>
@@ -3455,16 +3794,19 @@
         <v>436</v>
       </c>
       <c r="C100" t="s">
+        <v>436</v>
+      </c>
+      <c r="D100" t="s">
         <v>396</v>
       </c>
-      <c r="D100" t="s">
+      <c r="E100" t="s">
         <v>397</v>
       </c>
-      <c r="E100" t="s">
+      <c r="F100" t="s">
         <v>398</v>
       </c>
     </row>
-    <row r="101" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
         <v>399</v>
       </c>
@@ -3472,16 +3814,19 @@
         <v>436</v>
       </c>
       <c r="C101" t="s">
+        <v>436</v>
+      </c>
+      <c r="D101" t="s">
         <v>400</v>
       </c>
-      <c r="D101" t="s">
+      <c r="E101" t="s">
         <v>401</v>
       </c>
-      <c r="E101" t="s">
+      <c r="F101" t="s">
         <v>402</v>
       </c>
     </row>
-    <row r="102" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
         <v>403</v>
       </c>
@@ -3489,16 +3834,19 @@
         <v>436</v>
       </c>
       <c r="C102" t="s">
+        <v>436</v>
+      </c>
+      <c r="D102" t="s">
         <v>404</v>
       </c>
-      <c r="D102" t="s">
+      <c r="E102" t="s">
         <v>405</v>
       </c>
-      <c r="E102" t="s">
+      <c r="F102" t="s">
         <v>406</v>
       </c>
     </row>
-    <row r="103" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
         <v>407</v>
       </c>
@@ -3506,16 +3854,19 @@
         <v>436</v>
       </c>
       <c r="C103" t="s">
+        <v>436</v>
+      </c>
+      <c r="D103" t="s">
         <v>408</v>
       </c>
-      <c r="D103" t="s">
+      <c r="E103" t="s">
         <v>409</v>
       </c>
-      <c r="E103" t="s">
+      <c r="F103" t="s">
         <v>410</v>
       </c>
     </row>
-    <row r="104" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
         <v>411</v>
       </c>
@@ -3523,16 +3874,19 @@
         <v>436</v>
       </c>
       <c r="C104" t="s">
+        <v>436</v>
+      </c>
+      <c r="D104" t="s">
         <v>412</v>
       </c>
-      <c r="D104" t="s">
+      <c r="E104" t="s">
         <v>413</v>
       </c>
-      <c r="E104" t="s">
+      <c r="F104" t="s">
         <v>414</v>
       </c>
     </row>
-    <row r="105" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
         <v>415</v>
       </c>
@@ -3540,16 +3894,19 @@
         <v>436</v>
       </c>
       <c r="C105" t="s">
+        <v>436</v>
+      </c>
+      <c r="D105" t="s">
         <v>416</v>
       </c>
-      <c r="D105" t="s">
+      <c r="E105" t="s">
         <v>417</v>
       </c>
-      <c r="E105" t="s">
+      <c r="F105" t="s">
         <v>418</v>
       </c>
     </row>
-    <row r="106" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
         <v>419</v>
       </c>
@@ -3557,16 +3914,19 @@
         <v>436</v>
       </c>
       <c r="C106" t="s">
+        <v>436</v>
+      </c>
+      <c r="D106" t="s">
         <v>420</v>
       </c>
-      <c r="D106" t="s">
+      <c r="E106" t="s">
         <v>421</v>
       </c>
-      <c r="E106" t="s">
+      <c r="F106" t="s">
         <v>422</v>
       </c>
     </row>
-    <row r="107" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
         <v>423</v>
       </c>
@@ -3574,16 +3934,19 @@
         <v>436</v>
       </c>
       <c r="C107" t="s">
+        <v>436</v>
+      </c>
+      <c r="D107" t="s">
         <v>424</v>
       </c>
-      <c r="D107" t="s">
+      <c r="E107" t="s">
         <v>425</v>
       </c>
-      <c r="E107" t="s">
+      <c r="F107" t="s">
         <v>426</v>
       </c>
     </row>
-    <row r="108" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
         <v>427</v>
       </c>
@@ -3591,16 +3954,19 @@
         <v>436</v>
       </c>
       <c r="C108" t="s">
+        <v>436</v>
+      </c>
+      <c r="D108" t="s">
         <v>428</v>
       </c>
-      <c r="D108" t="s">
+      <c r="E108" t="s">
         <v>429</v>
       </c>
-      <c r="E108" t="s">
+      <c r="F108" t="s">
         <v>430</v>
       </c>
     </row>
-    <row r="109" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
         <v>431</v>
       </c>
@@ -3608,12 +3974,15 @@
         <v>436</v>
       </c>
       <c r="C109" t="s">
+        <v>436</v>
+      </c>
+      <c r="D109" t="s">
         <v>432</v>
       </c>
-      <c r="D109" t="s">
+      <c r="E109" t="s">
         <v>433</v>
       </c>
-      <c r="E109" t="s">
+      <c r="F109" t="s">
         <v>434</v>
       </c>
     </row>
@@ -3621,7 +3990,7 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
   <ignoredErrors>
-    <ignoredError sqref="A2:A109 C1:C109 D1:D109 E1:E109" numberStoredAsText="1"/>
+    <ignoredError sqref="A2:A109 D1:D109 E1:E109 F1:F109" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/grilla.xlsx
+++ b/grilla.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aetch\Desktop\proyecto_aamas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{129F7578-4FCF-400B-ACA1-CEBCAB3876C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A78DE81A-290B-42A1-9E9A-AFE0D8D41885}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4275" yWindow="4275" windowWidth="21600" windowHeight="11385" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="10440" yWindow="3780" windowWidth="21600" windowHeight="11385" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Grilla" sheetId="1" r:id="rId1"/>
@@ -942,7 +942,7 @@
         <v>9239.39</v>
       </c>
       <c r="F9">
-        <v>7921.86</v>
+        <v>7921.03</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
@@ -1036,13 +1036,13 @@
         <v>22315.55</v>
       </c>
       <c r="D14">
-        <v>19030.63</v>
+        <v>18030.63</v>
       </c>
       <c r="E14">
         <v>13859.09</v>
       </c>
       <c r="F14">
-        <v>11882.8</v>
+        <v>11881.54</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
@@ -1142,7 +1142,7 @@
         <v>18478.79</v>
       </c>
       <c r="F19">
-        <v>15843.72</v>
+        <v>15842.05</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
@@ -1242,7 +1242,7 @@
         <v>23098.48</v>
       </c>
       <c r="F24">
-        <v>19804.66</v>
+        <v>19802.560000000001</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
@@ -1342,7 +1342,7 @@
         <v>27718.18</v>
       </c>
       <c r="F29">
-        <v>23765.599999999999</v>
+        <v>23763.08</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
@@ -1442,7 +1442,7 @@
         <v>32337.88</v>
       </c>
       <c r="F34">
-        <v>27726.52</v>
+        <v>27723.59</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
@@ -1542,7 +1542,7 @@
         <v>36957.57</v>
       </c>
       <c r="F39">
-        <v>31687.46</v>
+        <v>31684.1</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
@@ -1642,7 +1642,7 @@
         <v>41557.269999999997</v>
       </c>
       <c r="F44">
-        <v>35648.39</v>
+        <v>35644.620000000003</v>
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.25">
@@ -1742,7 +1742,7 @@
         <v>46196.97</v>
       </c>
       <c r="F49">
-        <v>39609.32</v>
+        <v>39605.129999999997</v>
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.25">
@@ -1842,7 +1842,7 @@
         <v>50816.66</v>
       </c>
       <c r="F54">
-        <v>43570.26</v>
+        <v>43565.64</v>
       </c>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.25">
@@ -1942,7 +1942,7 @@
         <v>55436.36</v>
       </c>
       <c r="F59">
-        <v>47531.18</v>
+        <v>47526.16</v>
       </c>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.25">

--- a/grilla.xlsx
+++ b/grilla.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aetch\Desktop\proyecto_aamas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A78DE81A-290B-42A1-9E9A-AFE0D8D41885}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B68E9204-576A-413E-9AD8-17E4F64024A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="10440" yWindow="3780" windowWidth="21600" windowHeight="11385" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3120" yWindow="3120" windowWidth="21600" windowHeight="11385" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Grilla" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="307" uniqueCount="115">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="404" uniqueCount="116">
   <si>
     <t>Cuotas12</t>
   </si>
@@ -379,6 +379,9 @@
   </si>
   <si>
     <t>Cuotas9</t>
+  </si>
+  <si>
+    <t>Cuotas3</t>
   </si>
 </sst>
 </file>
@@ -757,35 +760,38 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F109"/>
+  <dimension ref="A1:G109"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="13.875" customWidth="1"/>
-    <col min="2" max="3" width="11.25" style="2" customWidth="1"/>
-    <col min="4" max="6" width="12.5" customWidth="1"/>
+    <col min="2" max="4" width="11.25" style="2" customWidth="1"/>
+    <col min="5" max="7" width="12.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>111</v>
       </c>
       <c r="B1" t="s">
+        <v>115</v>
+      </c>
+      <c r="C1" t="s">
         <v>113</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>114</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>0</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>1</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -795,17 +801,20 @@
       <c r="C2" t="s">
         <v>112</v>
       </c>
-      <c r="D2">
+      <c r="D2" t="s">
+        <v>112</v>
+      </c>
+      <c r="E2">
         <v>3606.13</v>
       </c>
-      <c r="E2">
+      <c r="F2">
         <v>2771.82</v>
       </c>
-      <c r="F2">
+      <c r="G2">
         <v>2376.56</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>4</v>
       </c>
@@ -815,17 +824,20 @@
       <c r="C3" t="s">
         <v>112</v>
       </c>
-      <c r="D3">
+      <c r="D3" t="s">
+        <v>112</v>
+      </c>
+      <c r="E3">
         <v>4808.17</v>
       </c>
-      <c r="E3">
+      <c r="F3">
         <v>3695.76</v>
       </c>
-      <c r="F3">
+      <c r="G3">
         <v>3168.75</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>5</v>
       </c>
@@ -835,17 +847,20 @@
       <c r="C4" t="s">
         <v>112</v>
       </c>
-      <c r="D4">
+      <c r="D4" t="s">
+        <v>112</v>
+      </c>
+      <c r="E4">
         <v>6010.21</v>
       </c>
-      <c r="E4">
+      <c r="F4">
         <v>4619.7</v>
       </c>
-      <c r="F4">
+      <c r="G4">
         <v>3960.94</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>6</v>
       </c>
@@ -855,17 +870,20 @@
       <c r="C5" t="s">
         <v>112</v>
       </c>
-      <c r="D5">
+      <c r="D5" t="s">
+        <v>112</v>
+      </c>
+      <c r="E5">
         <v>7212.25</v>
       </c>
-      <c r="E5">
+      <c r="F5">
         <v>5543.64</v>
       </c>
-      <c r="F5">
+      <c r="G5">
         <v>4753.12</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>7</v>
       </c>
@@ -875,17 +893,20 @@
       <c r="C6" t="s">
         <v>112</v>
       </c>
-      <c r="D6">
+      <c r="D6" t="s">
+        <v>112</v>
+      </c>
+      <c r="E6">
         <v>8414.2999999999993</v>
       </c>
-      <c r="E6">
+      <c r="F6">
         <v>6467.58</v>
       </c>
-      <c r="F6">
+      <c r="G6">
         <v>5545.3</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>8</v>
       </c>
@@ -895,17 +916,20 @@
       <c r="C7" t="s">
         <v>112</v>
       </c>
-      <c r="D7">
+      <c r="D7" t="s">
+        <v>112</v>
+      </c>
+      <c r="E7">
         <v>9616.64</v>
       </c>
-      <c r="E7" s="1">
+      <c r="F7" s="1">
         <v>7391.51</v>
       </c>
-      <c r="F7">
+      <c r="G7">
         <v>6337.49</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>9</v>
       </c>
@@ -915,57 +939,66 @@
       <c r="C8" t="s">
         <v>112</v>
       </c>
-      <c r="D8">
+      <c r="D8" t="s">
+        <v>112</v>
+      </c>
+      <c r="E8">
         <v>10818.38</v>
       </c>
-      <c r="E8">
+      <c r="F8">
         <v>8315.4500000000007</v>
       </c>
-      <c r="F8">
+      <c r="G8">
         <v>7129.68</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>10</v>
       </c>
       <c r="B9">
+        <v>38197.839999999997</v>
+      </c>
+      <c r="C9">
         <v>20667.89</v>
       </c>
-      <c r="C9">
+      <c r="D9">
         <v>14877.03</v>
       </c>
-      <c r="D9">
+      <c r="E9">
         <v>12020.42</v>
       </c>
-      <c r="E9">
+      <c r="F9">
         <v>9239.39</v>
       </c>
-      <c r="F9">
+      <c r="G9">
         <v>7921.03</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>11</v>
       </c>
       <c r="B10">
         <v>22734.68</v>
       </c>
-      <c r="C10" t="s">
-        <v>112</v>
-      </c>
-      <c r="D10">
+      <c r="C10">
+        <v>22734.68</v>
+      </c>
+      <c r="D10" t="s">
+        <v>112</v>
+      </c>
+      <c r="E10">
         <v>13222.46</v>
       </c>
-      <c r="E10">
+      <c r="F10">
         <v>10163.33</v>
       </c>
-      <c r="F10">
+      <c r="G10">
         <v>8714.0499999999993</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>12</v>
       </c>
@@ -975,17 +1008,20 @@
       <c r="C11" t="s">
         <v>112</v>
       </c>
-      <c r="D11">
+      <c r="D11" t="s">
+        <v>112</v>
+      </c>
+      <c r="E11">
         <v>14424.51</v>
       </c>
-      <c r="E11">
+      <c r="F11">
         <v>11087.27</v>
       </c>
-      <c r="F11">
+      <c r="G11">
         <v>9506.24</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>13</v>
       </c>
@@ -995,17 +1031,20 @@
       <c r="C12" t="s">
         <v>112</v>
       </c>
-      <c r="D12">
+      <c r="D12" t="s">
+        <v>112</v>
+      </c>
+      <c r="E12">
         <v>15626.55</v>
       </c>
-      <c r="E12">
+      <c r="F12">
         <v>12011.21</v>
       </c>
-      <c r="F12">
+      <c r="G12">
         <v>10298.42</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>14</v>
       </c>
@@ -1015,37 +1054,43 @@
       <c r="C13" t="s">
         <v>112</v>
       </c>
-      <c r="D13">
+      <c r="D13" t="s">
+        <v>112</v>
+      </c>
+      <c r="E13">
         <v>16828.59</v>
       </c>
-      <c r="E13">
+      <c r="F13">
         <v>12935.15</v>
       </c>
-      <c r="F13">
+      <c r="G13">
         <v>11090.61</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>15</v>
       </c>
       <c r="B14">
+        <v>57296.76</v>
+      </c>
+      <c r="C14">
         <v>31001.84</v>
       </c>
-      <c r="C14">
+      <c r="D14">
         <v>22315.55</v>
       </c>
-      <c r="D14">
+      <c r="E14">
         <v>18030.63</v>
       </c>
-      <c r="E14">
+      <c r="F14">
         <v>13859.09</v>
       </c>
-      <c r="F14">
+      <c r="G14">
         <v>11881.54</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>16</v>
       </c>
@@ -1055,17 +1100,20 @@
       <c r="C15" t="s">
         <v>112</v>
       </c>
-      <c r="D15">
+      <c r="D15" t="s">
+        <v>112</v>
+      </c>
+      <c r="E15">
         <v>19232.68</v>
       </c>
-      <c r="E15">
+      <c r="F15">
         <v>14783.03</v>
       </c>
-      <c r="F15">
+      <c r="G15">
         <v>12674.99</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>17</v>
       </c>
@@ -1075,17 +1123,20 @@
       <c r="C16" t="s">
         <v>112</v>
       </c>
-      <c r="D16">
+      <c r="D16" t="s">
+        <v>112</v>
+      </c>
+      <c r="E16">
         <v>20434.72</v>
       </c>
-      <c r="E16">
+      <c r="F16">
         <v>15706.87</v>
       </c>
-      <c r="F16">
+      <c r="G16">
         <v>13467.17</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>18</v>
       </c>
@@ -1095,17 +1146,20 @@
       <c r="C17" t="s">
         <v>112</v>
       </c>
-      <c r="D17">
+      <c r="D17" t="s">
+        <v>112</v>
+      </c>
+      <c r="E17">
         <v>21636.76</v>
       </c>
-      <c r="E17">
+      <c r="F17">
         <v>16630.91</v>
       </c>
-      <c r="F17">
+      <c r="G17">
         <v>14259.36</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>19</v>
       </c>
@@ -1115,37 +1169,43 @@
       <c r="C18" t="s">
         <v>112</v>
       </c>
-      <c r="D18">
+      <c r="D18" t="s">
+        <v>112</v>
+      </c>
+      <c r="E18">
         <v>22838.799999999999</v>
       </c>
-      <c r="E18">
+      <c r="F18">
         <v>17554.849999999999</v>
       </c>
-      <c r="F18">
+      <c r="G18">
         <v>15051.54</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>20</v>
       </c>
       <c r="B19">
+        <v>76395.69</v>
+      </c>
+      <c r="C19">
         <v>41335.78</v>
       </c>
-      <c r="C19">
+      <c r="D19">
         <v>29754.07</v>
       </c>
-      <c r="D19">
+      <c r="E19">
         <v>24040.84</v>
       </c>
-      <c r="E19">
+      <c r="F19">
         <v>18478.79</v>
       </c>
-      <c r="F19">
+      <c r="G19">
         <v>15842.05</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>21</v>
       </c>
@@ -1155,17 +1215,20 @@
       <c r="C20" t="s">
         <v>112</v>
       </c>
-      <c r="D20">
+      <c r="D20" t="s">
+        <v>112</v>
+      </c>
+      <c r="E20">
         <v>25242.89</v>
       </c>
-      <c r="E20">
+      <c r="F20">
         <v>19402.73</v>
       </c>
-      <c r="F20">
+      <c r="G20">
         <v>16635.91</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>22</v>
       </c>
@@ -1175,17 +1238,20 @@
       <c r="C21" t="s">
         <v>112</v>
       </c>
-      <c r="D21">
+      <c r="D21" t="s">
+        <v>112</v>
+      </c>
+      <c r="E21">
         <v>26444.93</v>
       </c>
-      <c r="E21">
+      <c r="F21">
         <v>20326.669999999998</v>
       </c>
-      <c r="F21">
+      <c r="G21">
         <v>17428.099999999999</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>23</v>
       </c>
@@ -1195,17 +1261,20 @@
       <c r="C22" t="s">
         <v>112</v>
       </c>
-      <c r="D22">
+      <c r="D22" t="s">
+        <v>112</v>
+      </c>
+      <c r="E22">
         <v>27646.97</v>
       </c>
-      <c r="E22">
+      <c r="F22">
         <v>21250.6</v>
       </c>
-      <c r="F22">
+      <c r="G22">
         <v>18220.29</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>24</v>
       </c>
@@ -1215,37 +1284,43 @@
       <c r="C23" t="s">
         <v>112</v>
       </c>
-      <c r="D23">
+      <c r="D23" t="s">
+        <v>112</v>
+      </c>
+      <c r="E23">
         <v>28848.01</v>
       </c>
-      <c r="E23">
+      <c r="F23">
         <v>22174.54</v>
       </c>
-      <c r="F23">
+      <c r="G23">
         <v>19021.47</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>25</v>
       </c>
       <c r="B24">
+        <v>95494.61</v>
+      </c>
+      <c r="C24">
         <v>51669.73</v>
       </c>
-      <c r="C24">
+      <c r="D24">
         <v>37192.58</v>
       </c>
-      <c r="D24">
+      <c r="E24">
         <v>30051.06</v>
       </c>
-      <c r="E24">
+      <c r="F24">
         <v>23098.48</v>
       </c>
-      <c r="F24">
+      <c r="G24">
         <v>19802.560000000001</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>26</v>
       </c>
@@ -1255,17 +1330,20 @@
       <c r="C25" t="s">
         <v>112</v>
       </c>
-      <c r="D25">
+      <c r="D25" t="s">
+        <v>112</v>
+      </c>
+      <c r="E25">
         <v>31253.1</v>
       </c>
-      <c r="E25">
+      <c r="F25">
         <v>24022.42</v>
       </c>
-      <c r="F25">
+      <c r="G25">
         <v>20596.849999999999</v>
       </c>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>27</v>
       </c>
@@ -1275,17 +1353,20 @@
       <c r="C26" t="s">
         <v>112</v>
       </c>
-      <c r="D26">
+      <c r="D26" t="s">
+        <v>112</v>
+      </c>
+      <c r="E26">
         <v>32455.14</v>
       </c>
-      <c r="E26">
+      <c r="F26">
         <v>24946.36</v>
       </c>
-      <c r="F26">
+      <c r="G26">
         <v>31389.040000000001</v>
       </c>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>28</v>
       </c>
@@ -1295,17 +1376,20 @@
       <c r="C27" t="s">
         <v>112</v>
       </c>
-      <c r="D27">
+      <c r="D27" t="s">
+        <v>112</v>
+      </c>
+      <c r="E27">
         <v>33657.18</v>
       </c>
-      <c r="E27">
+      <c r="F27">
         <v>25870.3</v>
       </c>
-      <c r="F27">
+      <c r="G27">
         <v>22181.22</v>
       </c>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>29</v>
       </c>
@@ -1315,37 +1399,43 @@
       <c r="C28" t="s">
         <v>112</v>
       </c>
-      <c r="D28">
+      <c r="D28" t="s">
+        <v>112</v>
+      </c>
+      <c r="E28">
         <v>34859.22</v>
       </c>
-      <c r="E28">
+      <c r="F28">
         <v>26794.240000000002</v>
       </c>
-      <c r="F28">
+      <c r="G28">
         <v>22973.41</v>
       </c>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>30</v>
       </c>
       <c r="B29">
+        <v>114593.53</v>
+      </c>
+      <c r="C29">
         <v>62003.67</v>
       </c>
-      <c r="C29">
+      <c r="D29">
         <v>44631.1</v>
       </c>
-      <c r="D29">
+      <c r="E29">
         <v>36061.269999999997</v>
       </c>
-      <c r="E29">
+      <c r="F29">
         <v>27718.18</v>
       </c>
-      <c r="F29">
+      <c r="G29">
         <v>23763.08</v>
       </c>
     </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>31</v>
       </c>
@@ -1355,17 +1445,20 @@
       <c r="C30" t="s">
         <v>112</v>
       </c>
-      <c r="D30">
+      <c r="D30" t="s">
+        <v>112</v>
+      </c>
+      <c r="E30">
         <v>37263.31</v>
       </c>
-      <c r="E30">
+      <c r="F30">
         <v>28642.12</v>
       </c>
-      <c r="F30">
+      <c r="G30">
         <v>24557.78</v>
       </c>
     </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>32</v>
       </c>
@@ -1375,17 +1468,20 @@
       <c r="C31" t="s">
         <v>112</v>
       </c>
-      <c r="D31">
+      <c r="D31" t="s">
+        <v>112</v>
+      </c>
+      <c r="E31">
         <v>38465.35</v>
       </c>
-      <c r="E31">
+      <c r="F31">
         <v>29566.06</v>
       </c>
-      <c r="F31">
+      <c r="G31">
         <v>25349.96</v>
       </c>
     </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>33</v>
       </c>
@@ -1395,17 +1491,20 @@
       <c r="C32" t="s">
         <v>112</v>
       </c>
-      <c r="D32">
+      <c r="D32" t="s">
+        <v>112</v>
+      </c>
+      <c r="E32">
         <v>39667.39</v>
       </c>
-      <c r="E32">
+      <c r="F32">
         <v>30490</v>
       </c>
-      <c r="F32">
+      <c r="G32">
         <v>26142.15</v>
       </c>
     </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>34</v>
       </c>
@@ -1415,37 +1514,43 @@
       <c r="C33" t="s">
         <v>112</v>
       </c>
-      <c r="D33">
+      <c r="D33" t="s">
+        <v>112</v>
+      </c>
+      <c r="E33">
         <v>40869.440000000002</v>
       </c>
-      <c r="E33">
+      <c r="F33">
         <v>31413.94</v>
       </c>
-      <c r="F33">
+      <c r="G33">
         <v>26934.34</v>
       </c>
     </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>35</v>
       </c>
       <c r="B34">
+        <v>133692.45000000001</v>
+      </c>
+      <c r="C34">
         <v>72337.62</v>
       </c>
-      <c r="C34">
+      <c r="D34">
         <v>52069.61</v>
       </c>
-      <c r="D34">
+      <c r="E34">
         <v>42071.48</v>
       </c>
-      <c r="E34">
+      <c r="F34">
         <v>32337.88</v>
       </c>
-      <c r="F34">
+      <c r="G34">
         <v>27723.59</v>
       </c>
     </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>36</v>
       </c>
@@ -1455,17 +1560,20 @@
       <c r="C35" t="s">
         <v>112</v>
       </c>
-      <c r="D35">
+      <c r="D35" t="s">
+        <v>112</v>
+      </c>
+      <c r="E35">
         <v>43273.52</v>
       </c>
-      <c r="E35">
+      <c r="F35">
         <v>33261.82</v>
       </c>
-      <c r="F35">
+      <c r="G35">
         <v>28518.71</v>
       </c>
     </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>37</v>
       </c>
@@ -1475,17 +1583,20 @@
       <c r="C36" t="s">
         <v>112</v>
       </c>
-      <c r="D36">
+      <c r="D36" t="s">
+        <v>112</v>
+      </c>
+      <c r="E36">
         <v>44475.56</v>
       </c>
-      <c r="E36">
+      <c r="F36">
         <v>34185.760000000002</v>
       </c>
-      <c r="F36">
+      <c r="G36">
         <v>29310.9</v>
       </c>
     </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>38</v>
       </c>
@@ -1495,17 +1606,20 @@
       <c r="C37" t="s">
         <v>112</v>
       </c>
-      <c r="D37">
+      <c r="D37" t="s">
+        <v>112</v>
+      </c>
+      <c r="E37">
         <v>45667.6</v>
       </c>
-      <c r="E37">
+      <c r="F37">
         <v>35109.69</v>
       </c>
-      <c r="F37">
+      <c r="G37">
         <v>30103.09</v>
       </c>
     </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>39</v>
       </c>
@@ -1515,37 +1629,43 @@
       <c r="C38" t="s">
         <v>112</v>
       </c>
-      <c r="D38">
+      <c r="D38" t="s">
+        <v>112</v>
+      </c>
+      <c r="E38">
         <v>46879.65</v>
       </c>
-      <c r="E38">
+      <c r="F38">
         <v>36033.629999999997</v>
       </c>
-      <c r="F38">
+      <c r="G38">
         <v>30895.27</v>
       </c>
     </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>40</v>
       </c>
       <c r="B39">
+        <v>152791.37</v>
+      </c>
+      <c r="C39">
         <v>82671.56</v>
       </c>
-      <c r="C39">
+      <c r="D39">
         <v>59508.13</v>
       </c>
-      <c r="D39">
+      <c r="E39">
         <v>48081.69</v>
       </c>
-      <c r="E39">
+      <c r="F39">
         <v>36957.57</v>
       </c>
-      <c r="F39">
+      <c r="G39">
         <v>31684.1</v>
       </c>
     </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>41</v>
       </c>
@@ -1555,17 +1675,20 @@
       <c r="C40" t="s">
         <v>112</v>
       </c>
-      <c r="D40">
+      <c r="D40" t="s">
+        <v>112</v>
+      </c>
+      <c r="E40">
         <v>49283.73</v>
       </c>
-      <c r="E40">
+      <c r="F40">
         <v>37881.51</v>
       </c>
-      <c r="F40">
+      <c r="G40">
         <v>32479.65</v>
       </c>
     </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>42</v>
       </c>
@@ -1575,17 +1698,20 @@
       <c r="C41" t="s">
         <v>112</v>
       </c>
-      <c r="D41">
+      <c r="D41" t="s">
+        <v>112</v>
+      </c>
+      <c r="E41">
         <v>50485.77</v>
       </c>
-      <c r="E41">
+      <c r="F41">
         <v>38805.449999999997</v>
       </c>
-      <c r="F41">
+      <c r="G41">
         <v>33271.83</v>
       </c>
     </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>43</v>
       </c>
@@ -1595,17 +1721,20 @@
       <c r="C42" t="s">
         <v>112</v>
       </c>
-      <c r="D42">
+      <c r="D42" t="s">
+        <v>112</v>
+      </c>
+      <c r="E42">
         <v>51687.82</v>
       </c>
-      <c r="E42">
+      <c r="F42">
         <v>39729.39</v>
       </c>
-      <c r="F42">
+      <c r="G42">
         <v>34064.019999999997</v>
       </c>
     </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>44</v>
       </c>
@@ -1615,37 +1744,43 @@
       <c r="C43" t="s">
         <v>112</v>
       </c>
-      <c r="D43">
+      <c r="D43" t="s">
+        <v>112</v>
+      </c>
+      <c r="E43">
         <v>52889.86</v>
       </c>
-      <c r="E43">
+      <c r="F43">
         <v>40653.33</v>
       </c>
-      <c r="F43">
+      <c r="G43">
         <v>34856.199999999997</v>
       </c>
     </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>45</v>
       </c>
       <c r="B44">
+        <v>171890.29</v>
+      </c>
+      <c r="C44">
         <v>93005.51</v>
       </c>
-      <c r="C44">
+      <c r="D44">
         <v>66946.649999999994</v>
       </c>
-      <c r="D44">
+      <c r="E44">
         <v>54091.9</v>
       </c>
-      <c r="E44">
+      <c r="F44">
         <v>41557.269999999997</v>
       </c>
-      <c r="F44">
+      <c r="G44">
         <v>35644.620000000003</v>
       </c>
     </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>46</v>
       </c>
@@ -1655,17 +1790,20 @@
       <c r="C45" t="s">
         <v>112</v>
       </c>
-      <c r="D45">
+      <c r="D45" t="s">
+        <v>112</v>
+      </c>
+      <c r="E45">
         <v>55293.94</v>
       </c>
-      <c r="E45">
+      <c r="F45">
         <v>42501.21</v>
       </c>
-      <c r="F45">
+      <c r="G45">
         <v>36440.57</v>
       </c>
     </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>47</v>
       </c>
@@ -1675,17 +1813,20 @@
       <c r="C46" t="s">
         <v>112</v>
       </c>
-      <c r="D46">
+      <c r="D46" t="s">
+        <v>112</v>
+      </c>
+      <c r="E46">
         <v>56495.98</v>
       </c>
-      <c r="E46">
+      <c r="F46">
         <v>43425.15</v>
       </c>
-      <c r="F46">
+      <c r="G46">
         <v>37232.76</v>
       </c>
     </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>48</v>
       </c>
@@ -1695,17 +1836,20 @@
       <c r="C47" t="s">
         <v>112</v>
       </c>
-      <c r="D47">
+      <c r="D47" t="s">
+        <v>112</v>
+      </c>
+      <c r="E47">
         <v>57698.03</v>
       </c>
-      <c r="E47">
+      <c r="F47">
         <v>44349.09</v>
       </c>
-      <c r="F47">
+      <c r="G47">
         <v>38024.949999999997</v>
       </c>
     </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>49</v>
       </c>
@@ -1715,37 +1859,43 @@
       <c r="C48" t="s">
         <v>112</v>
       </c>
-      <c r="D48">
+      <c r="D48" t="s">
+        <v>112</v>
+      </c>
+      <c r="E48">
         <v>59800.07</v>
       </c>
-      <c r="E48">
+      <c r="F48">
         <v>45273.03</v>
       </c>
-      <c r="F48">
+      <c r="G48">
         <v>38817.14</v>
       </c>
     </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>50</v>
       </c>
       <c r="B49">
+        <v>190989.22</v>
+      </c>
+      <c r="C49">
         <v>103339.45</v>
       </c>
-      <c r="C49">
+      <c r="D49">
         <v>74385.16</v>
       </c>
-      <c r="D49">
+      <c r="E49">
         <v>60102.11</v>
       </c>
-      <c r="E49">
+      <c r="F49">
         <v>46196.97</v>
       </c>
-      <c r="F49">
+      <c r="G49">
         <v>39605.129999999997</v>
       </c>
     </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>51</v>
       </c>
@@ -1755,17 +1905,20 @@
       <c r="C50" t="s">
         <v>112</v>
       </c>
-      <c r="D50">
+      <c r="D50" t="s">
+        <v>112</v>
+      </c>
+      <c r="E50">
         <v>61304.15</v>
       </c>
-      <c r="E50">
+      <c r="F50">
         <v>47120.91</v>
       </c>
-      <c r="F50">
+      <c r="G50">
         <v>40401.51</v>
       </c>
     </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>52</v>
       </c>
@@ -1775,17 +1928,20 @@
       <c r="C51" t="s">
         <v>112</v>
       </c>
-      <c r="D51">
+      <c r="D51" t="s">
+        <v>112</v>
+      </c>
+      <c r="E51">
         <v>62506.2</v>
       </c>
-      <c r="E51">
+      <c r="F51">
         <v>48044.85</v>
       </c>
-      <c r="F51">
+      <c r="G51">
         <v>41193.699999999997</v>
       </c>
     </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>53</v>
       </c>
@@ -1795,17 +1951,20 @@
       <c r="C52" t="s">
         <v>112</v>
       </c>
-      <c r="D52">
+      <c r="D52" t="s">
+        <v>112</v>
+      </c>
+      <c r="E52">
         <v>63708.24</v>
       </c>
-      <c r="E52">
+      <c r="F52">
         <v>48968.78</v>
       </c>
-      <c r="F52">
+      <c r="G52">
         <v>41985.88</v>
       </c>
     </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>54</v>
       </c>
@@ -1815,37 +1974,43 @@
       <c r="C53" t="s">
         <v>112</v>
       </c>
-      <c r="D53">
+      <c r="D53" t="s">
+        <v>112</v>
+      </c>
+      <c r="E53">
         <v>64910.28</v>
       </c>
-      <c r="E53">
+      <c r="F53">
         <v>49892.72</v>
       </c>
-      <c r="F53">
+      <c r="G53">
         <v>42778.07</v>
       </c>
     </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>55</v>
       </c>
       <c r="B54">
+        <v>210088.14</v>
+      </c>
+      <c r="C54">
         <v>113673.4</v>
       </c>
-      <c r="C54">
+      <c r="D54">
         <v>81823.679999999993</v>
       </c>
-      <c r="D54">
+      <c r="E54">
         <v>66112.320000000007</v>
       </c>
-      <c r="E54">
+      <c r="F54">
         <v>50816.66</v>
       </c>
-      <c r="F54">
+      <c r="G54">
         <v>43565.64</v>
       </c>
     </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>56</v>
       </c>
@@ -1855,17 +2020,20 @@
       <c r="C55" t="s">
         <v>112</v>
       </c>
-      <c r="D55">
+      <c r="D55" t="s">
+        <v>112</v>
+      </c>
+      <c r="E55">
         <v>67314.36</v>
       </c>
-      <c r="E55">
+      <c r="F55">
         <v>51740.6</v>
       </c>
-      <c r="F55">
+      <c r="G55">
         <v>44362.45</v>
       </c>
     </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>57</v>
       </c>
@@ -1875,17 +2043,20 @@
       <c r="C56" t="s">
         <v>112</v>
       </c>
-      <c r="D56">
+      <c r="D56" t="s">
+        <v>112</v>
+      </c>
+      <c r="E56">
         <v>68516.41</v>
       </c>
-      <c r="E56">
+      <c r="F56">
         <v>52664.54</v>
       </c>
-      <c r="F56">
+      <c r="G56">
         <v>45154.62</v>
       </c>
     </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>58</v>
       </c>
@@ -1895,17 +2066,20 @@
       <c r="C57" t="s">
         <v>112</v>
       </c>
-      <c r="D57">
+      <c r="D57" t="s">
+        <v>112</v>
+      </c>
+      <c r="E57">
         <v>69718.45</v>
       </c>
-      <c r="E57">
+      <c r="F57">
         <v>53588.480000000003</v>
       </c>
-      <c r="F57">
+      <c r="G57">
         <v>45946.81</v>
       </c>
     </row>
-    <row r="58" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>59</v>
       </c>
@@ -1915,37 +2089,43 @@
       <c r="C58" t="s">
         <v>112</v>
       </c>
-      <c r="D58">
+      <c r="D58" t="s">
+        <v>112</v>
+      </c>
+      <c r="E58">
         <v>70920.490000000005</v>
       </c>
-      <c r="E58">
+      <c r="F58">
         <v>54512.42</v>
       </c>
-      <c r="F58">
+      <c r="G58">
         <v>46739</v>
       </c>
     </row>
-    <row r="59" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>60</v>
       </c>
       <c r="B59">
+        <v>229187.06</v>
+      </c>
+      <c r="C59">
         <v>124007.34</v>
       </c>
-      <c r="C59">
+      <c r="D59">
         <v>89262.2</v>
       </c>
-      <c r="D59">
+      <c r="E59">
         <v>72112.53</v>
       </c>
-      <c r="E59">
+      <c r="F59">
         <v>55436.36</v>
       </c>
-      <c r="F59">
+      <c r="G59">
         <v>47526.16</v>
       </c>
     </row>
-    <row r="60" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>61</v>
       </c>
@@ -1955,17 +2135,20 @@
       <c r="C60" t="s">
         <v>112</v>
       </c>
-      <c r="D60">
+      <c r="D60" t="s">
+        <v>112</v>
+      </c>
+      <c r="E60">
         <v>73324.58</v>
       </c>
-      <c r="E60">
+      <c r="F60">
         <v>56360.3</v>
       </c>
-      <c r="F60">
+      <c r="G60">
         <v>48323.37</v>
       </c>
     </row>
-    <row r="61" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>62</v>
       </c>
@@ -1975,17 +2158,20 @@
       <c r="C61" t="s">
         <v>112</v>
       </c>
-      <c r="D61">
+      <c r="D61" t="s">
+        <v>112</v>
+      </c>
+      <c r="E61">
         <v>74526.62</v>
       </c>
-      <c r="E61">
+      <c r="F61">
         <v>57284.24</v>
       </c>
-      <c r="F61">
+      <c r="G61">
         <v>49115.56</v>
       </c>
     </row>
-    <row r="62" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>63</v>
       </c>
@@ -1995,17 +2181,20 @@
       <c r="C62" t="s">
         <v>112</v>
       </c>
-      <c r="D62">
+      <c r="D62" t="s">
+        <v>112</v>
+      </c>
+      <c r="E62">
         <v>75728.66</v>
       </c>
-      <c r="E62">
+      <c r="F62">
         <v>58208.18</v>
       </c>
-      <c r="F62">
+      <c r="G62">
         <v>49907.75</v>
       </c>
     </row>
-    <row r="63" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>64</v>
       </c>
@@ -2015,17 +2204,20 @@
       <c r="C63" t="s">
         <v>112</v>
       </c>
-      <c r="D63">
+      <c r="D63" t="s">
+        <v>112</v>
+      </c>
+      <c r="E63">
         <v>76930.7</v>
       </c>
-      <c r="E63">
+      <c r="F63">
         <v>59132.12</v>
       </c>
-      <c r="F63">
+      <c r="G63">
         <v>50699.93</v>
       </c>
     </row>
-    <row r="64" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>65</v>
       </c>
@@ -2035,17 +2227,20 @@
       <c r="C64" t="s">
         <v>112</v>
       </c>
-      <c r="D64">
+      <c r="D64" t="s">
+        <v>112</v>
+      </c>
+      <c r="E64">
         <v>78132.740000000005</v>
       </c>
-      <c r="E64">
+      <c r="F64">
         <v>60056.06</v>
       </c>
-      <c r="F64">
+      <c r="G64">
         <v>51492.12</v>
       </c>
     </row>
-    <row r="65" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>66</v>
       </c>
@@ -2055,17 +2250,20 @@
       <c r="C65" t="s">
         <v>112</v>
       </c>
-      <c r="D65">
+      <c r="D65" t="s">
+        <v>112</v>
+      </c>
+      <c r="E65">
         <v>79334.789999999994</v>
       </c>
-      <c r="E65">
+      <c r="F65">
         <v>60980</v>
       </c>
-      <c r="F65">
+      <c r="G65">
         <v>52284.31</v>
       </c>
     </row>
-    <row r="66" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>67</v>
       </c>
@@ -2075,17 +2273,20 @@
       <c r="C66" t="s">
         <v>112</v>
       </c>
-      <c r="D66">
+      <c r="D66" t="s">
+        <v>112</v>
+      </c>
+      <c r="E66">
         <v>80536.83</v>
       </c>
-      <c r="E66">
+      <c r="F66">
         <v>61903.94</v>
       </c>
-      <c r="F66">
+      <c r="G66">
         <v>53076.5</v>
       </c>
     </row>
-    <row r="67" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>68</v>
       </c>
@@ -2095,17 +2296,20 @@
       <c r="C67" t="s">
         <v>112</v>
       </c>
-      <c r="D67">
+      <c r="D67" t="s">
+        <v>112</v>
+      </c>
+      <c r="E67">
         <v>81738.87</v>
       </c>
-      <c r="E67">
+      <c r="F67">
         <v>62827.87</v>
       </c>
-      <c r="F67">
+      <c r="G67">
         <v>53868.68</v>
       </c>
     </row>
-    <row r="68" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
         <v>69</v>
       </c>
@@ -2115,17 +2319,20 @@
       <c r="C68" t="s">
         <v>112</v>
       </c>
-      <c r="D68">
+      <c r="D68" t="s">
+        <v>112</v>
+      </c>
+      <c r="E68">
         <v>82940.91</v>
       </c>
-      <c r="E68">
+      <c r="F68">
         <v>63751.81</v>
       </c>
-      <c r="F68">
+      <c r="G68">
         <v>54660.86</v>
       </c>
     </row>
-    <row r="69" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
         <v>70</v>
       </c>
@@ -2135,17 +2342,20 @@
       <c r="C69" t="s">
         <v>112</v>
       </c>
-      <c r="D69">
+      <c r="D69" t="s">
+        <v>112</v>
+      </c>
+      <c r="E69">
         <v>84142.96</v>
       </c>
-      <c r="E69">
+      <c r="F69">
         <v>64675.75</v>
       </c>
-      <c r="F69">
+      <c r="G69">
         <v>55453.05</v>
       </c>
     </row>
-    <row r="70" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
         <v>71</v>
       </c>
@@ -2155,17 +2365,20 @@
       <c r="C70" t="s">
         <v>112</v>
       </c>
-      <c r="D70">
+      <c r="D70" t="s">
+        <v>112</v>
+      </c>
+      <c r="E70">
         <v>85345</v>
       </c>
-      <c r="E70">
+      <c r="F70">
         <v>65599.69</v>
       </c>
-      <c r="F70">
+      <c r="G70">
         <v>56245.23</v>
       </c>
     </row>
-    <row r="71" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
         <v>72</v>
       </c>
@@ -2175,17 +2388,20 @@
       <c r="C71" t="s">
         <v>112</v>
       </c>
-      <c r="D71">
+      <c r="D71" t="s">
+        <v>112</v>
+      </c>
+      <c r="E71">
         <v>86547.04</v>
       </c>
-      <c r="E71">
+      <c r="F71">
         <v>66523.63</v>
       </c>
-      <c r="F71">
+      <c r="G71">
         <v>57037.42</v>
       </c>
     </row>
-    <row r="72" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
         <v>73</v>
       </c>
@@ -2195,17 +2411,20 @@
       <c r="C72" t="s">
         <v>112</v>
       </c>
-      <c r="D72">
+      <c r="D72" t="s">
+        <v>112</v>
+      </c>
+      <c r="E72">
         <v>87749.08</v>
       </c>
-      <c r="E72">
+      <c r="F72">
         <v>67447.570000000007</v>
       </c>
-      <c r="F72">
+      <c r="G72">
         <v>57829.61</v>
       </c>
     </row>
-    <row r="73" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
         <v>74</v>
       </c>
@@ -2215,17 +2434,20 @@
       <c r="C73" t="s">
         <v>112</v>
       </c>
-      <c r="D73">
+      <c r="D73" t="s">
+        <v>112</v>
+      </c>
+      <c r="E73">
         <v>88951.12</v>
       </c>
-      <c r="E73">
+      <c r="F73">
         <v>68371.509999999995</v>
       </c>
-      <c r="F73">
+      <c r="G73">
         <v>58621.8</v>
       </c>
     </row>
-    <row r="74" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
         <v>75</v>
       </c>
@@ -2235,17 +2457,20 @@
       <c r="C74" t="s">
         <v>112</v>
       </c>
-      <c r="D74">
+      <c r="D74" t="s">
+        <v>112</v>
+      </c>
+      <c r="E74">
         <v>90153.17</v>
       </c>
-      <c r="E74">
+      <c r="F74">
         <v>69295.45</v>
       </c>
-      <c r="F74">
+      <c r="G74">
         <v>59413.98</v>
       </c>
     </row>
-    <row r="75" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
         <v>76</v>
       </c>
@@ -2255,17 +2480,20 @@
       <c r="C75" t="s">
         <v>112</v>
       </c>
-      <c r="D75">
+      <c r="D75" t="s">
+        <v>112</v>
+      </c>
+      <c r="E75">
         <v>91355.21</v>
       </c>
-      <c r="E75">
+      <c r="F75">
         <v>70219.39</v>
       </c>
-      <c r="F75">
+      <c r="G75">
         <v>60206.17</v>
       </c>
     </row>
-    <row r="76" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
         <v>77</v>
       </c>
@@ -2275,17 +2503,20 @@
       <c r="C76" t="s">
         <v>112</v>
       </c>
-      <c r="D76">
+      <c r="D76" t="s">
+        <v>112</v>
+      </c>
+      <c r="E76">
         <v>92557.25</v>
       </c>
-      <c r="E76">
+      <c r="F76">
         <v>71143.33</v>
       </c>
-      <c r="F76">
+      <c r="G76">
         <v>60998.36</v>
       </c>
     </row>
-    <row r="77" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
         <v>78</v>
       </c>
@@ -2295,17 +2526,20 @@
       <c r="C77" t="s">
         <v>112</v>
       </c>
-      <c r="D77">
+      <c r="D77" t="s">
+        <v>112</v>
+      </c>
+      <c r="E77">
         <v>93759.29</v>
       </c>
-      <c r="E77">
+      <c r="F77">
         <v>72067.27</v>
       </c>
-      <c r="F77">
+      <c r="G77">
         <v>61790.55</v>
       </c>
     </row>
-    <row r="78" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
         <v>79</v>
       </c>
@@ -2315,17 +2549,20 @@
       <c r="C78" t="s">
         <v>112</v>
       </c>
-      <c r="D78">
+      <c r="D78" t="s">
+        <v>112</v>
+      </c>
+      <c r="E78">
         <v>94961.34</v>
       </c>
-      <c r="E78">
+      <c r="F78">
         <v>72991.210000000006</v>
       </c>
-      <c r="F78">
+      <c r="G78">
         <v>62582.73</v>
       </c>
     </row>
-    <row r="79" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
         <v>80</v>
       </c>
@@ -2335,17 +2572,20 @@
       <c r="C79" t="s">
         <v>112</v>
       </c>
-      <c r="D79">
+      <c r="D79" t="s">
+        <v>112</v>
+      </c>
+      <c r="E79">
         <v>96163.38</v>
       </c>
-      <c r="E79">
+      <c r="F79">
         <v>73915.149999999994</v>
       </c>
-      <c r="F79">
+      <c r="G79">
         <v>63374.92</v>
       </c>
     </row>
-    <row r="80" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
         <v>81</v>
       </c>
@@ -2355,17 +2595,20 @@
       <c r="C80" t="s">
         <v>112</v>
       </c>
-      <c r="D80">
+      <c r="D80" t="s">
+        <v>112</v>
+      </c>
+      <c r="E80">
         <v>97365.42</v>
       </c>
-      <c r="E80">
+      <c r="F80">
         <v>74839.09</v>
       </c>
-      <c r="F80">
+      <c r="G80">
         <v>64167.11</v>
       </c>
     </row>
-    <row r="81" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
         <v>82</v>
       </c>
@@ -2375,17 +2618,20 @@
       <c r="C81" t="s">
         <v>112</v>
       </c>
-      <c r="D81">
+      <c r="D81" t="s">
+        <v>112</v>
+      </c>
+      <c r="E81">
         <v>98567.46</v>
       </c>
-      <c r="E81">
+      <c r="F81">
         <v>75763.03</v>
       </c>
-      <c r="F81">
+      <c r="G81">
         <v>64959.28</v>
       </c>
     </row>
-    <row r="82" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
         <v>83</v>
       </c>
@@ -2395,17 +2641,20 @@
       <c r="C82" t="s">
         <v>112</v>
       </c>
-      <c r="D82">
+      <c r="D82" t="s">
+        <v>112</v>
+      </c>
+      <c r="E82">
         <v>99769.5</v>
       </c>
-      <c r="E82">
+      <c r="F82">
         <v>76686.960000000006</v>
       </c>
-      <c r="F82">
+      <c r="G82">
         <v>65751.47</v>
       </c>
     </row>
-    <row r="83" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
         <v>84</v>
       </c>
@@ -2415,17 +2664,20 @@
       <c r="C83" t="s">
         <v>112</v>
       </c>
-      <c r="D83">
+      <c r="D83" t="s">
+        <v>112</v>
+      </c>
+      <c r="E83">
         <v>100971.55</v>
       </c>
-      <c r="E83">
+      <c r="F83">
         <v>77610.899999999994</v>
       </c>
-      <c r="F83">
+      <c r="G83">
         <v>66543.66</v>
       </c>
     </row>
-    <row r="84" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
         <v>85</v>
       </c>
@@ -2435,17 +2687,20 @@
       <c r="C84" t="s">
         <v>112</v>
       </c>
-      <c r="D84">
+      <c r="D84" t="s">
+        <v>112</v>
+      </c>
+      <c r="E84">
         <v>102173.59</v>
       </c>
-      <c r="E84">
+      <c r="F84">
         <v>78534.84</v>
       </c>
-      <c r="F84">
+      <c r="G84">
         <v>67335.850000000006</v>
       </c>
     </row>
-    <row r="85" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
         <v>86</v>
       </c>
@@ -2455,17 +2710,20 @@
       <c r="C85" t="s">
         <v>112</v>
       </c>
-      <c r="D85">
+      <c r="D85" t="s">
+        <v>112</v>
+      </c>
+      <c r="E85">
         <v>103375.63</v>
       </c>
-      <c r="E85">
+      <c r="F85">
         <v>79458.78</v>
       </c>
-      <c r="F85">
+      <c r="G85">
         <v>68128.03</v>
       </c>
     </row>
-    <row r="86" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
         <v>87</v>
       </c>
@@ -2475,17 +2733,20 @@
       <c r="C86" t="s">
         <v>112</v>
       </c>
-      <c r="D86">
+      <c r="D86" t="s">
+        <v>112</v>
+      </c>
+      <c r="E86">
         <v>104577.67</v>
       </c>
-      <c r="E86">
+      <c r="F86">
         <v>80382.720000000001</v>
       </c>
-      <c r="F86">
+      <c r="G86">
         <v>68920.22</v>
       </c>
     </row>
-    <row r="87" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
         <v>88</v>
       </c>
@@ -2495,17 +2756,20 @@
       <c r="C87" t="s">
         <v>112</v>
       </c>
-      <c r="D87">
+      <c r="D87" t="s">
+        <v>112</v>
+      </c>
+      <c r="E87">
         <v>105779.72</v>
       </c>
-      <c r="E87">
+      <c r="F87">
         <v>81306.66</v>
       </c>
-      <c r="F87">
+      <c r="G87">
         <v>69712.41</v>
       </c>
     </row>
-    <row r="88" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
         <v>89</v>
       </c>
@@ -2515,17 +2779,20 @@
       <c r="C88" t="s">
         <v>112</v>
       </c>
-      <c r="D88">
+      <c r="D88" t="s">
+        <v>112</v>
+      </c>
+      <c r="E88">
         <v>106981.75999999999</v>
       </c>
-      <c r="E88">
+      <c r="F88">
         <v>82230.600000000006</v>
       </c>
-      <c r="F88">
+      <c r="G88">
         <v>70504.59</v>
       </c>
     </row>
-    <row r="89" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
         <v>90</v>
       </c>
@@ -2535,17 +2802,20 @@
       <c r="C89" t="s">
         <v>112</v>
       </c>
-      <c r="D89">
+      <c r="D89" t="s">
+        <v>112</v>
+      </c>
+      <c r="E89">
         <v>108183.8</v>
       </c>
-      <c r="E89">
+      <c r="F89">
         <v>83154.539999999994</v>
       </c>
-      <c r="F89">
+      <c r="G89">
         <v>71296.78</v>
       </c>
     </row>
-    <row r="90" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
         <v>91</v>
       </c>
@@ -2555,17 +2825,20 @@
       <c r="C90" t="s">
         <v>112</v>
       </c>
-      <c r="D90">
+      <c r="D90" t="s">
+        <v>112</v>
+      </c>
+      <c r="E90">
         <v>109385.84</v>
       </c>
-      <c r="E90">
+      <c r="F90">
         <v>84078.48</v>
       </c>
-      <c r="F90">
+      <c r="G90">
         <v>72088.97</v>
       </c>
     </row>
-    <row r="91" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
         <v>92</v>
       </c>
@@ -2575,17 +2848,20 @@
       <c r="C91" t="s">
         <v>112</v>
       </c>
-      <c r="D91">
+      <c r="D91" t="s">
+        <v>112</v>
+      </c>
+      <c r="E91">
         <v>110587.88</v>
       </c>
-      <c r="E91">
+      <c r="F91">
         <v>85002.42</v>
       </c>
-      <c r="F91">
+      <c r="G91">
         <v>72881.16</v>
       </c>
     </row>
-    <row r="92" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
         <v>93</v>
       </c>
@@ -2595,17 +2871,20 @@
       <c r="C92" t="s">
         <v>112</v>
       </c>
-      <c r="D92">
+      <c r="D92" t="s">
+        <v>112</v>
+      </c>
+      <c r="E92">
         <v>111789.93</v>
       </c>
-      <c r="E92">
+      <c r="F92">
         <v>85926.36</v>
       </c>
-      <c r="F92">
+      <c r="G92">
         <v>73673.34</v>
       </c>
     </row>
-    <row r="93" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
         <v>94</v>
       </c>
@@ -2615,17 +2894,20 @@
       <c r="C93" t="s">
         <v>112</v>
       </c>
-      <c r="D93">
+      <c r="D93" t="s">
+        <v>112</v>
+      </c>
+      <c r="E93">
         <v>112991.97</v>
       </c>
-      <c r="E93">
+      <c r="F93">
         <v>86850.3</v>
       </c>
-      <c r="F93">
+      <c r="G93">
         <v>74465.52</v>
       </c>
     </row>
-    <row r="94" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
         <v>95</v>
       </c>
@@ -2635,17 +2917,20 @@
       <c r="C94" t="s">
         <v>112</v>
       </c>
-      <c r="D94">
+      <c r="D94" t="s">
+        <v>112</v>
+      </c>
+      <c r="E94">
         <v>114194.01</v>
       </c>
-      <c r="E94">
+      <c r="F94">
         <v>87774.24</v>
       </c>
-      <c r="F94">
+      <c r="G94">
         <v>75257.710000000006</v>
       </c>
     </row>
-    <row r="95" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
         <v>96</v>
       </c>
@@ -2655,17 +2940,20 @@
       <c r="C95" t="s">
         <v>112</v>
       </c>
-      <c r="D95">
+      <c r="D95" t="s">
+        <v>112</v>
+      </c>
+      <c r="E95">
         <v>115396.05</v>
       </c>
-      <c r="E95">
+      <c r="F95">
         <v>88698.18</v>
       </c>
-      <c r="F95">
+      <c r="G95">
         <v>76049.899999999994</v>
       </c>
     </row>
-    <row r="96" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
         <v>97</v>
       </c>
@@ -2675,17 +2963,20 @@
       <c r="C96" t="s">
         <v>112</v>
       </c>
-      <c r="D96">
+      <c r="D96" t="s">
+        <v>112</v>
+      </c>
+      <c r="E96">
         <v>116598.1</v>
       </c>
-      <c r="E96">
+      <c r="F96">
         <v>89622.12</v>
       </c>
-      <c r="F96">
+      <c r="G96">
         <v>76842.080000000002</v>
       </c>
     </row>
-    <row r="97" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
         <v>98</v>
       </c>
@@ -2695,17 +2986,20 @@
       <c r="C97" t="s">
         <v>112</v>
       </c>
-      <c r="D97">
+      <c r="D97" t="s">
+        <v>112</v>
+      </c>
+      <c r="E97">
         <v>117800.14</v>
       </c>
-      <c r="E97">
+      <c r="F97">
         <v>90546.05</v>
       </c>
-      <c r="F97">
+      <c r="G97">
         <v>77634.27</v>
       </c>
     </row>
-    <row r="98" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
         <v>99</v>
       </c>
@@ -2715,17 +3009,20 @@
       <c r="C98" t="s">
         <v>112</v>
       </c>
-      <c r="D98">
+      <c r="D98" t="s">
+        <v>112</v>
+      </c>
+      <c r="E98">
         <v>119002.18</v>
       </c>
-      <c r="E98">
+      <c r="F98">
         <v>91469.99</v>
       </c>
-      <c r="F98">
+      <c r="G98">
         <v>78426.460000000006</v>
       </c>
     </row>
-    <row r="99" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
         <v>100</v>
       </c>
@@ -2735,17 +3032,20 @@
       <c r="C99" t="s">
         <v>112</v>
       </c>
-      <c r="D99">
+      <c r="D99" t="s">
+        <v>112</v>
+      </c>
+      <c r="E99">
         <v>120204.22</v>
       </c>
-      <c r="E99">
+      <c r="F99">
         <v>92393.93</v>
       </c>
-      <c r="F99">
+      <c r="G99">
         <v>79218.64</v>
       </c>
     </row>
-    <row r="100" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
         <v>101</v>
       </c>
@@ -2755,17 +3055,20 @@
       <c r="C100" t="s">
         <v>112</v>
       </c>
-      <c r="D100">
+      <c r="D100" t="s">
+        <v>112</v>
+      </c>
+      <c r="E100">
         <v>126214.43</v>
       </c>
-      <c r="E100">
+      <c r="F100">
         <v>97013.63</v>
       </c>
-      <c r="F100">
+      <c r="G100">
         <v>83179.58</v>
       </c>
     </row>
-    <row r="101" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
         <v>102</v>
       </c>
@@ -2775,17 +3078,20 @@
       <c r="C101" t="s">
         <v>112</v>
       </c>
-      <c r="D101">
+      <c r="D101" t="s">
+        <v>112</v>
+      </c>
+      <c r="E101">
         <v>132224.64000000001</v>
       </c>
-      <c r="E101">
+      <c r="F101">
         <v>101633.33</v>
       </c>
-      <c r="F101">
+      <c r="G101">
         <v>87140.58</v>
       </c>
     </row>
-    <row r="102" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
         <v>103</v>
       </c>
@@ -2795,17 +3101,20 @@
       <c r="C102" t="s">
         <v>112</v>
       </c>
-      <c r="D102">
+      <c r="D102" t="s">
+        <v>112</v>
+      </c>
+      <c r="E102">
         <v>138234.85999999999</v>
       </c>
-      <c r="E102">
+      <c r="F102">
         <v>106253.02</v>
       </c>
-      <c r="F102">
+      <c r="G102">
         <v>91101.440000000002</v>
       </c>
     </row>
-    <row r="103" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
         <v>104</v>
       </c>
@@ -2815,17 +3124,20 @@
       <c r="C103" t="s">
         <v>112</v>
       </c>
-      <c r="D103">
+      <c r="D103" t="s">
+        <v>112</v>
+      </c>
+      <c r="E103">
         <v>144245.07</v>
       </c>
-      <c r="E103">
+      <c r="F103">
         <v>110872.72</v>
       </c>
-      <c r="F103">
+      <c r="G103">
         <v>95062.37</v>
       </c>
     </row>
-    <row r="104" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
         <v>105</v>
       </c>
@@ -2835,17 +3147,20 @@
       <c r="C104" t="s">
         <v>112</v>
       </c>
-      <c r="D104">
+      <c r="D104" t="s">
+        <v>112</v>
+      </c>
+      <c r="E104">
         <v>150255.28</v>
       </c>
-      <c r="E104">
+      <c r="F104">
         <v>115492.42</v>
       </c>
-      <c r="F104">
+      <c r="G104">
         <v>99023.31</v>
       </c>
     </row>
-    <row r="105" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
         <v>106</v>
       </c>
@@ -2855,17 +3170,20 @@
       <c r="C105" t="s">
         <v>112</v>
       </c>
-      <c r="D105">
+      <c r="D105" t="s">
+        <v>112</v>
+      </c>
+      <c r="E105">
         <v>156265.49</v>
       </c>
-      <c r="E105">
+      <c r="F105">
         <v>120112.11</v>
       </c>
-      <c r="F105">
+      <c r="G105">
         <v>102984.24</v>
       </c>
     </row>
-    <row r="106" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
         <v>107</v>
       </c>
@@ -2875,17 +3193,20 @@
       <c r="C106" t="s">
         <v>112</v>
       </c>
-      <c r="D106">
+      <c r="D106" t="s">
+        <v>112</v>
+      </c>
+      <c r="E106">
         <v>162275.70000000001</v>
       </c>
-      <c r="E106">
+      <c r="F106">
         <v>124731.81</v>
       </c>
-      <c r="F106">
+      <c r="G106">
         <v>106945.17</v>
       </c>
     </row>
-    <row r="107" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
         <v>108</v>
       </c>
@@ -2895,17 +3216,20 @@
       <c r="C107" t="s">
         <v>112</v>
       </c>
-      <c r="D107">
+      <c r="D107" t="s">
+        <v>112</v>
+      </c>
+      <c r="E107">
         <v>168285.91</v>
       </c>
-      <c r="E107">
+      <c r="F107">
         <v>129351.51</v>
       </c>
-      <c r="F107">
+      <c r="G107">
         <v>110906.1</v>
       </c>
     </row>
-    <row r="108" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
         <v>109</v>
       </c>
@@ -2915,17 +3239,20 @@
       <c r="C108" t="s">
         <v>112</v>
       </c>
-      <c r="D108">
+      <c r="D108" t="s">
+        <v>112</v>
+      </c>
+      <c r="E108">
         <v>174296.12</v>
       </c>
-      <c r="E108">
+      <c r="F108">
         <v>133971.20000000001</v>
       </c>
-      <c r="F108">
+      <c r="G108">
         <v>114867.03</v>
       </c>
     </row>
-    <row r="109" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
         <v>110</v>
       </c>
@@ -2935,13 +3262,16 @@
       <c r="C109" t="s">
         <v>112</v>
       </c>
-      <c r="D109">
+      <c r="D109" t="s">
+        <v>112</v>
+      </c>
+      <c r="E109">
         <v>180306.33</v>
       </c>
-      <c r="E109">
+      <c r="F109">
         <v>138590.9</v>
       </c>
-      <c r="F109">
+      <c r="G109">
         <v>118827.97</v>
       </c>
     </row>
@@ -2949,7 +3279,7 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
   <ignoredErrors>
-    <ignoredError sqref="A2:A109 D1 E1 F1" numberStoredAsText="1"/>
+    <ignoredError sqref="A2:A109 E1 F1 G1" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/grilla.xlsx
+++ b/grilla.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aetch\Desktop\proyecto_aamas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B68E9204-576A-413E-9AD8-17E4F64024A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{634FD11B-BFA0-4360-A893-AB0DD5BABBAE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3120" yWindow="3120" windowWidth="21600" windowHeight="11385" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Grilla" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="404" uniqueCount="116">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="401" uniqueCount="116">
   <si>
     <t>Cuotas12</t>
   </si>
@@ -2116,7 +2116,7 @@
         <v>89262.2</v>
       </c>
       <c r="E59">
-        <v>72112.53</v>
+        <v>72122.53</v>
       </c>
       <c r="F59">
         <v>55436.36</v>
@@ -2221,14 +2221,14 @@
       <c r="A64" t="s">
         <v>65</v>
       </c>
-      <c r="B64" t="s">
-        <v>112</v>
-      </c>
-      <c r="C64" t="s">
-        <v>112</v>
-      </c>
-      <c r="D64" t="s">
-        <v>112</v>
+      <c r="B64">
+        <v>248285.9</v>
+      </c>
+      <c r="C64">
+        <v>134341.29</v>
+      </c>
+      <c r="D64">
+        <v>96700.71</v>
       </c>
       <c r="E64">
         <v>78132.740000000005</v>
@@ -2237,7 +2237,7 @@
         <v>60056.06</v>
       </c>
       <c r="G64">
-        <v>51492.12</v>
+        <v>51486.67</v>
       </c>
     </row>
     <row r="65" spans="1:7" x14ac:dyDescent="0.25">

--- a/grilla.xlsx
+++ b/grilla.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aetch\Desktop\proyecto_aamas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{634FD11B-BFA0-4360-A893-AB0DD5BABBAE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8AA50334-2057-454D-B350-F6F49235F240}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -388,8 +388,16 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
       <sz val="12"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -417,10 +425,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1773,8 +1782,8 @@
       <c r="E44">
         <v>54091.9</v>
       </c>
-      <c r="F44">
-        <v>41557.269999999997</v>
+      <c r="F44" s="3">
+        <v>41577.269999999997</v>
       </c>
       <c r="G44">
         <v>35644.620000000003</v>

--- a/grilla.xlsx
+++ b/grilla.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aetch\Desktop\proyecto_aamas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8AA50334-2057-454D-B350-F6F49235F240}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{34180D95-C8A3-4354-809E-62C986C24B74}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1125" yWindow="1125" windowWidth="21600" windowHeight="11385" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Grilla" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="401" uniqueCount="116">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="115">
   <si>
     <t>Cuotas12</t>
   </si>
@@ -370,9 +370,6 @@
   </si>
   <si>
     <t>Monto</t>
-  </si>
-  <si>
-    <t>0.00</t>
   </si>
   <si>
     <t>Cuotas6</t>
@@ -388,16 +385,8 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
-      <sz val="12"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
       <sz val="12"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -425,11 +414,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -782,13 +770,13 @@
         <v>111</v>
       </c>
       <c r="B1" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C1" t="s">
+        <v>112</v>
+      </c>
+      <c r="D1" t="s">
         <v>113</v>
-      </c>
-      <c r="D1" t="s">
-        <v>114</v>
       </c>
       <c r="E1" t="s">
         <v>0</v>
@@ -804,14 +792,14 @@
       <c r="A2" t="s">
         <v>3</v>
       </c>
-      <c r="B2" t="s">
-        <v>112</v>
-      </c>
-      <c r="C2" t="s">
-        <v>112</v>
-      </c>
-      <c r="D2" t="s">
-        <v>112</v>
+      <c r="B2">
+        <v>11459.35</v>
+      </c>
+      <c r="C2">
+        <v>6200.37</v>
+      </c>
+      <c r="D2">
+        <v>4463.1099999999997</v>
       </c>
       <c r="E2">
         <v>3606.13</v>
@@ -827,14 +815,14 @@
       <c r="A3" t="s">
         <v>4</v>
       </c>
-      <c r="B3" t="s">
-        <v>112</v>
-      </c>
-      <c r="C3" t="s">
-        <v>112</v>
-      </c>
-      <c r="D3" t="s">
-        <v>112</v>
+      <c r="B3">
+        <v>15279.14</v>
+      </c>
+      <c r="C3">
+        <v>8267.16</v>
+      </c>
+      <c r="D3">
+        <v>5950.81</v>
       </c>
       <c r="E3">
         <v>4808.17</v>
@@ -850,14 +838,14 @@
       <c r="A4" t="s">
         <v>5</v>
       </c>
-      <c r="B4" t="s">
-        <v>112</v>
-      </c>
-      <c r="C4" t="s">
-        <v>112</v>
-      </c>
-      <c r="D4" t="s">
-        <v>112</v>
+      <c r="B4">
+        <v>19098.919999999998</v>
+      </c>
+      <c r="C4">
+        <v>10333.950000000001</v>
+      </c>
+      <c r="D4">
+        <v>7438.52</v>
       </c>
       <c r="E4">
         <v>6010.21</v>
@@ -873,14 +861,14 @@
       <c r="A5" t="s">
         <v>6</v>
       </c>
-      <c r="B5" t="s">
-        <v>112</v>
-      </c>
-      <c r="C5" t="s">
-        <v>112</v>
-      </c>
-      <c r="D5" t="s">
-        <v>112</v>
+      <c r="B5">
+        <v>22918.71</v>
+      </c>
+      <c r="C5">
+        <v>12400.73</v>
+      </c>
+      <c r="D5">
+        <v>8926.2199999999993</v>
       </c>
       <c r="E5">
         <v>7212.25</v>
@@ -896,14 +884,14 @@
       <c r="A6" t="s">
         <v>7</v>
       </c>
-      <c r="B6" t="s">
-        <v>112</v>
-      </c>
-      <c r="C6" t="s">
-        <v>112</v>
-      </c>
-      <c r="D6" t="s">
-        <v>112</v>
+      <c r="B6">
+        <v>26738.49</v>
+      </c>
+      <c r="C6">
+        <v>14467.52</v>
+      </c>
+      <c r="D6">
+        <v>10413.92</v>
       </c>
       <c r="E6">
         <v>8414.2999999999993</v>
@@ -919,14 +907,14 @@
       <c r="A7" t="s">
         <v>8</v>
       </c>
-      <c r="B7" t="s">
-        <v>112</v>
-      </c>
-      <c r="C7" t="s">
-        <v>112</v>
-      </c>
-      <c r="D7" t="s">
-        <v>112</v>
+      <c r="B7">
+        <v>30558.27</v>
+      </c>
+      <c r="C7">
+        <v>16534.310000000001</v>
+      </c>
+      <c r="D7">
+        <v>11901.63</v>
       </c>
       <c r="E7">
         <v>9616.64</v>
@@ -942,14 +930,14 @@
       <c r="A8" t="s">
         <v>9</v>
       </c>
-      <c r="B8" t="s">
-        <v>112</v>
-      </c>
-      <c r="C8" t="s">
-        <v>112</v>
-      </c>
-      <c r="D8" t="s">
-        <v>112</v>
+      <c r="B8">
+        <v>34378.06</v>
+      </c>
+      <c r="C8">
+        <v>18601.099999999999</v>
+      </c>
+      <c r="D8">
+        <v>13389.33</v>
       </c>
       <c r="E8">
         <v>10818.38</v>
@@ -989,13 +977,13 @@
         <v>11</v>
       </c>
       <c r="B10">
-        <v>22734.68</v>
+        <v>42017.63</v>
       </c>
       <c r="C10">
         <v>22734.68</v>
       </c>
-      <c r="D10" t="s">
-        <v>112</v>
+      <c r="D10">
+        <v>16364.74</v>
       </c>
       <c r="E10">
         <v>13222.46</v>
@@ -1011,14 +999,14 @@
       <c r="A11" t="s">
         <v>12</v>
       </c>
-      <c r="B11" t="s">
-        <v>112</v>
-      </c>
-      <c r="C11" t="s">
-        <v>112</v>
-      </c>
-      <c r="D11" t="s">
-        <v>112</v>
+      <c r="B11">
+        <v>45833.97</v>
+      </c>
+      <c r="C11">
+        <v>24801.47</v>
+      </c>
+      <c r="D11">
+        <v>17852.439999999999</v>
       </c>
       <c r="E11">
         <v>14424.51</v>
@@ -1034,14 +1022,14 @@
       <c r="A12" t="s">
         <v>13</v>
       </c>
-      <c r="B12" t="s">
-        <v>112</v>
-      </c>
-      <c r="C12" t="s">
-        <v>112</v>
-      </c>
-      <c r="D12" t="s">
-        <v>112</v>
+      <c r="B12">
+        <v>49657.2</v>
+      </c>
+      <c r="C12">
+        <v>26868.26</v>
+      </c>
+      <c r="D12">
+        <v>19340.14</v>
       </c>
       <c r="E12">
         <v>15626.55</v>
@@ -1057,14 +1045,14 @@
       <c r="A13" t="s">
         <v>14</v>
       </c>
-      <c r="B13" t="s">
-        <v>112</v>
-      </c>
-      <c r="C13" t="s">
-        <v>112</v>
-      </c>
-      <c r="D13" t="s">
-        <v>112</v>
+      <c r="B13">
+        <v>53473.54</v>
+      </c>
+      <c r="C13">
+        <v>28935.05</v>
+      </c>
+      <c r="D13">
+        <v>20827.849999999999</v>
       </c>
       <c r="E13">
         <v>16828.59</v>
@@ -1103,14 +1091,14 @@
       <c r="A15" t="s">
         <v>16</v>
       </c>
-      <c r="B15" t="s">
-        <v>112</v>
-      </c>
-      <c r="C15" t="s">
-        <v>112</v>
-      </c>
-      <c r="D15" t="s">
-        <v>112</v>
+      <c r="B15">
+        <v>61116.55</v>
+      </c>
+      <c r="C15">
+        <v>33068.620000000003</v>
+      </c>
+      <c r="D15">
+        <v>23803.25</v>
       </c>
       <c r="E15">
         <v>19232.68</v>
@@ -1126,14 +1114,14 @@
       <c r="A16" t="s">
         <v>17</v>
       </c>
-      <c r="B16" t="s">
-        <v>112</v>
-      </c>
-      <c r="C16" t="s">
-        <v>112</v>
-      </c>
-      <c r="D16" t="s">
-        <v>112</v>
+      <c r="B16">
+        <v>64936.33</v>
+      </c>
+      <c r="C16">
+        <v>35135.410000000003</v>
+      </c>
+      <c r="D16">
+        <v>25290.959999999999</v>
       </c>
       <c r="E16">
         <v>20434.72</v>
@@ -1149,14 +1137,14 @@
       <c r="A17" t="s">
         <v>18</v>
       </c>
-      <c r="B17" t="s">
-        <v>112</v>
-      </c>
-      <c r="C17" t="s">
-        <v>112</v>
-      </c>
-      <c r="D17" t="s">
-        <v>112</v>
+      <c r="B17">
+        <v>68756.12</v>
+      </c>
+      <c r="C17">
+        <v>37202.199999999997</v>
+      </c>
+      <c r="D17">
+        <v>26778.66</v>
       </c>
       <c r="E17">
         <v>21636.76</v>
@@ -1172,14 +1160,14 @@
       <c r="A18" t="s">
         <v>19</v>
       </c>
-      <c r="B18" t="s">
-        <v>112</v>
-      </c>
-      <c r="C18" t="s">
-        <v>112</v>
-      </c>
-      <c r="D18" t="s">
-        <v>112</v>
+      <c r="B18">
+        <v>72575.899999999994</v>
+      </c>
+      <c r="C18">
+        <v>39268.99</v>
+      </c>
+      <c r="D18">
+        <v>28266.36</v>
       </c>
       <c r="E18">
         <v>22838.799999999999</v>
@@ -1218,14 +1206,14 @@
       <c r="A20" t="s">
         <v>21</v>
       </c>
-      <c r="B20" t="s">
-        <v>112</v>
-      </c>
-      <c r="C20" t="s">
-        <v>112</v>
-      </c>
-      <c r="D20" t="s">
-        <v>112</v>
+      <c r="B20">
+        <v>80215.47</v>
+      </c>
+      <c r="C20">
+        <v>43402.57</v>
+      </c>
+      <c r="D20">
+        <v>31241.77</v>
       </c>
       <c r="E20">
         <v>25242.89</v>
@@ -1241,14 +1229,14 @@
       <c r="A21" t="s">
         <v>22</v>
       </c>
-      <c r="B21" t="s">
-        <v>112</v>
-      </c>
-      <c r="C21" t="s">
-        <v>112</v>
-      </c>
-      <c r="D21" t="s">
-        <v>112</v>
+      <c r="B21">
+        <v>84035.26</v>
+      </c>
+      <c r="C21">
+        <v>45469.36</v>
+      </c>
+      <c r="D21">
+        <v>32729.47</v>
       </c>
       <c r="E21">
         <v>26444.93</v>
@@ -1264,14 +1252,14 @@
       <c r="A22" t="s">
         <v>23</v>
       </c>
-      <c r="B22" t="s">
-        <v>112</v>
-      </c>
-      <c r="C22" t="s">
-        <v>112</v>
-      </c>
-      <c r="D22" t="s">
-        <v>112</v>
+      <c r="B22">
+        <v>87855.039999999994</v>
+      </c>
+      <c r="C22">
+        <v>47536.15</v>
+      </c>
+      <c r="D22">
+        <v>34217.18</v>
       </c>
       <c r="E22">
         <v>27646.97</v>
@@ -1287,14 +1275,14 @@
       <c r="A23" t="s">
         <v>24</v>
       </c>
-      <c r="B23" t="s">
-        <v>112</v>
-      </c>
-      <c r="C23" t="s">
-        <v>112</v>
-      </c>
-      <c r="D23" t="s">
-        <v>112</v>
+      <c r="B23">
+        <v>91674.82</v>
+      </c>
+      <c r="C23">
+        <v>49602.94</v>
+      </c>
+      <c r="D23">
+        <v>35704.879999999997</v>
       </c>
       <c r="E23">
         <v>28848.01</v>
@@ -1333,14 +1321,14 @@
       <c r="A25" t="s">
         <v>26</v>
       </c>
-      <c r="B25" t="s">
-        <v>112</v>
-      </c>
-      <c r="C25" t="s">
-        <v>112</v>
-      </c>
-      <c r="D25" t="s">
-        <v>112</v>
+      <c r="B25">
+        <v>99314.39</v>
+      </c>
+      <c r="C25">
+        <v>53736.51</v>
+      </c>
+      <c r="D25">
+        <v>38680.29</v>
       </c>
       <c r="E25">
         <v>31253.1</v>
@@ -1356,14 +1344,14 @@
       <c r="A26" t="s">
         <v>27</v>
       </c>
-      <c r="B26" t="s">
-        <v>112</v>
-      </c>
-      <c r="C26" t="s">
-        <v>112</v>
-      </c>
-      <c r="D26" t="s">
-        <v>112</v>
+      <c r="B26">
+        <v>103134.18</v>
+      </c>
+      <c r="C26">
+        <v>55803.3</v>
+      </c>
+      <c r="D26">
+        <v>40167.99</v>
       </c>
       <c r="E26">
         <v>32455.14</v>
@@ -1379,14 +1367,14 @@
       <c r="A27" t="s">
         <v>28</v>
       </c>
-      <c r="B27" t="s">
-        <v>112</v>
-      </c>
-      <c r="C27" t="s">
-        <v>112</v>
-      </c>
-      <c r="D27" t="s">
-        <v>112</v>
+      <c r="B27">
+        <v>106953.96</v>
+      </c>
+      <c r="C27">
+        <v>57870.09</v>
+      </c>
+      <c r="D27">
+        <v>41655.69</v>
       </c>
       <c r="E27">
         <v>33657.18</v>
@@ -1402,14 +1390,14 @@
       <c r="A28" t="s">
         <v>29</v>
       </c>
-      <c r="B28" t="s">
-        <v>112</v>
-      </c>
-      <c r="C28" t="s">
-        <v>112</v>
-      </c>
-      <c r="D28" t="s">
-        <v>112</v>
+      <c r="B28">
+        <v>110773.75</v>
+      </c>
+      <c r="C28">
+        <v>59936.88</v>
+      </c>
+      <c r="D28">
+        <v>43413.4</v>
       </c>
       <c r="E28">
         <v>34859.22</v>
@@ -1448,14 +1436,14 @@
       <c r="A30" t="s">
         <v>31</v>
       </c>
-      <c r="B30" t="s">
-        <v>112</v>
-      </c>
-      <c r="C30" t="s">
-        <v>112</v>
-      </c>
-      <c r="D30" t="s">
-        <v>112</v>
+      <c r="B30">
+        <v>118413.31</v>
+      </c>
+      <c r="C30">
+        <v>64070.46</v>
+      </c>
+      <c r="D30">
+        <v>46118.8</v>
       </c>
       <c r="E30">
         <v>37263.31</v>
@@ -1471,14 +1459,14 @@
       <c r="A31" t="s">
         <v>32</v>
       </c>
-      <c r="B31" t="s">
-        <v>112</v>
-      </c>
-      <c r="C31" t="s">
-        <v>112</v>
-      </c>
-      <c r="D31" t="s">
-        <v>112</v>
+      <c r="B31">
+        <v>122233.1</v>
+      </c>
+      <c r="C31">
+        <v>66137.25</v>
+      </c>
+      <c r="D31">
+        <v>47606.51</v>
       </c>
       <c r="E31">
         <v>38465.35</v>
@@ -1494,14 +1482,14 @@
       <c r="A32" t="s">
         <v>33</v>
       </c>
-      <c r="B32" t="s">
-        <v>112</v>
-      </c>
-      <c r="C32" t="s">
-        <v>112</v>
-      </c>
-      <c r="D32" t="s">
-        <v>112</v>
+      <c r="B32">
+        <v>126052.88</v>
+      </c>
+      <c r="C32">
+        <v>68204.039999999994</v>
+      </c>
+      <c r="D32">
+        <v>49094.21</v>
       </c>
       <c r="E32">
         <v>39667.39</v>
@@ -1517,14 +1505,14 @@
       <c r="A33" t="s">
         <v>34</v>
       </c>
-      <c r="B33" t="s">
-        <v>112</v>
-      </c>
-      <c r="C33" t="s">
-        <v>112</v>
-      </c>
-      <c r="D33" t="s">
-        <v>112</v>
+      <c r="B33">
+        <v>129872.67</v>
+      </c>
+      <c r="C33">
+        <v>70270.83</v>
+      </c>
+      <c r="D33">
+        <v>50581.91</v>
       </c>
       <c r="E33">
         <v>40869.440000000002</v>
@@ -1563,14 +1551,14 @@
       <c r="A35" t="s">
         <v>36</v>
       </c>
-      <c r="B35" t="s">
-        <v>112</v>
-      </c>
-      <c r="C35" t="s">
-        <v>112</v>
-      </c>
-      <c r="D35" t="s">
-        <v>112</v>
+      <c r="B35">
+        <v>137512.24</v>
+      </c>
+      <c r="C35">
+        <v>74404.399999999994</v>
+      </c>
+      <c r="D35">
+        <v>53557.32</v>
       </c>
       <c r="E35">
         <v>43273.52</v>
@@ -1586,14 +1574,14 @@
       <c r="A36" t="s">
         <v>37</v>
       </c>
-      <c r="B36" t="s">
-        <v>112</v>
-      </c>
-      <c r="C36" t="s">
-        <v>112</v>
-      </c>
-      <c r="D36" t="s">
-        <v>112</v>
+      <c r="B36">
+        <v>141332.01999999999</v>
+      </c>
+      <c r="C36">
+        <v>76471.19</v>
+      </c>
+      <c r="D36">
+        <v>55045.02</v>
       </c>
       <c r="E36">
         <v>44475.56</v>
@@ -1609,14 +1597,14 @@
       <c r="A37" t="s">
         <v>38</v>
       </c>
-      <c r="B37" t="s">
-        <v>112</v>
-      </c>
-      <c r="C37" t="s">
-        <v>112</v>
-      </c>
-      <c r="D37" t="s">
-        <v>112</v>
+      <c r="B37">
+        <v>145151.79999999999</v>
+      </c>
+      <c r="C37">
+        <v>78537.98</v>
+      </c>
+      <c r="D37">
+        <v>56532.72</v>
       </c>
       <c r="E37">
         <v>45667.6</v>
@@ -1632,14 +1620,14 @@
       <c r="A38" t="s">
         <v>39</v>
       </c>
-      <c r="B38" t="s">
-        <v>112</v>
-      </c>
-      <c r="C38" t="s">
-        <v>112</v>
-      </c>
-      <c r="D38" t="s">
-        <v>112</v>
+      <c r="B38">
+        <v>148971.59</v>
+      </c>
+      <c r="C38">
+        <v>80604.77</v>
+      </c>
+      <c r="D38">
+        <v>58020.43</v>
       </c>
       <c r="E38">
         <v>46879.65</v>
@@ -1678,14 +1666,14 @@
       <c r="A40" t="s">
         <v>41</v>
       </c>
-      <c r="B40" t="s">
-        <v>112</v>
-      </c>
-      <c r="C40" t="s">
-        <v>112</v>
-      </c>
-      <c r="D40" t="s">
-        <v>112</v>
+      <c r="B40">
+        <v>156611.16</v>
+      </c>
+      <c r="C40">
+        <v>84738.35</v>
+      </c>
+      <c r="D40">
+        <v>60995.83</v>
       </c>
       <c r="E40">
         <v>49283.73</v>
@@ -1701,14 +1689,14 @@
       <c r="A41" t="s">
         <v>42</v>
       </c>
-      <c r="B41" t="s">
-        <v>112</v>
-      </c>
-      <c r="C41" t="s">
-        <v>112</v>
-      </c>
-      <c r="D41" t="s">
-        <v>112</v>
+      <c r="B41">
+        <v>160430.94</v>
+      </c>
+      <c r="C41">
+        <v>86805.14</v>
+      </c>
+      <c r="D41">
+        <v>62483.54</v>
       </c>
       <c r="E41">
         <v>50485.77</v>
@@ -1724,14 +1712,14 @@
       <c r="A42" t="s">
         <v>43</v>
       </c>
-      <c r="B42" t="s">
-        <v>112</v>
-      </c>
-      <c r="C42" t="s">
-        <v>112</v>
-      </c>
-      <c r="D42" t="s">
-        <v>112</v>
+      <c r="B42">
+        <v>164250.73000000001</v>
+      </c>
+      <c r="C42">
+        <v>88871.93</v>
+      </c>
+      <c r="D42">
+        <v>63971.24</v>
       </c>
       <c r="E42">
         <v>51687.82</v>
@@ -1747,14 +1735,14 @@
       <c r="A43" t="s">
         <v>44</v>
       </c>
-      <c r="B43" t="s">
-        <v>112</v>
-      </c>
-      <c r="C43" t="s">
-        <v>112</v>
-      </c>
-      <c r="D43" t="s">
-        <v>112</v>
+      <c r="B43">
+        <v>168070.51</v>
+      </c>
+      <c r="C43">
+        <v>90938.72</v>
+      </c>
+      <c r="D43">
+        <v>65458.94</v>
       </c>
       <c r="E43">
         <v>52889.86</v>
@@ -1782,7 +1770,7 @@
       <c r="E44">
         <v>54091.9</v>
       </c>
-      <c r="F44" s="3">
+      <c r="F44" s="1">
         <v>41577.269999999997</v>
       </c>
       <c r="G44">
@@ -1793,14 +1781,14 @@
       <c r="A45" t="s">
         <v>46</v>
       </c>
-      <c r="B45" t="s">
-        <v>112</v>
-      </c>
-      <c r="C45" t="s">
-        <v>112</v>
-      </c>
-      <c r="D45" t="s">
-        <v>112</v>
+      <c r="B45">
+        <v>175710.07999999999</v>
+      </c>
+      <c r="C45">
+        <v>95072.29</v>
+      </c>
+      <c r="D45">
+        <v>68434.350000000006</v>
       </c>
       <c r="E45">
         <v>55293.94</v>
@@ -1816,14 +1804,14 @@
       <c r="A46" t="s">
         <v>47</v>
       </c>
-      <c r="B46" t="s">
-        <v>112</v>
-      </c>
-      <c r="C46" t="s">
-        <v>112</v>
-      </c>
-      <c r="D46" t="s">
-        <v>112</v>
+      <c r="B46">
+        <v>179529.86</v>
+      </c>
+      <c r="C46">
+        <v>97139.08</v>
+      </c>
+      <c r="D46">
+        <v>69922.05</v>
       </c>
       <c r="E46">
         <v>56495.98</v>
@@ -1839,14 +1827,14 @@
       <c r="A47" t="s">
         <v>48</v>
       </c>
-      <c r="B47" t="s">
-        <v>112</v>
-      </c>
-      <c r="C47" t="s">
-        <v>112</v>
-      </c>
-      <c r="D47" t="s">
-        <v>112</v>
+      <c r="B47">
+        <v>183349.65</v>
+      </c>
+      <c r="C47">
+        <v>99205.87</v>
+      </c>
+      <c r="D47">
+        <v>71409.759999999995</v>
       </c>
       <c r="E47">
         <v>57698.03</v>
@@ -1862,14 +1850,14 @@
       <c r="A48" t="s">
         <v>49</v>
       </c>
-      <c r="B48" t="s">
-        <v>112</v>
-      </c>
-      <c r="C48" t="s">
-        <v>112</v>
-      </c>
-      <c r="D48" t="s">
-        <v>112</v>
+      <c r="B48">
+        <v>187169.43</v>
+      </c>
+      <c r="C48">
+        <v>101272.66</v>
+      </c>
+      <c r="D48">
+        <v>72897.460000000006</v>
       </c>
       <c r="E48">
         <v>59800.07</v>
@@ -1908,14 +1896,14 @@
       <c r="A50" t="s">
         <v>51</v>
       </c>
-      <c r="B50" t="s">
-        <v>112</v>
-      </c>
-      <c r="C50" t="s">
-        <v>112</v>
-      </c>
-      <c r="D50" t="s">
-        <v>112</v>
+      <c r="B50">
+        <v>194809</v>
+      </c>
+      <c r="C50">
+        <v>105406.24</v>
+      </c>
+      <c r="D50">
+        <v>75872.87</v>
       </c>
       <c r="E50">
         <v>61304.15</v>
@@ -1931,14 +1919,14 @@
       <c r="A51" t="s">
         <v>52</v>
       </c>
-      <c r="B51" t="s">
-        <v>112</v>
-      </c>
-      <c r="C51" t="s">
-        <v>112</v>
-      </c>
-      <c r="D51" t="s">
-        <v>112</v>
+      <c r="B51">
+        <v>198628.79</v>
+      </c>
+      <c r="C51">
+        <v>107473.03</v>
+      </c>
+      <c r="D51">
+        <v>77360.570000000007</v>
       </c>
       <c r="E51">
         <v>62506.2</v>
@@ -1954,14 +1942,14 @@
       <c r="A52" t="s">
         <v>53</v>
       </c>
-      <c r="B52" t="s">
-        <v>112</v>
-      </c>
-      <c r="C52" t="s">
-        <v>112</v>
-      </c>
-      <c r="D52" t="s">
-        <v>112</v>
+      <c r="B52">
+        <v>202448.57</v>
+      </c>
+      <c r="C52">
+        <v>109539.82</v>
+      </c>
+      <c r="D52">
+        <v>78848.27</v>
       </c>
       <c r="E52">
         <v>63708.24</v>
@@ -1977,14 +1965,14 @@
       <c r="A53" t="s">
         <v>54</v>
       </c>
-      <c r="B53" t="s">
-        <v>112</v>
-      </c>
-      <c r="C53" t="s">
-        <v>112</v>
-      </c>
-      <c r="D53" t="s">
-        <v>112</v>
+      <c r="B53">
+        <v>206268.35</v>
+      </c>
+      <c r="C53">
+        <v>111606.61</v>
+      </c>
+      <c r="D53">
+        <v>80335.98</v>
       </c>
       <c r="E53">
         <v>64910.28</v>
@@ -2023,14 +2011,14 @@
       <c r="A55" t="s">
         <v>56</v>
       </c>
-      <c r="B55" t="s">
-        <v>112</v>
-      </c>
-      <c r="C55" t="s">
-        <v>112</v>
-      </c>
-      <c r="D55" t="s">
-        <v>112</v>
+      <c r="B55">
+        <v>213907.92</v>
+      </c>
+      <c r="C55">
+        <v>115740.18</v>
+      </c>
+      <c r="D55">
+        <v>83311.38</v>
       </c>
       <c r="E55">
         <v>67314.36</v>
@@ -2046,14 +2034,14 @@
       <c r="A56" t="s">
         <v>57</v>
       </c>
-      <c r="B56" t="s">
-        <v>112</v>
-      </c>
-      <c r="C56" t="s">
-        <v>112</v>
-      </c>
-      <c r="D56" t="s">
-        <v>112</v>
+      <c r="B56">
+        <v>217727.71</v>
+      </c>
+      <c r="C56">
+        <v>117806.97</v>
+      </c>
+      <c r="D56">
+        <v>84799.09</v>
       </c>
       <c r="E56">
         <v>68516.41</v>
@@ -2069,14 +2057,14 @@
       <c r="A57" t="s">
         <v>58</v>
       </c>
-      <c r="B57" t="s">
-        <v>112</v>
-      </c>
-      <c r="C57" t="s">
-        <v>112</v>
-      </c>
-      <c r="D57" t="s">
-        <v>112</v>
+      <c r="B57">
+        <v>221547.49</v>
+      </c>
+      <c r="C57">
+        <v>119873.76</v>
+      </c>
+      <c r="D57">
+        <v>86286.79</v>
       </c>
       <c r="E57">
         <v>69718.45</v>
@@ -2092,14 +2080,14 @@
       <c r="A58" t="s">
         <v>59</v>
       </c>
-      <c r="B58" t="s">
-        <v>112</v>
-      </c>
-      <c r="C58" t="s">
-        <v>112</v>
-      </c>
-      <c r="D58" t="s">
-        <v>112</v>
+      <c r="B58">
+        <v>225367.28</v>
+      </c>
+      <c r="C58">
+        <v>121940.55</v>
+      </c>
+      <c r="D58">
+        <v>87774.49</v>
       </c>
       <c r="E58">
         <v>70920.490000000005</v>
@@ -2138,14 +2126,14 @@
       <c r="A60" t="s">
         <v>61</v>
       </c>
-      <c r="B60" t="s">
-        <v>112</v>
-      </c>
-      <c r="C60" t="s">
-        <v>112</v>
-      </c>
-      <c r="D60" t="s">
-        <v>112</v>
+      <c r="B60">
+        <v>233006.84</v>
+      </c>
+      <c r="C60">
+        <v>126074.13</v>
+      </c>
+      <c r="D60">
+        <v>90749.9</v>
       </c>
       <c r="E60">
         <v>73324.58</v>
@@ -2161,14 +2149,14 @@
       <c r="A61" t="s">
         <v>62</v>
       </c>
-      <c r="B61" t="s">
-        <v>112</v>
-      </c>
-      <c r="C61" t="s">
-        <v>112</v>
-      </c>
-      <c r="D61" t="s">
-        <v>112</v>
+      <c r="B61">
+        <v>236826.63</v>
+      </c>
+      <c r="C61">
+        <v>128140.92</v>
+      </c>
+      <c r="D61">
+        <v>92237.6</v>
       </c>
       <c r="E61">
         <v>74526.62</v>
@@ -2184,14 +2172,14 @@
       <c r="A62" t="s">
         <v>63</v>
       </c>
-      <c r="B62" t="s">
-        <v>112</v>
-      </c>
-      <c r="C62" t="s">
-        <v>112</v>
-      </c>
-      <c r="D62" t="s">
-        <v>112</v>
+      <c r="B62">
+        <v>240646.41</v>
+      </c>
+      <c r="C62">
+        <v>130207.71</v>
+      </c>
+      <c r="D62">
+        <v>93725.31</v>
       </c>
       <c r="E62">
         <v>75728.66</v>
@@ -2207,14 +2195,14 @@
       <c r="A63" t="s">
         <v>64</v>
       </c>
-      <c r="B63" t="s">
-        <v>112</v>
-      </c>
-      <c r="C63" t="s">
-        <v>112</v>
-      </c>
-      <c r="D63" t="s">
-        <v>112</v>
+      <c r="B63">
+        <v>244466.2</v>
+      </c>
+      <c r="C63">
+        <v>132274.5</v>
+      </c>
+      <c r="D63">
+        <v>95213.01</v>
       </c>
       <c r="E63">
         <v>76930.7</v>
@@ -2253,14 +2241,14 @@
       <c r="A65" t="s">
         <v>66</v>
       </c>
-      <c r="B65" t="s">
-        <v>112</v>
-      </c>
-      <c r="C65" t="s">
-        <v>112</v>
-      </c>
-      <c r="D65" t="s">
-        <v>112</v>
+      <c r="B65">
+        <v>252105.77</v>
+      </c>
+      <c r="C65">
+        <v>136408.07</v>
+      </c>
+      <c r="D65">
+        <v>98188.42</v>
       </c>
       <c r="E65">
         <v>79334.789999999994</v>
@@ -2276,14 +2264,14 @@
       <c r="A66" t="s">
         <v>67</v>
       </c>
-      <c r="B66" t="s">
-        <v>112</v>
-      </c>
-      <c r="C66" t="s">
-        <v>112</v>
-      </c>
-      <c r="D66" t="s">
-        <v>112</v>
+      <c r="B66">
+        <v>255925.55</v>
+      </c>
+      <c r="C66">
+        <v>138474.85999999999</v>
+      </c>
+      <c r="D66">
+        <v>99676.12</v>
       </c>
       <c r="E66">
         <v>80536.83</v>
@@ -2299,14 +2287,14 @@
       <c r="A67" t="s">
         <v>68</v>
       </c>
-      <c r="B67" t="s">
-        <v>112</v>
-      </c>
-      <c r="C67" t="s">
-        <v>112</v>
-      </c>
-      <c r="D67" t="s">
-        <v>112</v>
+      <c r="B67">
+        <v>259745.33</v>
+      </c>
+      <c r="C67">
+        <v>140541.65</v>
+      </c>
+      <c r="D67">
+        <v>101163.82</v>
       </c>
       <c r="E67">
         <v>81738.87</v>
@@ -2322,14 +2310,14 @@
       <c r="A68" t="s">
         <v>69</v>
       </c>
-      <c r="B68" t="s">
-        <v>112</v>
-      </c>
-      <c r="C68" t="s">
-        <v>112</v>
-      </c>
-      <c r="D68" t="s">
-        <v>112</v>
+      <c r="B68">
+        <v>263565.12</v>
+      </c>
+      <c r="C68">
+        <v>142608.44</v>
+      </c>
+      <c r="D68">
+        <v>102651.53</v>
       </c>
       <c r="E68">
         <v>82940.91</v>
@@ -2345,14 +2333,14 @@
       <c r="A69" t="s">
         <v>70</v>
       </c>
-      <c r="B69" t="s">
-        <v>112</v>
-      </c>
-      <c r="C69" t="s">
-        <v>112</v>
-      </c>
-      <c r="D69" t="s">
-        <v>112</v>
+      <c r="B69">
+        <v>267384.90000000002</v>
+      </c>
+      <c r="C69">
+        <v>144675.23000000001</v>
+      </c>
+      <c r="D69">
+        <v>104139.23</v>
       </c>
       <c r="E69">
         <v>84142.96</v>
@@ -2368,14 +2356,14 @@
       <c r="A70" t="s">
         <v>71</v>
       </c>
-      <c r="B70" t="s">
-        <v>112</v>
-      </c>
-      <c r="C70" t="s">
-        <v>112</v>
-      </c>
-      <c r="D70" t="s">
-        <v>112</v>
+      <c r="B70">
+        <v>271204.69</v>
+      </c>
+      <c r="C70">
+        <v>146742.01999999999</v>
+      </c>
+      <c r="D70">
+        <v>105626.93</v>
       </c>
       <c r="E70">
         <v>85345</v>
@@ -2391,14 +2379,14 @@
       <c r="A71" t="s">
         <v>72</v>
       </c>
-      <c r="B71" t="s">
-        <v>112</v>
-      </c>
-      <c r="C71" t="s">
-        <v>112</v>
-      </c>
-      <c r="D71" t="s">
-        <v>112</v>
+      <c r="B71">
+        <v>275024.46999999997</v>
+      </c>
+      <c r="C71">
+        <v>148808.81</v>
+      </c>
+      <c r="D71">
+        <v>107114.64</v>
       </c>
       <c r="E71">
         <v>86547.04</v>
@@ -2414,14 +2402,14 @@
       <c r="A72" t="s">
         <v>73</v>
       </c>
-      <c r="B72" t="s">
-        <v>112</v>
-      </c>
-      <c r="C72" t="s">
-        <v>112</v>
-      </c>
-      <c r="D72" t="s">
-        <v>112</v>
+      <c r="B72">
+        <v>278844.26</v>
+      </c>
+      <c r="C72">
+        <v>150875.6</v>
+      </c>
+      <c r="D72">
+        <v>108602.34</v>
       </c>
       <c r="E72">
         <v>87749.08</v>
@@ -2437,14 +2425,14 @@
       <c r="A73" t="s">
         <v>74</v>
       </c>
-      <c r="B73" t="s">
-        <v>112</v>
-      </c>
-      <c r="C73" t="s">
-        <v>112</v>
-      </c>
-      <c r="D73" t="s">
-        <v>112</v>
+      <c r="B73">
+        <v>282664.03999999998</v>
+      </c>
+      <c r="C73">
+        <v>152942.39000000001</v>
+      </c>
+      <c r="D73">
+        <v>110090.04</v>
       </c>
       <c r="E73">
         <v>88951.12</v>
@@ -2460,14 +2448,14 @@
       <c r="A74" t="s">
         <v>75</v>
       </c>
-      <c r="B74" t="s">
-        <v>112</v>
-      </c>
-      <c r="C74" t="s">
-        <v>112</v>
-      </c>
-      <c r="D74" t="s">
-        <v>112</v>
+      <c r="B74">
+        <v>286483.82</v>
+      </c>
+      <c r="C74">
+        <v>155009.18</v>
+      </c>
+      <c r="D74">
+        <v>111577.75</v>
       </c>
       <c r="E74">
         <v>90153.17</v>
@@ -2483,14 +2471,14 @@
       <c r="A75" t="s">
         <v>76</v>
       </c>
-      <c r="B75" t="s">
-        <v>112</v>
-      </c>
-      <c r="C75" t="s">
-        <v>112</v>
-      </c>
-      <c r="D75" t="s">
-        <v>112</v>
+      <c r="B75">
+        <v>290303.61</v>
+      </c>
+      <c r="C75">
+        <v>157075.96</v>
+      </c>
+      <c r="D75">
+        <v>113065.45</v>
       </c>
       <c r="E75">
         <v>91355.21</v>
@@ -2506,14 +2494,14 @@
       <c r="A76" t="s">
         <v>77</v>
       </c>
-      <c r="B76" t="s">
-        <v>112</v>
-      </c>
-      <c r="C76" t="s">
-        <v>112</v>
-      </c>
-      <c r="D76" t="s">
-        <v>112</v>
+      <c r="B76">
+        <v>294123.39</v>
+      </c>
+      <c r="C76">
+        <v>159142.75</v>
+      </c>
+      <c r="D76">
+        <v>114553.15</v>
       </c>
       <c r="E76">
         <v>92557.25</v>
@@ -2529,14 +2517,14 @@
       <c r="A77" t="s">
         <v>78</v>
       </c>
-      <c r="B77" t="s">
-        <v>112</v>
-      </c>
-      <c r="C77" t="s">
-        <v>112</v>
-      </c>
-      <c r="D77" t="s">
-        <v>112</v>
+      <c r="B77">
+        <v>297943.18</v>
+      </c>
+      <c r="C77">
+        <v>161209.54</v>
+      </c>
+      <c r="D77">
+        <v>116040.86</v>
       </c>
       <c r="E77">
         <v>93759.29</v>
@@ -2552,14 +2540,14 @@
       <c r="A78" t="s">
         <v>79</v>
       </c>
-      <c r="B78" t="s">
-        <v>112</v>
-      </c>
-      <c r="C78" t="s">
-        <v>112</v>
-      </c>
-      <c r="D78" t="s">
-        <v>112</v>
+      <c r="B78">
+        <v>301762.96000000002</v>
+      </c>
+      <c r="C78">
+        <v>163276.32999999999</v>
+      </c>
+      <c r="D78">
+        <v>117528.56</v>
       </c>
       <c r="E78">
         <v>94961.34</v>
@@ -2575,14 +2563,14 @@
       <c r="A79" t="s">
         <v>80</v>
       </c>
-      <c r="B79" t="s">
-        <v>112</v>
-      </c>
-      <c r="C79" t="s">
-        <v>112</v>
-      </c>
-      <c r="D79" t="s">
-        <v>112</v>
+      <c r="B79">
+        <v>305582.75</v>
+      </c>
+      <c r="C79">
+        <v>165343.12</v>
+      </c>
+      <c r="D79">
+        <v>119016.26</v>
       </c>
       <c r="E79">
         <v>96163.38</v>
@@ -2598,14 +2586,14 @@
       <c r="A80" t="s">
         <v>81</v>
       </c>
-      <c r="B80" t="s">
-        <v>112</v>
-      </c>
-      <c r="C80" t="s">
-        <v>112</v>
-      </c>
-      <c r="D80" t="s">
-        <v>112</v>
+      <c r="B80">
+        <v>309402.53000000003</v>
+      </c>
+      <c r="C80">
+        <v>167409.91</v>
+      </c>
+      <c r="D80">
+        <v>120503.97</v>
       </c>
       <c r="E80">
         <v>97365.42</v>
@@ -2621,14 +2609,14 @@
       <c r="A81" t="s">
         <v>82</v>
       </c>
-      <c r="B81" t="s">
-        <v>112</v>
-      </c>
-      <c r="C81" t="s">
-        <v>112</v>
-      </c>
-      <c r="D81" t="s">
-        <v>112</v>
+      <c r="B81">
+        <v>313222.32</v>
+      </c>
+      <c r="C81">
+        <v>169476.7</v>
+      </c>
+      <c r="D81">
+        <v>121991.67</v>
       </c>
       <c r="E81">
         <v>98567.46</v>
@@ -2644,14 +2632,14 @@
       <c r="A82" t="s">
         <v>83</v>
       </c>
-      <c r="B82" t="s">
-        <v>112</v>
-      </c>
-      <c r="C82" t="s">
-        <v>112</v>
-      </c>
-      <c r="D82" t="s">
-        <v>112</v>
+      <c r="B82">
+        <v>317042.09999999998</v>
+      </c>
+      <c r="C82">
+        <v>171543.49</v>
+      </c>
+      <c r="D82">
+        <v>123479.37</v>
       </c>
       <c r="E82">
         <v>99769.5</v>
@@ -2667,14 +2655,14 @@
       <c r="A83" t="s">
         <v>84</v>
       </c>
-      <c r="B83" t="s">
-        <v>112</v>
-      </c>
-      <c r="C83" t="s">
-        <v>112</v>
-      </c>
-      <c r="D83" t="s">
-        <v>112</v>
+      <c r="B83">
+        <v>320861.88</v>
+      </c>
+      <c r="C83">
+        <v>173610.28</v>
+      </c>
+      <c r="D83">
+        <v>124967.08</v>
       </c>
       <c r="E83">
         <v>100971.55</v>
@@ -2690,14 +2678,14 @@
       <c r="A84" t="s">
         <v>85</v>
       </c>
-      <c r="B84" t="s">
-        <v>112</v>
-      </c>
-      <c r="C84" t="s">
-        <v>112</v>
-      </c>
-      <c r="D84" t="s">
-        <v>112</v>
+      <c r="B84">
+        <v>324681.67</v>
+      </c>
+      <c r="C84">
+        <v>175677.07</v>
+      </c>
+      <c r="D84">
+        <v>126454.78</v>
       </c>
       <c r="E84">
         <v>102173.59</v>
@@ -2713,14 +2701,14 @@
       <c r="A85" t="s">
         <v>86</v>
       </c>
-      <c r="B85" t="s">
-        <v>112</v>
-      </c>
-      <c r="C85" t="s">
-        <v>112</v>
-      </c>
-      <c r="D85" t="s">
-        <v>112</v>
+      <c r="B85">
+        <v>328501.45</v>
+      </c>
+      <c r="C85">
+        <v>177743.85</v>
+      </c>
+      <c r="D85">
+        <v>127942.48</v>
       </c>
       <c r="E85">
         <v>103375.63</v>
@@ -2736,14 +2724,14 @@
       <c r="A86" t="s">
         <v>87</v>
       </c>
-      <c r="B86" t="s">
-        <v>112</v>
-      </c>
-      <c r="C86" t="s">
-        <v>112</v>
-      </c>
-      <c r="D86" t="s">
-        <v>112</v>
+      <c r="B86">
+        <v>332321.24</v>
+      </c>
+      <c r="C86">
+        <v>179810.64</v>
+      </c>
+      <c r="D86">
+        <v>129430.19</v>
       </c>
       <c r="E86">
         <v>104577.67</v>
@@ -2759,14 +2747,14 @@
       <c r="A87" t="s">
         <v>88</v>
       </c>
-      <c r="B87" t="s">
-        <v>112</v>
-      </c>
-      <c r="C87" t="s">
-        <v>112</v>
-      </c>
-      <c r="D87" t="s">
-        <v>112</v>
+      <c r="B87">
+        <v>336141.02</v>
+      </c>
+      <c r="C87">
+        <v>181877.43</v>
+      </c>
+      <c r="D87">
+        <v>130917.89</v>
       </c>
       <c r="E87">
         <v>105779.72</v>
@@ -2782,14 +2770,14 @@
       <c r="A88" t="s">
         <v>89</v>
       </c>
-      <c r="B88" t="s">
-        <v>112</v>
-      </c>
-      <c r="C88" t="s">
-        <v>112</v>
-      </c>
-      <c r="D88" t="s">
-        <v>112</v>
+      <c r="B88">
+        <v>339960.81</v>
+      </c>
+      <c r="C88">
+        <v>183944.22</v>
+      </c>
+      <c r="D88">
+        <v>132405.59</v>
       </c>
       <c r="E88">
         <v>106981.75999999999</v>
@@ -2805,14 +2793,14 @@
       <c r="A89" t="s">
         <v>90</v>
       </c>
-      <c r="B89" t="s">
-        <v>112</v>
-      </c>
-      <c r="C89" t="s">
-        <v>112</v>
-      </c>
-      <c r="D89" t="s">
-        <v>112</v>
+      <c r="B89">
+        <v>343780.59</v>
+      </c>
+      <c r="C89">
+        <v>186011.01</v>
+      </c>
+      <c r="D89">
+        <v>133893.29999999999</v>
       </c>
       <c r="E89">
         <v>108183.8</v>
@@ -2828,14 +2816,14 @@
       <c r="A90" t="s">
         <v>91</v>
       </c>
-      <c r="B90" t="s">
-        <v>112</v>
-      </c>
-      <c r="C90" t="s">
-        <v>112</v>
-      </c>
-      <c r="D90" t="s">
-        <v>112</v>
+      <c r="B90">
+        <v>347600.37</v>
+      </c>
+      <c r="C90">
+        <v>188077.8</v>
+      </c>
+      <c r="D90">
+        <v>135381</v>
       </c>
       <c r="E90">
         <v>109385.84</v>
@@ -2851,14 +2839,14 @@
       <c r="A91" t="s">
         <v>92</v>
       </c>
-      <c r="B91" t="s">
-        <v>112</v>
-      </c>
-      <c r="C91" t="s">
-        <v>112</v>
-      </c>
-      <c r="D91" t="s">
-        <v>112</v>
+      <c r="B91">
+        <v>351420.15999999997</v>
+      </c>
+      <c r="C91">
+        <v>190144.59</v>
+      </c>
+      <c r="D91">
+        <v>136868.70000000001</v>
       </c>
       <c r="E91">
         <v>110587.88</v>
@@ -2874,14 +2862,14 @@
       <c r="A92" t="s">
         <v>93</v>
       </c>
-      <c r="B92" t="s">
-        <v>112</v>
-      </c>
-      <c r="C92" t="s">
-        <v>112</v>
-      </c>
-      <c r="D92" t="s">
-        <v>112</v>
+      <c r="B92">
+        <v>355239.94</v>
+      </c>
+      <c r="C92">
+        <v>192211.38</v>
+      </c>
+      <c r="D92">
+        <v>138356.41</v>
       </c>
       <c r="E92">
         <v>111789.93</v>
@@ -2897,14 +2885,14 @@
       <c r="A93" t="s">
         <v>94</v>
       </c>
-      <c r="B93" t="s">
-        <v>112</v>
-      </c>
-      <c r="C93" t="s">
-        <v>112</v>
-      </c>
-      <c r="D93" t="s">
-        <v>112</v>
+      <c r="B93">
+        <v>359059.73</v>
+      </c>
+      <c r="C93">
+        <v>194278.17</v>
+      </c>
+      <c r="D93">
+        <v>139844.10999999999</v>
       </c>
       <c r="E93">
         <v>112991.97</v>
@@ -2920,14 +2908,14 @@
       <c r="A94" t="s">
         <v>95</v>
       </c>
-      <c r="B94" t="s">
-        <v>112</v>
-      </c>
-      <c r="C94" t="s">
-        <v>112</v>
-      </c>
-      <c r="D94" t="s">
-        <v>112</v>
+      <c r="B94">
+        <v>362879.51</v>
+      </c>
+      <c r="C94">
+        <v>196344.95999999999</v>
+      </c>
+      <c r="D94">
+        <v>141331.81</v>
       </c>
       <c r="E94">
         <v>114194.01</v>
@@ -2943,14 +2931,14 @@
       <c r="A95" t="s">
         <v>96</v>
       </c>
-      <c r="B95" t="s">
-        <v>112</v>
-      </c>
-      <c r="C95" t="s">
-        <v>112</v>
-      </c>
-      <c r="D95" t="s">
-        <v>112</v>
+      <c r="B95">
+        <v>366699.3</v>
+      </c>
+      <c r="C95">
+        <v>198411.74</v>
+      </c>
+      <c r="D95">
+        <v>142819.51999999999</v>
       </c>
       <c r="E95">
         <v>115396.05</v>
@@ -2966,14 +2954,14 @@
       <c r="A96" t="s">
         <v>97</v>
       </c>
-      <c r="B96" t="s">
-        <v>112</v>
-      </c>
-      <c r="C96" t="s">
-        <v>112</v>
-      </c>
-      <c r="D96" t="s">
-        <v>112</v>
+      <c r="B96">
+        <v>370519.08</v>
+      </c>
+      <c r="C96">
+        <v>200478.53</v>
+      </c>
+      <c r="D96">
+        <v>144307.22</v>
       </c>
       <c r="E96">
         <v>116598.1</v>
@@ -2989,14 +2977,14 @@
       <c r="A97" t="s">
         <v>98</v>
       </c>
-      <c r="B97" t="s">
-        <v>112</v>
-      </c>
-      <c r="C97" t="s">
-        <v>112</v>
-      </c>
-      <c r="D97" t="s">
-        <v>112</v>
+      <c r="B97">
+        <v>374338.86</v>
+      </c>
+      <c r="C97">
+        <v>202545.32</v>
+      </c>
+      <c r="D97">
+        <v>145794.92000000001</v>
       </c>
       <c r="E97">
         <v>117800.14</v>
@@ -3012,14 +3000,14 @@
       <c r="A98" t="s">
         <v>99</v>
       </c>
-      <c r="B98" t="s">
-        <v>112</v>
-      </c>
-      <c r="C98" t="s">
-        <v>112</v>
-      </c>
-      <c r="D98" t="s">
-        <v>112</v>
+      <c r="B98">
+        <v>378158.65</v>
+      </c>
+      <c r="C98">
+        <v>204612.11</v>
+      </c>
+      <c r="D98">
+        <v>147282.63</v>
       </c>
       <c r="E98">
         <v>119002.18</v>
@@ -3035,14 +3023,14 @@
       <c r="A99" t="s">
         <v>100</v>
       </c>
-      <c r="B99" t="s">
-        <v>112</v>
-      </c>
-      <c r="C99" t="s">
-        <v>112</v>
-      </c>
-      <c r="D99" t="s">
-        <v>112</v>
+      <c r="B99">
+        <v>381978.43</v>
+      </c>
+      <c r="C99">
+        <v>206678.9</v>
+      </c>
+      <c r="D99">
+        <v>148770.32999999999</v>
       </c>
       <c r="E99">
         <v>120204.22</v>
@@ -3058,14 +3046,14 @@
       <c r="A100" t="s">
         <v>101</v>
       </c>
-      <c r="B100" t="s">
-        <v>112</v>
-      </c>
-      <c r="C100" t="s">
-        <v>112</v>
-      </c>
-      <c r="D100" t="s">
-        <v>112</v>
+      <c r="B100">
+        <v>401077.35</v>
+      </c>
+      <c r="C100">
+        <v>217012.85</v>
+      </c>
+      <c r="D100">
+        <v>156208.84</v>
       </c>
       <c r="E100">
         <v>126214.43</v>
@@ -3081,14 +3069,14 @@
       <c r="A101" t="s">
         <v>102</v>
       </c>
-      <c r="B101" t="s">
-        <v>112</v>
-      </c>
-      <c r="C101" t="s">
-        <v>112</v>
-      </c>
-      <c r="D101" t="s">
-        <v>112</v>
+      <c r="B101">
+        <v>420176.28</v>
+      </c>
+      <c r="C101">
+        <v>227346.79</v>
+      </c>
+      <c r="D101">
+        <v>163647.35999999999</v>
       </c>
       <c r="E101">
         <v>132224.64000000001</v>
@@ -3104,14 +3092,14 @@
       <c r="A102" t="s">
         <v>103</v>
       </c>
-      <c r="B102" t="s">
-        <v>112</v>
-      </c>
-      <c r="C102" t="s">
-        <v>112</v>
-      </c>
-      <c r="D102" t="s">
-        <v>112</v>
+      <c r="B102">
+        <v>439275.2</v>
+      </c>
+      <c r="C102">
+        <v>237680.74</v>
+      </c>
+      <c r="D102">
+        <v>171085.88</v>
       </c>
       <c r="E102">
         <v>138234.85999999999</v>
@@ -3127,14 +3115,14 @@
       <c r="A103" t="s">
         <v>104</v>
       </c>
-      <c r="B103" t="s">
-        <v>112</v>
-      </c>
-      <c r="C103" t="s">
-        <v>112</v>
-      </c>
-      <c r="D103" t="s">
-        <v>112</v>
+      <c r="B103">
+        <v>458374.12</v>
+      </c>
+      <c r="C103">
+        <v>248014.68</v>
+      </c>
+      <c r="D103">
+        <v>178524.39</v>
       </c>
       <c r="E103">
         <v>144245.07</v>
@@ -3150,14 +3138,14 @@
       <c r="A104" t="s">
         <v>105</v>
       </c>
-      <c r="B104" t="s">
-        <v>112</v>
-      </c>
-      <c r="C104" t="s">
-        <v>112</v>
-      </c>
-      <c r="D104" t="s">
-        <v>112</v>
+      <c r="B104">
+        <v>477473.04</v>
+      </c>
+      <c r="C104">
+        <v>258348.63</v>
+      </c>
+      <c r="D104">
+        <v>15962.91</v>
       </c>
       <c r="E104">
         <v>150255.28</v>
@@ -3173,14 +3161,14 @@
       <c r="A105" t="s">
         <v>106</v>
       </c>
-      <c r="B105" t="s">
-        <v>112</v>
-      </c>
-      <c r="C105" t="s">
-        <v>112</v>
-      </c>
-      <c r="D105" t="s">
-        <v>112</v>
+      <c r="B105">
+        <v>496571.96</v>
+      </c>
+      <c r="C105">
+        <v>268682.57</v>
+      </c>
+      <c r="D105">
+        <v>193401.43</v>
       </c>
       <c r="E105">
         <v>156265.49</v>
@@ -3196,14 +3184,14 @@
       <c r="A106" t="s">
         <v>107</v>
       </c>
-      <c r="B106" t="s">
-        <v>112</v>
-      </c>
-      <c r="C106" t="s">
-        <v>112</v>
-      </c>
-      <c r="D106" t="s">
-        <v>112</v>
+      <c r="B106">
+        <v>515670.88</v>
+      </c>
+      <c r="C106">
+        <v>279016.52</v>
+      </c>
+      <c r="D106">
+        <v>200839.94</v>
       </c>
       <c r="E106">
         <v>162275.70000000001</v>
@@ -3219,14 +3207,14 @@
       <c r="A107" t="s">
         <v>108</v>
       </c>
-      <c r="B107" t="s">
-        <v>112</v>
-      </c>
-      <c r="C107" t="s">
-        <v>112</v>
-      </c>
-      <c r="D107" t="s">
-        <v>112</v>
+      <c r="B107">
+        <v>534769.81000000006</v>
+      </c>
+      <c r="C107">
+        <v>289350.46000000002</v>
+      </c>
+      <c r="D107">
+        <v>208278.46</v>
       </c>
       <c r="E107">
         <v>168285.91</v>
@@ -3242,14 +3230,14 @@
       <c r="A108" t="s">
         <v>109</v>
       </c>
-      <c r="B108" t="s">
-        <v>112</v>
-      </c>
-      <c r="C108" t="s">
-        <v>112</v>
-      </c>
-      <c r="D108" t="s">
-        <v>112</v>
+      <c r="B108">
+        <v>553868.73</v>
+      </c>
+      <c r="C108">
+        <v>299684.40999999997</v>
+      </c>
+      <c r="D108">
+        <v>215716.98</v>
       </c>
       <c r="E108">
         <v>174296.12</v>
@@ -3265,14 +3253,14 @@
       <c r="A109" t="s">
         <v>110</v>
       </c>
-      <c r="B109" t="s">
-        <v>112</v>
-      </c>
-      <c r="C109" t="s">
-        <v>112</v>
-      </c>
-      <c r="D109" t="s">
-        <v>112</v>
+      <c r="B109">
+        <v>572967.65</v>
+      </c>
+      <c r="C109">
+        <v>310018.34999999998</v>
+      </c>
+      <c r="D109">
+        <v>223155.49</v>
       </c>
       <c r="E109">
         <v>180306.33</v>

--- a/grilla.xlsx
+++ b/grilla.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aetch\Desktop\proyecto_aamas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{34180D95-C8A3-4354-809E-62C986C24B74}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4DE27F61-7258-43A2-A4A4-C261772700A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1125" yWindow="1125" windowWidth="21600" windowHeight="11385" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1815" yWindow="1815" windowWidth="21600" windowHeight="11385" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Grilla" sheetId="1" r:id="rId1"/>
@@ -854,7 +854,7 @@
         <v>4619.7</v>
       </c>
       <c r="G4">
-        <v>3960.94</v>
+        <v>3960.51</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
@@ -877,7 +877,7 @@
         <v>5543.64</v>
       </c>
       <c r="G5">
-        <v>4753.12</v>
+        <v>4752.62</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
@@ -900,7 +900,7 @@
         <v>6467.58</v>
       </c>
       <c r="G6">
-        <v>5545.3</v>
+        <v>5544.72</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
@@ -923,7 +923,7 @@
         <v>7391.51</v>
       </c>
       <c r="G7">
-        <v>6337.49</v>
+        <v>6336.82</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
@@ -946,7 +946,7 @@
         <v>8315.4500000000007</v>
       </c>
       <c r="G8">
-        <v>7129.68</v>
+        <v>7128.92</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
@@ -992,7 +992,7 @@
         <v>10163.33</v>
       </c>
       <c r="G10">
-        <v>8714.0499999999993</v>
+        <v>8713.1299999999992</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
@@ -1015,7 +1015,7 @@
         <v>11087.27</v>
       </c>
       <c r="G11">
-        <v>9506.24</v>
+        <v>9505.23</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
@@ -1038,7 +1038,7 @@
         <v>12011.21</v>
       </c>
       <c r="G12">
-        <v>10298.42</v>
+        <v>10297.33</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
@@ -1061,7 +1061,7 @@
         <v>12935.15</v>
       </c>
       <c r="G13">
-        <v>11090.61</v>
+        <v>11089.44</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
@@ -1107,7 +1107,7 @@
         <v>14783.03</v>
       </c>
       <c r="G15">
-        <v>12674.99</v>
+        <v>12673.64</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
@@ -1130,7 +1130,7 @@
         <v>15706.87</v>
       </c>
       <c r="G16">
-        <v>13467.17</v>
+        <v>13465.74</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
@@ -1153,7 +1153,7 @@
         <v>16630.91</v>
       </c>
       <c r="G17">
-        <v>14259.36</v>
+        <v>14257.85</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
@@ -1176,7 +1176,7 @@
         <v>17554.849999999999</v>
       </c>
       <c r="G18">
-        <v>15051.54</v>
+        <v>15049.95</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
@@ -1222,7 +1222,7 @@
         <v>19402.73</v>
       </c>
       <c r="G20">
-        <v>16635.91</v>
+        <v>16634.150000000001</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
@@ -1245,7 +1245,7 @@
         <v>20326.669999999998</v>
       </c>
       <c r="G21">
-        <v>17428.099999999999</v>
+        <v>17426.259999999998</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
@@ -1268,7 +1268,7 @@
         <v>21250.6</v>
       </c>
       <c r="G22">
-        <v>18220.29</v>
+        <v>18218.36</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
@@ -1291,7 +1291,7 @@
         <v>22174.54</v>
       </c>
       <c r="G23">
-        <v>19021.47</v>
+        <v>19010.46</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
@@ -1337,7 +1337,7 @@
         <v>24022.42</v>
       </c>
       <c r="G25">
-        <v>20596.849999999999</v>
+        <v>20594.669999999998</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.25">
@@ -1360,7 +1360,7 @@
         <v>24946.36</v>
       </c>
       <c r="G26">
-        <v>31389.040000000001</v>
+        <v>21386.77</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.25">
@@ -1383,7 +1383,7 @@
         <v>25870.3</v>
       </c>
       <c r="G27">
-        <v>22181.22</v>
+        <v>22178.87</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.25">
@@ -1406,7 +1406,7 @@
         <v>26794.240000000002</v>
       </c>
       <c r="G28">
-        <v>22973.41</v>
+        <v>22970.98</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.25">
@@ -1452,7 +1452,7 @@
         <v>28642.12</v>
       </c>
       <c r="G30">
-        <v>24557.78</v>
+        <v>24555.18</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
@@ -1475,7 +1475,7 @@
         <v>29566.06</v>
       </c>
       <c r="G31">
-        <v>25349.96</v>
+        <v>25347.279999999999</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.25">
@@ -1498,7 +1498,7 @@
         <v>30490</v>
       </c>
       <c r="G32">
-        <v>26142.15</v>
+        <v>26139.39</v>
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.25">
@@ -1521,7 +1521,7 @@
         <v>31413.94</v>
       </c>
       <c r="G33">
-        <v>26934.34</v>
+        <v>26931.49</v>
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.25">
@@ -1567,7 +1567,7 @@
         <v>33261.82</v>
       </c>
       <c r="G35">
-        <v>28518.71</v>
+        <v>28515.69</v>
       </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.25">
@@ -1590,7 +1590,7 @@
         <v>34185.760000000002</v>
       </c>
       <c r="G36">
-        <v>29310.9</v>
+        <v>29307.8</v>
       </c>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.25">
@@ -1613,7 +1613,7 @@
         <v>35109.69</v>
       </c>
       <c r="G37">
-        <v>30103.09</v>
+        <v>30099.9</v>
       </c>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.25">
@@ -1636,7 +1636,7 @@
         <v>36033.629999999997</v>
       </c>
       <c r="G38">
-        <v>30895.27</v>
+        <v>30892</v>
       </c>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.25">
@@ -1682,7 +1682,7 @@
         <v>37881.51</v>
       </c>
       <c r="G40">
-        <v>32479.65</v>
+        <v>32476.21</v>
       </c>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.25">
@@ -1705,7 +1705,7 @@
         <v>38805.449999999997</v>
       </c>
       <c r="G41">
-        <v>33271.83</v>
+        <v>33268.31</v>
       </c>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.25">
@@ -1728,7 +1728,7 @@
         <v>39729.39</v>
       </c>
       <c r="G42">
-        <v>34064.019999999997</v>
+        <v>34060.410000000003</v>
       </c>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.25">
@@ -1751,7 +1751,7 @@
         <v>40653.33</v>
       </c>
       <c r="G43">
-        <v>34856.199999999997</v>
+        <v>34852.51</v>
       </c>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.25">
@@ -1797,7 +1797,7 @@
         <v>42501.21</v>
       </c>
       <c r="G45">
-        <v>36440.57</v>
+        <v>36436.720000000001</v>
       </c>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.25">
@@ -1820,7 +1820,7 @@
         <v>43425.15</v>
       </c>
       <c r="G46">
-        <v>37232.76</v>
+        <v>37228.82</v>
       </c>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.25">
@@ -1843,7 +1843,7 @@
         <v>44349.09</v>
       </c>
       <c r="G47">
-        <v>38024.949999999997</v>
+        <v>38020.92</v>
       </c>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.25">
@@ -1866,7 +1866,7 @@
         <v>45273.03</v>
       </c>
       <c r="G48">
-        <v>38817.14</v>
+        <v>38813.03</v>
       </c>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.25">
@@ -1912,7 +1912,7 @@
         <v>47120.91</v>
       </c>
       <c r="G50">
-        <v>40401.51</v>
+        <v>40397.230000000003</v>
       </c>
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.25">
@@ -1935,7 +1935,7 @@
         <v>48044.85</v>
       </c>
       <c r="G51">
-        <v>41193.699999999997</v>
+        <v>41189.33</v>
       </c>
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.25">
@@ -1958,7 +1958,7 @@
         <v>48968.78</v>
       </c>
       <c r="G52">
-        <v>41985.88</v>
+        <v>41981.440000000002</v>
       </c>
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.25">
@@ -1981,7 +1981,7 @@
         <v>49892.72</v>
       </c>
       <c r="G53">
-        <v>42778.07</v>
+        <v>42773.54</v>
       </c>
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.25">
@@ -2027,7 +2027,7 @@
         <v>51740.6</v>
       </c>
       <c r="G55">
-        <v>44362.45</v>
+        <v>44357.75</v>
       </c>
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.25">
@@ -2050,7 +2050,7 @@
         <v>52664.54</v>
       </c>
       <c r="G56">
-        <v>45154.62</v>
+        <v>45149.85</v>
       </c>
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.25">
@@ -2073,7 +2073,7 @@
         <v>53588.480000000003</v>
       </c>
       <c r="G57">
-        <v>45946.81</v>
+        <v>45941.95</v>
       </c>
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.25">
@@ -2096,7 +2096,7 @@
         <v>54512.42</v>
       </c>
       <c r="G58">
-        <v>46739</v>
+        <v>46734.05</v>
       </c>
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.25">
@@ -2142,7 +2142,7 @@
         <v>56360.3</v>
       </c>
       <c r="G60">
-        <v>48323.37</v>
+        <v>48318.26</v>
       </c>
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.25">
@@ -2165,7 +2165,7 @@
         <v>57284.24</v>
       </c>
       <c r="G61">
-        <v>49115.56</v>
+        <v>49110.36</v>
       </c>
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.25">
@@ -2188,7 +2188,7 @@
         <v>58208.18</v>
       </c>
       <c r="G62">
-        <v>49907.75</v>
+        <v>49902.46</v>
       </c>
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.25">
@@ -2211,7 +2211,7 @@
         <v>59132.12</v>
       </c>
       <c r="G63">
-        <v>50699.93</v>
+        <v>50694.57</v>
       </c>
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.25">
@@ -2257,7 +2257,7 @@
         <v>60980</v>
       </c>
       <c r="G65">
-        <v>52284.31</v>
+        <v>52278.77</v>
       </c>
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.25">
@@ -2280,7 +2280,7 @@
         <v>61903.94</v>
       </c>
       <c r="G66">
-        <v>53076.5</v>
+        <v>53070.87</v>
       </c>
     </row>
     <row r="67" spans="1:7" x14ac:dyDescent="0.25">
@@ -2303,7 +2303,7 @@
         <v>62827.87</v>
       </c>
       <c r="G67">
-        <v>53868.68</v>
+        <v>53862.98</v>
       </c>
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.25">
@@ -2326,7 +2326,7 @@
         <v>63751.81</v>
       </c>
       <c r="G68">
-        <v>54660.86</v>
+        <v>54655.08</v>
       </c>
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.25">
@@ -2349,7 +2349,7 @@
         <v>64675.75</v>
       </c>
       <c r="G69">
-        <v>55453.05</v>
+        <v>55447.18</v>
       </c>
     </row>
     <row r="70" spans="1:7" x14ac:dyDescent="0.25">
@@ -2372,7 +2372,7 @@
         <v>65599.69</v>
       </c>
       <c r="G70">
-        <v>56245.23</v>
+        <v>56239.28</v>
       </c>
     </row>
     <row r="71" spans="1:7" x14ac:dyDescent="0.25">
@@ -2395,7 +2395,7 @@
         <v>66523.63</v>
       </c>
       <c r="G71">
-        <v>57037.42</v>
+        <v>57031.39</v>
       </c>
     </row>
     <row r="72" spans="1:7" x14ac:dyDescent="0.25">
@@ -2418,7 +2418,7 @@
         <v>67447.570000000007</v>
       </c>
       <c r="G72">
-        <v>57829.61</v>
+        <v>57823.49</v>
       </c>
     </row>
     <row r="73" spans="1:7" x14ac:dyDescent="0.25">
@@ -2441,7 +2441,7 @@
         <v>68371.509999999995</v>
       </c>
       <c r="G73">
-        <v>58621.8</v>
+        <v>58615.59</v>
       </c>
     </row>
     <row r="74" spans="1:7" x14ac:dyDescent="0.25">
@@ -2464,7 +2464,7 @@
         <v>69295.45</v>
       </c>
       <c r="G74">
-        <v>59413.98</v>
+        <v>59407.69</v>
       </c>
     </row>
     <row r="75" spans="1:7" x14ac:dyDescent="0.25">
@@ -2487,7 +2487,7 @@
         <v>70219.39</v>
       </c>
       <c r="G75">
-        <v>60206.17</v>
+        <v>60199.8</v>
       </c>
     </row>
     <row r="76" spans="1:7" x14ac:dyDescent="0.25">
@@ -2510,7 +2510,7 @@
         <v>71143.33</v>
       </c>
       <c r="G76">
-        <v>60998.36</v>
+        <v>60991.9</v>
       </c>
     </row>
     <row r="77" spans="1:7" x14ac:dyDescent="0.25">
@@ -2533,7 +2533,7 @@
         <v>72067.27</v>
       </c>
       <c r="G77">
-        <v>61790.55</v>
+        <v>61784</v>
       </c>
     </row>
     <row r="78" spans="1:7" x14ac:dyDescent="0.25">
@@ -2556,7 +2556,7 @@
         <v>72991.210000000006</v>
       </c>
       <c r="G78">
-        <v>62582.73</v>
+        <v>62576.1</v>
       </c>
     </row>
     <row r="79" spans="1:7" x14ac:dyDescent="0.25">
@@ -2579,7 +2579,7 @@
         <v>73915.149999999994</v>
       </c>
       <c r="G79">
-        <v>63374.92</v>
+        <v>63368.21</v>
       </c>
     </row>
     <row r="80" spans="1:7" x14ac:dyDescent="0.25">
@@ -2602,7 +2602,7 @@
         <v>74839.09</v>
       </c>
       <c r="G80">
-        <v>64167.11</v>
+        <v>64160.31</v>
       </c>
     </row>
     <row r="81" spans="1:7" x14ac:dyDescent="0.25">
@@ -2625,7 +2625,7 @@
         <v>75763.03</v>
       </c>
       <c r="G81">
-        <v>64959.28</v>
+        <v>64952.41</v>
       </c>
     </row>
     <row r="82" spans="1:7" x14ac:dyDescent="0.25">
@@ -2648,7 +2648,7 @@
         <v>76686.960000000006</v>
       </c>
       <c r="G82">
-        <v>65751.47</v>
+        <v>65744.52</v>
       </c>
     </row>
     <row r="83" spans="1:7" x14ac:dyDescent="0.25">
@@ -2671,7 +2671,7 @@
         <v>77610.899999999994</v>
       </c>
       <c r="G83">
-        <v>66543.66</v>
+        <v>66536.62</v>
       </c>
     </row>
     <row r="84" spans="1:7" x14ac:dyDescent="0.25">
@@ -2694,7 +2694,7 @@
         <v>78534.84</v>
       </c>
       <c r="G84">
-        <v>67335.850000000006</v>
+        <v>67328.72</v>
       </c>
     </row>
     <row r="85" spans="1:7" x14ac:dyDescent="0.25">
@@ -2717,7 +2717,7 @@
         <v>79458.78</v>
       </c>
       <c r="G85">
-        <v>68128.03</v>
+        <v>68120.820000000007</v>
       </c>
     </row>
     <row r="86" spans="1:7" x14ac:dyDescent="0.25">
@@ -2740,7 +2740,7 @@
         <v>80382.720000000001</v>
       </c>
       <c r="G86">
-        <v>68920.22</v>
+        <v>68912.929999999993</v>
       </c>
     </row>
     <row r="87" spans="1:7" x14ac:dyDescent="0.25">
@@ -2763,7 +2763,7 @@
         <v>81306.66</v>
       </c>
       <c r="G87">
-        <v>69712.41</v>
+        <v>69705.03</v>
       </c>
     </row>
     <row r="88" spans="1:7" x14ac:dyDescent="0.25">
@@ -2786,7 +2786,7 @@
         <v>82230.600000000006</v>
       </c>
       <c r="G88">
-        <v>70504.59</v>
+        <v>70497.13</v>
       </c>
     </row>
     <row r="89" spans="1:7" x14ac:dyDescent="0.25">
@@ -2809,7 +2809,7 @@
         <v>83154.539999999994</v>
       </c>
       <c r="G89">
-        <v>71296.78</v>
+        <v>71289.23</v>
       </c>
     </row>
     <row r="90" spans="1:7" x14ac:dyDescent="0.25">
@@ -2832,7 +2832,7 @@
         <v>84078.48</v>
       </c>
       <c r="G90">
-        <v>72088.97</v>
+        <v>72081.34</v>
       </c>
     </row>
     <row r="91" spans="1:7" x14ac:dyDescent="0.25">
@@ -2855,7 +2855,7 @@
         <v>85002.42</v>
       </c>
       <c r="G91">
-        <v>72881.16</v>
+        <v>72873.440000000002</v>
       </c>
     </row>
     <row r="92" spans="1:7" x14ac:dyDescent="0.25">
@@ -2878,7 +2878,7 @@
         <v>85926.36</v>
       </c>
       <c r="G92">
-        <v>73673.34</v>
+        <v>73665.539999999994</v>
       </c>
     </row>
     <row r="93" spans="1:7" x14ac:dyDescent="0.25">
@@ -2901,7 +2901,7 @@
         <v>86850.3</v>
       </c>
       <c r="G93">
-        <v>74465.52</v>
+        <v>74457.64</v>
       </c>
     </row>
     <row r="94" spans="1:7" x14ac:dyDescent="0.25">
@@ -2924,7 +2924,7 @@
         <v>87774.24</v>
       </c>
       <c r="G94">
-        <v>75257.710000000006</v>
+        <v>75249.75</v>
       </c>
     </row>
     <row r="95" spans="1:7" x14ac:dyDescent="0.25">
@@ -2947,7 +2947,7 @@
         <v>88698.18</v>
       </c>
       <c r="G95">
-        <v>76049.899999999994</v>
+        <v>76041.850000000006</v>
       </c>
     </row>
     <row r="96" spans="1:7" x14ac:dyDescent="0.25">
@@ -2970,7 +2970,7 @@
         <v>89622.12</v>
       </c>
       <c r="G96">
-        <v>76842.080000000002</v>
+        <v>76833.95</v>
       </c>
     </row>
     <row r="97" spans="1:7" x14ac:dyDescent="0.25">
@@ -2993,7 +2993,7 @@
         <v>90546.05</v>
       </c>
       <c r="G97">
-        <v>77634.27</v>
+        <v>77626.05</v>
       </c>
     </row>
     <row r="98" spans="1:7" x14ac:dyDescent="0.25">
@@ -3016,7 +3016,7 @@
         <v>91469.99</v>
       </c>
       <c r="G98">
-        <v>78426.460000000006</v>
+        <v>78418.16</v>
       </c>
     </row>
     <row r="99" spans="1:7" x14ac:dyDescent="0.25">
@@ -3039,7 +3039,7 @@
         <v>92393.93</v>
       </c>
       <c r="G99">
-        <v>79218.64</v>
+        <v>79210.259999999995</v>
       </c>
     </row>
     <row r="100" spans="1:7" x14ac:dyDescent="0.25">
@@ -3062,7 +3062,7 @@
         <v>97013.63</v>
       </c>
       <c r="G100">
-        <v>83179.58</v>
+        <v>83170.77</v>
       </c>
     </row>
     <row r="101" spans="1:7" x14ac:dyDescent="0.25">
@@ -3085,7 +3085,7 @@
         <v>101633.33</v>
       </c>
       <c r="G101">
-        <v>87140.58</v>
+        <v>87131.29</v>
       </c>
     </row>
     <row r="102" spans="1:7" x14ac:dyDescent="0.25">
@@ -3108,7 +3108,7 @@
         <v>106253.02</v>
       </c>
       <c r="G102">
-        <v>91101.440000000002</v>
+        <v>91091.8</v>
       </c>
     </row>
     <row r="103" spans="1:7" x14ac:dyDescent="0.25">
@@ -3131,7 +3131,7 @@
         <v>110872.72</v>
       </c>
       <c r="G103">
-        <v>95062.37</v>
+        <v>95052.31</v>
       </c>
     </row>
     <row r="104" spans="1:7" x14ac:dyDescent="0.25">
@@ -3154,7 +3154,7 @@
         <v>115492.42</v>
       </c>
       <c r="G104">
-        <v>99023.31</v>
+        <v>99012.82</v>
       </c>
     </row>
     <row r="105" spans="1:7" x14ac:dyDescent="0.25">
@@ -3177,7 +3177,7 @@
         <v>120112.11</v>
       </c>
       <c r="G105">
-        <v>102984.24</v>
+        <v>102973.34</v>
       </c>
     </row>
     <row r="106" spans="1:7" x14ac:dyDescent="0.25">
@@ -3200,7 +3200,7 @@
         <v>124731.81</v>
       </c>
       <c r="G106">
-        <v>106945.17</v>
+        <v>106933.85</v>
       </c>
     </row>
     <row r="107" spans="1:7" x14ac:dyDescent="0.25">
@@ -3223,7 +3223,7 @@
         <v>129351.51</v>
       </c>
       <c r="G107">
-        <v>110906.1</v>
+        <v>110894.36</v>
       </c>
     </row>
     <row r="108" spans="1:7" x14ac:dyDescent="0.25">
@@ -3246,7 +3246,7 @@
         <v>133971.20000000001</v>
       </c>
       <c r="G108">
-        <v>114867.03</v>
+        <v>114854.88</v>
       </c>
     </row>
     <row r="109" spans="1:7" x14ac:dyDescent="0.25">
@@ -3269,7 +3269,7 @@
         <v>138590.9</v>
       </c>
       <c r="G109">
-        <v>118827.97</v>
+        <v>118815.39</v>
       </c>
     </row>
   </sheetData>

--- a/grilla.xlsx
+++ b/grilla.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aetch\Desktop\proyecto_aamas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4DE27F61-7258-43A2-A4A4-C261772700A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A2568CB1-3AAC-4549-B43D-E74039BF1FF1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1815" yWindow="1815" windowWidth="21600" windowHeight="11385" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="285" yWindow="2310" windowWidth="14475" windowHeight="11385" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Grilla" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="115">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="117">
   <si>
     <t>Cuotas12</t>
   </si>
@@ -379,6 +379,12 @@
   </si>
   <si>
     <t>Cuotas3</t>
+  </si>
+  <si>
+    <t>1550000.00</t>
+  </si>
+  <si>
+    <t>1600000.00</t>
   </si>
 </sst>
 </file>
@@ -757,7 +763,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G109"/>
+  <dimension ref="A1:G111"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="13.875" customWidth="1"/>
@@ -3272,6 +3278,52 @@
         <v>118815.39</v>
       </c>
     </row>
+    <row r="110" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A110" t="s">
+        <v>115</v>
+      </c>
+      <c r="B110" s="2">
+        <v>592066.56999999995</v>
+      </c>
+      <c r="C110" s="2">
+        <v>320352.3</v>
+      </c>
+      <c r="D110" s="2">
+        <v>230594.01</v>
+      </c>
+      <c r="E110">
+        <v>186316.54</v>
+      </c>
+      <c r="F110">
+        <v>143210.6</v>
+      </c>
+      <c r="G110">
+        <v>122775.9</v>
+      </c>
+    </row>
+    <row r="111" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A111" t="s">
+        <v>116</v>
+      </c>
+      <c r="B111" s="2">
+        <v>611165.49</v>
+      </c>
+      <c r="C111" s="2">
+        <v>330686.24</v>
+      </c>
+      <c r="D111" s="2">
+        <v>238032.53</v>
+      </c>
+      <c r="E111">
+        <v>192326.76</v>
+      </c>
+      <c r="F111">
+        <v>147830.29</v>
+      </c>
+      <c r="G111">
+        <v>126736.42</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/grilla.xlsx
+++ b/grilla.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aetch\Desktop\proyecto_aamas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A2568CB1-3AAC-4549-B43D-E74039BF1FF1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4602D88F-AF4D-428D-AA27-43D5954DC9B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="285" yWindow="2310" windowWidth="14475" windowHeight="11385" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="90" yWindow="2100" windowWidth="14475" windowHeight="11385" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Grilla" sheetId="1" r:id="rId1"/>
@@ -3151,7 +3151,7 @@
         <v>258348.63</v>
       </c>
       <c r="D104">
-        <v>15962.91</v>
+        <v>185962.91</v>
       </c>
       <c r="E104">
         <v>150255.28</v>

--- a/grilla.xlsx
+++ b/grilla.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aetch\Desktop\proyecto_aamas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4602D88F-AF4D-428D-AA27-43D5954DC9B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C8DEB0B3-B778-41E2-ACB3-C3392F5D2743}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="90" yWindow="2100" windowWidth="14475" windowHeight="11385" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/grilla.xlsx
+++ b/grilla.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aetch\Desktop\proyecto_aamas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C8DEB0B3-B778-41E2-ACB3-C3392F5D2743}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{208DF7E0-118C-4694-BE52-4EC829B00D55}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="90" yWindow="2100" windowWidth="14475" windowHeight="11385" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="5955" yWindow="5250" windowWidth="21600" windowHeight="11385" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Grilla" sheetId="1" r:id="rId1"/>
@@ -799,22 +799,22 @@
         <v>3</v>
       </c>
       <c r="B2">
-        <v>11459.35</v>
+        <v>11399.23</v>
       </c>
       <c r="C2">
-        <v>6200.37</v>
+        <v>6149.7</v>
       </c>
       <c r="D2">
-        <v>4463.1099999999997</v>
+        <v>4414.38</v>
       </c>
       <c r="E2">
-        <v>3606.13</v>
+        <v>3557.47</v>
       </c>
       <c r="F2">
-        <v>2771.82</v>
+        <v>2721.54</v>
       </c>
       <c r="G2">
-        <v>2376.56</v>
+        <v>2323.6799999999998</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
@@ -822,22 +822,22 @@
         <v>4</v>
       </c>
       <c r="B3">
-        <v>15279.14</v>
+        <v>15198.97</v>
       </c>
       <c r="C3">
-        <v>8267.16</v>
+        <v>8199.6</v>
       </c>
       <c r="D3">
-        <v>5950.81</v>
+        <v>5885.83</v>
       </c>
       <c r="E3">
-        <v>4808.17</v>
+        <v>4743.29</v>
       </c>
       <c r="F3">
-        <v>3695.76</v>
+        <v>3628.72</v>
       </c>
       <c r="G3">
-        <v>3168.75</v>
+        <v>3098.24</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
@@ -845,22 +845,22 @@
         <v>5</v>
       </c>
       <c r="B4">
-        <v>19098.919999999998</v>
+        <v>18998.71</v>
       </c>
       <c r="C4">
-        <v>10333.950000000001</v>
+        <v>10249.5</v>
       </c>
       <c r="D4">
-        <v>7438.52</v>
+        <v>7357.29</v>
       </c>
       <c r="E4">
-        <v>6010.21</v>
+        <v>5929.11</v>
       </c>
       <c r="F4">
-        <v>4619.7</v>
+        <v>4535.91</v>
       </c>
       <c r="G4">
-        <v>3960.51</v>
+        <v>3872.8</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
@@ -868,22 +868,22 @@
         <v>6</v>
       </c>
       <c r="B5">
-        <v>22918.71</v>
+        <v>22798.45</v>
       </c>
       <c r="C5">
-        <v>12400.73</v>
+        <v>12299.4</v>
       </c>
       <c r="D5">
-        <v>8926.2199999999993</v>
+        <v>8828.75</v>
       </c>
       <c r="E5">
-        <v>7212.25</v>
+        <v>7114.94</v>
       </c>
       <c r="F5">
-        <v>5543.64</v>
+        <v>5443.09</v>
       </c>
       <c r="G5">
-        <v>4752.62</v>
+        <v>4647.3599999999997</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
@@ -891,22 +891,22 @@
         <v>7</v>
       </c>
       <c r="B6">
-        <v>26738.49</v>
+        <v>26598.19</v>
       </c>
       <c r="C6">
-        <v>14467.52</v>
+        <v>14349.3</v>
       </c>
       <c r="D6">
-        <v>10413.92</v>
+        <v>10300.209999999999</v>
       </c>
       <c r="E6">
-        <v>8414.2999999999993</v>
+        <v>8300.76</v>
       </c>
       <c r="F6">
-        <v>6467.58</v>
+        <v>6350.27</v>
       </c>
       <c r="G6">
-        <v>5544.72</v>
+        <v>5421.92</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
@@ -914,22 +914,22 @@
         <v>8</v>
       </c>
       <c r="B7">
-        <v>30558.27</v>
+        <v>30397.93</v>
       </c>
       <c r="C7">
-        <v>16534.310000000001</v>
+        <v>16399.2</v>
       </c>
       <c r="D7">
-        <v>11901.63</v>
+        <v>11771.67</v>
       </c>
       <c r="E7">
-        <v>9616.64</v>
+        <v>9486.58</v>
       </c>
       <c r="F7" s="1">
-        <v>7391.51</v>
+        <v>7257.45</v>
       </c>
       <c r="G7">
-        <v>6336.82</v>
+        <v>6196.48</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
@@ -937,22 +937,22 @@
         <v>9</v>
       </c>
       <c r="B8">
-        <v>34378.06</v>
+        <v>34197.68</v>
       </c>
       <c r="C8">
-        <v>18601.099999999999</v>
+        <v>18449.099999999999</v>
       </c>
       <c r="D8">
-        <v>13389.33</v>
+        <v>13243.13</v>
       </c>
       <c r="E8">
-        <v>10818.38</v>
+        <v>10672.41</v>
       </c>
       <c r="F8">
-        <v>8315.4500000000007</v>
+        <v>8164.63</v>
       </c>
       <c r="G8">
-        <v>7128.92</v>
+        <v>6971.04</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
@@ -960,22 +960,22 @@
         <v>10</v>
       </c>
       <c r="B9">
-        <v>38197.839999999997</v>
+        <v>37997.42</v>
       </c>
       <c r="C9">
-        <v>20667.89</v>
+        <v>20499</v>
       </c>
       <c r="D9">
-        <v>14877.03</v>
+        <v>14714.59</v>
       </c>
       <c r="E9">
-        <v>12020.42</v>
+        <v>11858.23</v>
       </c>
       <c r="F9">
-        <v>9239.39</v>
+        <v>9071.81</v>
       </c>
       <c r="G9">
-        <v>7921.03</v>
+        <v>7745.6</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
@@ -983,22 +983,22 @@
         <v>11</v>
       </c>
       <c r="B10">
-        <v>42017.63</v>
+        <v>41797.160000000003</v>
       </c>
       <c r="C10">
-        <v>22734.68</v>
+        <v>22548.9</v>
       </c>
       <c r="D10">
-        <v>16364.74</v>
+        <v>16186.05</v>
       </c>
       <c r="E10">
-        <v>13222.46</v>
+        <v>13044.05</v>
       </c>
       <c r="F10">
-        <v>10163.33</v>
+        <v>9978.99</v>
       </c>
       <c r="G10">
-        <v>8713.1299999999992</v>
+        <v>8520.16</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
@@ -1006,22 +1006,22 @@
         <v>12</v>
       </c>
       <c r="B11">
-        <v>45833.97</v>
+        <v>45596.9</v>
       </c>
       <c r="C11">
-        <v>24801.47</v>
+        <v>24598.799999999999</v>
       </c>
       <c r="D11">
-        <v>17852.439999999999</v>
+        <v>17657.5</v>
       </c>
       <c r="E11">
-        <v>14424.51</v>
+        <v>14229.88</v>
       </c>
       <c r="F11">
-        <v>11087.27</v>
+        <v>10886.17</v>
       </c>
       <c r="G11">
-        <v>9505.23</v>
+        <v>9294.7199999999993</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
@@ -1029,22 +1029,22 @@
         <v>13</v>
       </c>
       <c r="B12">
-        <v>49657.2</v>
+        <v>49396.639999999999</v>
       </c>
       <c r="C12">
-        <v>26868.26</v>
+        <v>26648.7</v>
       </c>
       <c r="D12">
-        <v>19340.14</v>
+        <v>19128.96</v>
       </c>
       <c r="E12">
-        <v>15626.55</v>
+        <v>15415.7</v>
       </c>
       <c r="F12">
-        <v>12011.21</v>
+        <v>11793.36</v>
       </c>
       <c r="G12">
-        <v>10297.33</v>
+        <v>10069.280000000001</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
@@ -1052,22 +1052,22 @@
         <v>14</v>
       </c>
       <c r="B13">
-        <v>53473.54</v>
+        <v>53196.38</v>
       </c>
       <c r="C13">
-        <v>28935.05</v>
+        <v>28698.6</v>
       </c>
       <c r="D13">
-        <v>20827.849999999999</v>
+        <v>20600.419999999998</v>
       </c>
       <c r="E13">
-        <v>16828.59</v>
+        <v>16601.52</v>
       </c>
       <c r="F13">
-        <v>12935.15</v>
+        <v>12700.54</v>
       </c>
       <c r="G13">
-        <v>11089.44</v>
+        <v>10843.84</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
@@ -1075,22 +1075,22 @@
         <v>15</v>
       </c>
       <c r="B14">
-        <v>57296.76</v>
+        <v>56996.13</v>
       </c>
       <c r="C14">
-        <v>31001.84</v>
+        <v>30748.5</v>
       </c>
       <c r="D14">
-        <v>22315.55</v>
+        <v>22071.88</v>
       </c>
       <c r="E14">
-        <v>18030.63</v>
+        <v>17787.34</v>
       </c>
       <c r="F14">
-        <v>13859.09</v>
+        <v>13607.72</v>
       </c>
       <c r="G14">
-        <v>11881.54</v>
+        <v>11618.4</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
@@ -1098,22 +1098,22 @@
         <v>16</v>
       </c>
       <c r="B15">
-        <v>61116.55</v>
+        <v>60795.87</v>
       </c>
       <c r="C15">
-        <v>33068.620000000003</v>
+        <v>32798.400000000001</v>
       </c>
       <c r="D15">
-        <v>23803.25</v>
+        <v>23543.34</v>
       </c>
       <c r="E15">
-        <v>19232.68</v>
+        <v>18973.169999999998</v>
       </c>
       <c r="F15">
-        <v>14783.03</v>
+        <v>14514.9</v>
       </c>
       <c r="G15">
-        <v>12673.64</v>
+        <v>12392.96</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
@@ -1121,22 +1121,22 @@
         <v>17</v>
       </c>
       <c r="B16">
-        <v>64936.33</v>
+        <v>64595.61</v>
       </c>
       <c r="C16">
-        <v>35135.410000000003</v>
+        <v>34848.29</v>
       </c>
       <c r="D16">
-        <v>25290.959999999999</v>
+        <v>25014.799999999999</v>
       </c>
       <c r="E16">
-        <v>20434.72</v>
+        <v>20158.990000000002</v>
       </c>
       <c r="F16">
-        <v>15706.87</v>
+        <v>15422.08</v>
       </c>
       <c r="G16">
-        <v>13465.74</v>
+        <v>13167.52</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
@@ -1144,22 +1144,22 @@
         <v>18</v>
       </c>
       <c r="B17">
-        <v>68756.12</v>
+        <v>68395.350000000006</v>
       </c>
       <c r="C17">
-        <v>37202.199999999997</v>
+        <v>36898.19</v>
       </c>
       <c r="D17">
-        <v>26778.66</v>
+        <v>26486.26</v>
       </c>
       <c r="E17">
-        <v>21636.76</v>
+        <v>21344.81</v>
       </c>
       <c r="F17">
-        <v>16630.91</v>
+        <v>16329.26</v>
       </c>
       <c r="G17">
-        <v>14257.85</v>
+        <v>13942.08</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
@@ -1167,22 +1167,22 @@
         <v>19</v>
       </c>
       <c r="B18">
-        <v>72575.899999999994</v>
+        <v>72195.09</v>
       </c>
       <c r="C18">
-        <v>39268.99</v>
+        <v>38948.089999999997</v>
       </c>
       <c r="D18">
-        <v>28266.36</v>
+        <v>27957.72</v>
       </c>
       <c r="E18">
-        <v>22838.799999999999</v>
+        <v>22530.639999999999</v>
       </c>
       <c r="F18">
-        <v>17554.849999999999</v>
+        <v>17236.439999999999</v>
       </c>
       <c r="G18">
-        <v>15049.95</v>
+        <v>14716.64</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
@@ -1190,22 +1190,22 @@
         <v>20</v>
       </c>
       <c r="B19">
-        <v>76395.69</v>
+        <v>75994.83</v>
       </c>
       <c r="C19">
-        <v>41335.78</v>
+        <v>40997.99</v>
       </c>
       <c r="D19">
-        <v>29754.07</v>
+        <v>29429.17</v>
       </c>
       <c r="E19">
-        <v>24040.84</v>
+        <v>23716.46</v>
       </c>
       <c r="F19">
-        <v>18478.79</v>
+        <v>18143.62</v>
       </c>
       <c r="G19">
-        <v>15842.05</v>
+        <v>15491.19</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
@@ -1213,22 +1213,22 @@
         <v>21</v>
       </c>
       <c r="B20">
-        <v>80215.47</v>
+        <v>79794.58</v>
       </c>
       <c r="C20">
-        <v>43402.57</v>
+        <v>43047.89</v>
       </c>
       <c r="D20">
-        <v>31241.77</v>
+        <v>30900.63</v>
       </c>
       <c r="E20">
-        <v>25242.89</v>
+        <v>24902.28</v>
       </c>
       <c r="F20">
-        <v>19402.73</v>
+        <v>19050.8</v>
       </c>
       <c r="G20">
-        <v>16634.150000000001</v>
+        <v>16265.75</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
@@ -1236,22 +1236,22 @@
         <v>22</v>
       </c>
       <c r="B21">
-        <v>84035.26</v>
+        <v>83594.320000000007</v>
       </c>
       <c r="C21">
-        <v>45469.36</v>
+        <v>45097.79</v>
       </c>
       <c r="D21">
-        <v>32729.47</v>
+        <v>32372.09</v>
       </c>
       <c r="E21">
-        <v>26444.93</v>
+        <v>26088.1</v>
       </c>
       <c r="F21">
-        <v>20326.669999999998</v>
+        <v>19957.990000000002</v>
       </c>
       <c r="G21">
-        <v>17426.259999999998</v>
+        <v>17040.310000000001</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
@@ -1259,22 +1259,22 @@
         <v>23</v>
       </c>
       <c r="B22">
-        <v>87855.039999999994</v>
+        <v>87394.06</v>
       </c>
       <c r="C22">
-        <v>47536.15</v>
+        <v>47147.69</v>
       </c>
       <c r="D22">
-        <v>34217.18</v>
+        <v>33843.550000000003</v>
       </c>
       <c r="E22">
-        <v>27646.97</v>
+        <v>27273.93</v>
       </c>
       <c r="F22">
-        <v>21250.6</v>
+        <v>20865.169999999998</v>
       </c>
       <c r="G22">
-        <v>18218.36</v>
+        <v>17814.87</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
@@ -1282,22 +1282,22 @@
         <v>24</v>
       </c>
       <c r="B23">
-        <v>91674.82</v>
+        <v>91193.8</v>
       </c>
       <c r="C23">
-        <v>49602.94</v>
+        <v>49197.59</v>
       </c>
       <c r="D23">
-        <v>35704.879999999997</v>
+        <v>35315.01</v>
       </c>
       <c r="E23">
-        <v>28848.01</v>
+        <v>28459.75</v>
       </c>
       <c r="F23">
-        <v>22174.54</v>
+        <v>21772.35</v>
       </c>
       <c r="G23">
-        <v>19010.46</v>
+        <v>18589.43</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
@@ -1305,22 +1305,22 @@
         <v>25</v>
       </c>
       <c r="B24">
-        <v>95494.61</v>
+        <v>94993.54</v>
       </c>
       <c r="C24">
-        <v>51669.73</v>
+        <v>51247.49</v>
       </c>
       <c r="D24">
-        <v>37192.58</v>
+        <v>36786.47</v>
       </c>
       <c r="E24">
-        <v>30051.06</v>
+        <v>29645.57</v>
       </c>
       <c r="F24">
-        <v>23098.48</v>
+        <v>22679.53</v>
       </c>
       <c r="G24">
-        <v>19802.560000000001</v>
+        <v>19363.990000000002</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.25">
@@ -1328,22 +1328,22 @@
         <v>26</v>
       </c>
       <c r="B25">
-        <v>99314.39</v>
+        <v>98793.29</v>
       </c>
       <c r="C25">
-        <v>53736.51</v>
+        <v>53297.39</v>
       </c>
       <c r="D25">
-        <v>38680.29</v>
+        <v>38257.93</v>
       </c>
       <c r="E25">
-        <v>31253.1</v>
+        <v>30831.4</v>
       </c>
       <c r="F25">
-        <v>24022.42</v>
+        <v>23586.71</v>
       </c>
       <c r="G25">
-        <v>20594.669999999998</v>
+        <v>20138.55</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.25">
@@ -1351,22 +1351,22 @@
         <v>27</v>
       </c>
       <c r="B26">
-        <v>103134.18</v>
+        <v>102593.03</v>
       </c>
       <c r="C26">
-        <v>55803.3</v>
+        <v>55347.29</v>
       </c>
       <c r="D26">
-        <v>40167.99</v>
+        <v>39729.379999999997</v>
       </c>
       <c r="E26">
-        <v>32455.14</v>
+        <v>32017.22</v>
       </c>
       <c r="F26">
-        <v>24946.36</v>
+        <v>24493.89</v>
       </c>
       <c r="G26">
-        <v>21386.77</v>
+        <v>20913.11</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.25">
@@ -1374,22 +1374,22 @@
         <v>28</v>
       </c>
       <c r="B27">
-        <v>106953.96</v>
+        <v>106392.77</v>
       </c>
       <c r="C27">
-        <v>57870.09</v>
+        <v>57397.19</v>
       </c>
       <c r="D27">
-        <v>41655.69</v>
+        <v>41200.839999999997</v>
       </c>
       <c r="E27">
-        <v>33657.18</v>
+        <v>33203.040000000001</v>
       </c>
       <c r="F27">
-        <v>25870.3</v>
+        <v>25401.07</v>
       </c>
       <c r="G27">
-        <v>22178.87</v>
+        <v>21687.67</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.25">
@@ -1397,22 +1397,22 @@
         <v>29</v>
       </c>
       <c r="B28">
-        <v>110773.75</v>
+        <v>110192.51</v>
       </c>
       <c r="C28">
-        <v>59936.88</v>
+        <v>59447.09</v>
       </c>
       <c r="D28">
-        <v>43413.4</v>
+        <v>42672.3</v>
       </c>
       <c r="E28">
-        <v>34859.22</v>
+        <v>34388.870000000003</v>
       </c>
       <c r="F28">
-        <v>26794.240000000002</v>
+        <v>26308.25</v>
       </c>
       <c r="G28">
-        <v>22970.98</v>
+        <v>22462.23</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.25">
@@ -1420,22 +1420,22 @@
         <v>30</v>
       </c>
       <c r="B29">
-        <v>114593.53</v>
+        <v>113992.25</v>
       </c>
       <c r="C29">
-        <v>62003.67</v>
+        <v>61496.99</v>
       </c>
       <c r="D29">
-        <v>44631.1</v>
+        <v>44143.76</v>
       </c>
       <c r="E29">
-        <v>36061.269999999997</v>
+        <v>35574.69</v>
       </c>
       <c r="F29">
-        <v>27718.18</v>
+        <v>27215.439999999999</v>
       </c>
       <c r="G29">
-        <v>23763.08</v>
+        <v>23236.79</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.25">
@@ -1443,22 +1443,22 @@
         <v>31</v>
       </c>
       <c r="B30">
-        <v>118413.31</v>
+        <v>117791.99</v>
       </c>
       <c r="C30">
-        <v>64070.46</v>
+        <v>63546.89</v>
       </c>
       <c r="D30">
-        <v>46118.8</v>
+        <v>45615.22</v>
       </c>
       <c r="E30">
-        <v>37263.31</v>
+        <v>36760.51</v>
       </c>
       <c r="F30">
-        <v>28642.12</v>
+        <v>28122.62</v>
       </c>
       <c r="G30">
-        <v>24555.18</v>
+        <v>24011.35</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
@@ -1466,22 +1466,22 @@
         <v>32</v>
       </c>
       <c r="B31">
-        <v>122233.1</v>
+        <v>121591.74</v>
       </c>
       <c r="C31">
-        <v>66137.25</v>
+        <v>65596.789999999994</v>
       </c>
       <c r="D31">
-        <v>47606.51</v>
+        <v>47086.68</v>
       </c>
       <c r="E31">
-        <v>38465.35</v>
+        <v>37946.33</v>
       </c>
       <c r="F31">
-        <v>29566.06</v>
+        <v>29029.8</v>
       </c>
       <c r="G31">
-        <v>25347.279999999999</v>
+        <v>24785.91</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.25">
@@ -1489,22 +1489,22 @@
         <v>33</v>
       </c>
       <c r="B32">
-        <v>126052.88</v>
+        <v>125391.48</v>
       </c>
       <c r="C32">
-        <v>68204.039999999994</v>
+        <v>67646.69</v>
       </c>
       <c r="D32">
-        <v>49094.21</v>
+        <v>48558.14</v>
       </c>
       <c r="E32">
-        <v>39667.39</v>
+        <v>39132.160000000003</v>
       </c>
       <c r="F32">
-        <v>30490</v>
+        <v>29936.98</v>
       </c>
       <c r="G32">
-        <v>26139.39</v>
+        <v>25560.47</v>
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.25">
@@ -1512,22 +1512,22 @@
         <v>34</v>
       </c>
       <c r="B33">
-        <v>129872.67</v>
+        <v>129191.22</v>
       </c>
       <c r="C33">
-        <v>70270.83</v>
+        <v>69696.59</v>
       </c>
       <c r="D33">
-        <v>50581.91</v>
+        <v>50029.599999999999</v>
       </c>
       <c r="E33">
-        <v>40869.440000000002</v>
+        <v>40317.980000000003</v>
       </c>
       <c r="F33">
-        <v>31413.94</v>
+        <v>30844.16</v>
       </c>
       <c r="G33">
-        <v>26931.49</v>
+        <v>26335.03</v>
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.25">
@@ -1535,22 +1535,22 @@
         <v>35</v>
       </c>
       <c r="B34">
-        <v>133692.45000000001</v>
+        <v>132990.96</v>
       </c>
       <c r="C34">
-        <v>72337.62</v>
+        <v>71746.490000000005</v>
       </c>
       <c r="D34">
-        <v>52069.61</v>
+        <v>51501.05</v>
       </c>
       <c r="E34">
-        <v>42071.48</v>
+        <v>41503.800000000003</v>
       </c>
       <c r="F34">
-        <v>32337.88</v>
+        <v>31751.34</v>
       </c>
       <c r="G34">
-        <v>27723.59</v>
+        <v>27109.59</v>
       </c>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.25">
@@ -1558,22 +1558,22 @@
         <v>36</v>
       </c>
       <c r="B35">
-        <v>137512.24</v>
+        <v>136790.70000000001</v>
       </c>
       <c r="C35">
-        <v>74404.399999999994</v>
+        <v>73796.39</v>
       </c>
       <c r="D35">
-        <v>53557.32</v>
+        <v>52972.51</v>
       </c>
       <c r="E35">
-        <v>43273.52</v>
+        <v>42689.63</v>
       </c>
       <c r="F35">
-        <v>33261.82</v>
+        <v>32658.52</v>
       </c>
       <c r="G35">
-        <v>28515.69</v>
+        <v>27884.15</v>
       </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.25">
@@ -1581,22 +1581,22 @@
         <v>37</v>
       </c>
       <c r="B36">
-        <v>141332.01999999999</v>
+        <v>140590.44</v>
       </c>
       <c r="C36">
-        <v>76471.19</v>
+        <v>75846.289999999994</v>
       </c>
       <c r="D36">
-        <v>55045.02</v>
+        <v>54443.97</v>
       </c>
       <c r="E36">
-        <v>44475.56</v>
+        <v>43875.45</v>
       </c>
       <c r="F36">
-        <v>34185.760000000002</v>
+        <v>33565.699999999997</v>
       </c>
       <c r="G36">
-        <v>29307.8</v>
+        <v>28658.71</v>
       </c>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.25">
@@ -1604,22 +1604,22 @@
         <v>38</v>
       </c>
       <c r="B37">
-        <v>145151.79999999999</v>
+        <v>144390.19</v>
       </c>
       <c r="C37">
-        <v>78537.98</v>
+        <v>77896.19</v>
       </c>
       <c r="D37">
-        <v>56532.72</v>
+        <v>55915.43</v>
       </c>
       <c r="E37">
-        <v>45667.6</v>
+        <v>45061.27</v>
       </c>
       <c r="F37">
-        <v>35109.69</v>
+        <v>34472.879999999997</v>
       </c>
       <c r="G37">
-        <v>30099.9</v>
+        <v>29433.27</v>
       </c>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.25">
@@ -1627,22 +1627,22 @@
         <v>39</v>
       </c>
       <c r="B38">
-        <v>148971.59</v>
+        <v>148189.93</v>
       </c>
       <c r="C38">
-        <v>80604.77</v>
+        <v>79946.09</v>
       </c>
       <c r="D38">
-        <v>58020.43</v>
+        <v>57386.89</v>
       </c>
       <c r="E38">
-        <v>46879.65</v>
+        <v>46247.09</v>
       </c>
       <c r="F38">
-        <v>36033.629999999997</v>
+        <v>35380.07</v>
       </c>
       <c r="G38">
-        <v>30892</v>
+        <v>30207.83</v>
       </c>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.25">
@@ -1650,22 +1650,22 @@
         <v>40</v>
       </c>
       <c r="B39">
-        <v>152791.37</v>
+        <v>151989.67000000001</v>
       </c>
       <c r="C39">
-        <v>82671.56</v>
+        <v>81995.990000000005</v>
       </c>
       <c r="D39">
-        <v>59508.13</v>
+        <v>58858.35</v>
       </c>
       <c r="E39">
-        <v>48081.69</v>
+        <v>47432.92</v>
       </c>
       <c r="F39">
-        <v>36957.57</v>
+        <v>36287.25</v>
       </c>
       <c r="G39">
-        <v>31684.1</v>
+        <v>30982.39</v>
       </c>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.25">
@@ -1673,22 +1673,22 @@
         <v>41</v>
       </c>
       <c r="B40">
-        <v>156611.16</v>
+        <v>155789.41</v>
       </c>
       <c r="C40">
-        <v>84738.35</v>
+        <v>84045.89</v>
       </c>
       <c r="D40">
-        <v>60995.83</v>
+        <v>60329.81</v>
       </c>
       <c r="E40">
-        <v>49283.73</v>
+        <v>48618.74</v>
       </c>
       <c r="F40">
-        <v>37881.51</v>
+        <v>37194.43</v>
       </c>
       <c r="G40">
-        <v>32476.21</v>
+        <v>31756.95</v>
       </c>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.25">
@@ -1696,22 +1696,22 @@
         <v>42</v>
       </c>
       <c r="B41">
-        <v>160430.94</v>
+        <v>159589.15</v>
       </c>
       <c r="C41">
-        <v>86805.14</v>
+        <v>86095.79</v>
       </c>
       <c r="D41">
-        <v>62483.54</v>
+        <v>61801.27</v>
       </c>
       <c r="E41">
-        <v>50485.77</v>
+        <v>49804.56</v>
       </c>
       <c r="F41">
-        <v>38805.449999999997</v>
+        <v>38101.61</v>
       </c>
       <c r="G41">
-        <v>33268.31</v>
+        <v>32531.51</v>
       </c>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.25">
@@ -1719,22 +1719,22 @@
         <v>43</v>
       </c>
       <c r="B42">
-        <v>164250.73000000001</v>
+        <v>163388.9</v>
       </c>
       <c r="C42">
-        <v>88871.93</v>
+        <v>88145.69</v>
       </c>
       <c r="D42">
-        <v>63971.24</v>
+        <v>63272.72</v>
       </c>
       <c r="E42">
-        <v>51687.82</v>
+        <v>50990.39</v>
       </c>
       <c r="F42">
-        <v>39729.39</v>
+        <v>39008.79</v>
       </c>
       <c r="G42">
-        <v>34060.410000000003</v>
+        <v>33306.07</v>
       </c>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.25">
@@ -1742,22 +1742,22 @@
         <v>44</v>
       </c>
       <c r="B43">
-        <v>168070.51</v>
+        <v>167188.64000000001</v>
       </c>
       <c r="C43">
-        <v>90938.72</v>
+        <v>90195.59</v>
       </c>
       <c r="D43">
-        <v>65458.94</v>
+        <v>64744.18</v>
       </c>
       <c r="E43">
-        <v>52889.86</v>
+        <v>52176.21</v>
       </c>
       <c r="F43">
-        <v>40653.33</v>
+        <v>39915.97</v>
       </c>
       <c r="G43">
-        <v>34852.51</v>
+        <v>34080.629999999997</v>
       </c>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.25">
@@ -1765,22 +1765,22 @@
         <v>45</v>
       </c>
       <c r="B44">
-        <v>171890.29</v>
+        <v>170988.38</v>
       </c>
       <c r="C44">
-        <v>93005.51</v>
+        <v>92245.49</v>
       </c>
       <c r="D44">
-        <v>66946.649999999994</v>
+        <v>66215.64</v>
       </c>
       <c r="E44">
-        <v>54091.9</v>
+        <v>53362.03</v>
       </c>
       <c r="F44" s="1">
-        <v>41577.269999999997</v>
+        <v>40823.15</v>
       </c>
       <c r="G44">
-        <v>35644.620000000003</v>
+        <v>34855.19</v>
       </c>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.25">
@@ -1788,22 +1788,22 @@
         <v>46</v>
       </c>
       <c r="B45">
-        <v>175710.07999999999</v>
+        <v>174788.12</v>
       </c>
       <c r="C45">
-        <v>95072.29</v>
+        <v>94295.39</v>
       </c>
       <c r="D45">
-        <v>68434.350000000006</v>
+        <v>67687.100000000006</v>
       </c>
       <c r="E45">
-        <v>55293.94</v>
+        <v>54547.86</v>
       </c>
       <c r="F45">
-        <v>42501.21</v>
+        <v>41730.33</v>
       </c>
       <c r="G45">
-        <v>36436.720000000001</v>
+        <v>35629.75</v>
       </c>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.25">
@@ -1811,22 +1811,22 @@
         <v>47</v>
       </c>
       <c r="B46">
-        <v>179529.86</v>
+        <v>178587.86</v>
       </c>
       <c r="C46">
-        <v>97139.08</v>
+        <v>96345.29</v>
       </c>
       <c r="D46">
-        <v>69922.05</v>
+        <v>69158.559999999998</v>
       </c>
       <c r="E46">
-        <v>56495.98</v>
+        <v>55733.68</v>
       </c>
       <c r="F46">
-        <v>43425.15</v>
+        <v>42637.52</v>
       </c>
       <c r="G46">
-        <v>37228.82</v>
+        <v>36404.31</v>
       </c>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.25">
@@ -1834,22 +1834,22 @@
         <v>48</v>
       </c>
       <c r="B47">
-        <v>183349.65</v>
+        <v>182387.6</v>
       </c>
       <c r="C47">
-        <v>99205.87</v>
+        <v>98395.19</v>
       </c>
       <c r="D47">
-        <v>71409.759999999995</v>
+        <v>70630.02</v>
       </c>
       <c r="E47">
-        <v>57698.03</v>
+        <v>56919.5</v>
       </c>
       <c r="F47">
-        <v>44349.09</v>
+        <v>43544.7</v>
       </c>
       <c r="G47">
-        <v>38020.92</v>
+        <v>37178.870000000003</v>
       </c>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.25">
@@ -1857,22 +1857,22 @@
         <v>49</v>
       </c>
       <c r="B48">
-        <v>187169.43</v>
+        <v>186187.35</v>
       </c>
       <c r="C48">
-        <v>101272.66</v>
+        <v>100445.09</v>
       </c>
       <c r="D48">
-        <v>72897.460000000006</v>
+        <v>72101.48</v>
       </c>
       <c r="E48">
-        <v>59800.07</v>
+        <v>58105.32</v>
       </c>
       <c r="F48">
-        <v>45273.03</v>
+        <v>44451.88</v>
       </c>
       <c r="G48">
-        <v>38813.03</v>
+        <v>37953.43</v>
       </c>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.25">
@@ -1880,22 +1880,22 @@
         <v>50</v>
       </c>
       <c r="B49">
-        <v>190989.22</v>
+        <v>189987.09</v>
       </c>
       <c r="C49">
-        <v>103339.45</v>
+        <v>102494.99</v>
       </c>
       <c r="D49">
-        <v>74385.16</v>
+        <v>73572.929999999993</v>
       </c>
       <c r="E49">
-        <v>60102.11</v>
+        <v>59291.15</v>
       </c>
       <c r="F49">
-        <v>46196.97</v>
+        <v>45359.06</v>
       </c>
       <c r="G49">
-        <v>39605.129999999997</v>
+        <v>38727.99</v>
       </c>
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.25">
@@ -1903,22 +1903,22 @@
         <v>51</v>
       </c>
       <c r="B50">
-        <v>194809</v>
+        <v>193786.83</v>
       </c>
       <c r="C50">
-        <v>105406.24</v>
+        <v>104544.88</v>
       </c>
       <c r="D50">
-        <v>75872.87</v>
+        <v>75044.39</v>
       </c>
       <c r="E50">
-        <v>61304.15</v>
+        <v>60476.97</v>
       </c>
       <c r="F50">
-        <v>47120.91</v>
+        <v>46266.239999999998</v>
       </c>
       <c r="G50">
-        <v>40397.230000000003</v>
+        <v>39502.550000000003</v>
       </c>
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.25">
@@ -1926,22 +1926,22 @@
         <v>52</v>
       </c>
       <c r="B51">
-        <v>198628.79</v>
+        <v>197586.57</v>
       </c>
       <c r="C51">
-        <v>107473.03</v>
+        <v>106594.78</v>
       </c>
       <c r="D51">
-        <v>77360.570000000007</v>
+        <v>76515.850000000006</v>
       </c>
       <c r="E51">
-        <v>62506.2</v>
+        <v>61662.79</v>
       </c>
       <c r="F51">
-        <v>48044.85</v>
+        <v>47173.42</v>
       </c>
       <c r="G51">
-        <v>41189.33</v>
+        <v>40277.11</v>
       </c>
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.25">
@@ -1949,22 +1949,22 @@
         <v>53</v>
       </c>
       <c r="B52">
-        <v>202448.57</v>
+        <v>201386.31</v>
       </c>
       <c r="C52">
-        <v>109539.82</v>
+        <v>108644.68</v>
       </c>
       <c r="D52">
-        <v>78848.27</v>
+        <v>77987.31</v>
       </c>
       <c r="E52">
-        <v>63708.24</v>
+        <v>62848.62</v>
       </c>
       <c r="F52">
-        <v>48968.78</v>
+        <v>48080.6</v>
       </c>
       <c r="G52">
-        <v>41981.440000000002</v>
+        <v>41051.67</v>
       </c>
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.25">
@@ -1972,22 +1972,22 @@
         <v>54</v>
       </c>
       <c r="B53">
-        <v>206268.35</v>
+        <v>205186.05</v>
       </c>
       <c r="C53">
-        <v>111606.61</v>
+        <v>110694.58</v>
       </c>
       <c r="D53">
-        <v>80335.98</v>
+        <v>79458.77</v>
       </c>
       <c r="E53">
-        <v>64910.28</v>
+        <v>64034.44</v>
       </c>
       <c r="F53">
-        <v>49892.72</v>
+        <v>48987.78</v>
       </c>
       <c r="G53">
-        <v>42773.54</v>
+        <v>41826.230000000003</v>
       </c>
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.25">
@@ -1995,22 +1995,22 @@
         <v>55</v>
       </c>
       <c r="B54">
-        <v>210088.14</v>
+        <v>208985.8</v>
       </c>
       <c r="C54">
-        <v>113673.4</v>
+        <v>112744.48</v>
       </c>
       <c r="D54">
-        <v>81823.679999999993</v>
+        <v>80930.23</v>
       </c>
       <c r="E54">
-        <v>66112.320000000007</v>
+        <v>65220.26</v>
       </c>
       <c r="F54">
-        <v>50816.66</v>
+        <v>49894.97</v>
       </c>
       <c r="G54">
-        <v>43565.64</v>
+        <v>42600.79</v>
       </c>
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.25">
@@ -2018,22 +2018,22 @@
         <v>56</v>
       </c>
       <c r="B55">
-        <v>213907.92</v>
+        <v>212785.54</v>
       </c>
       <c r="C55">
-        <v>115740.18</v>
+        <v>114794.38</v>
       </c>
       <c r="D55">
-        <v>83311.38</v>
+        <v>82401.69</v>
       </c>
       <c r="E55">
-        <v>67314.36</v>
+        <v>66406.09</v>
       </c>
       <c r="F55">
-        <v>51740.6</v>
+        <v>50802.15</v>
       </c>
       <c r="G55">
-        <v>44357.75</v>
+        <v>43375.35</v>
       </c>
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.25">
@@ -2041,22 +2041,22 @@
         <v>57</v>
       </c>
       <c r="B56">
-        <v>217727.71</v>
+        <v>216585.28</v>
       </c>
       <c r="C56">
-        <v>117806.97</v>
+        <v>116844.28</v>
       </c>
       <c r="D56">
-        <v>84799.09</v>
+        <v>83873.149999999994</v>
       </c>
       <c r="E56">
-        <v>68516.41</v>
+        <v>67591.91</v>
       </c>
       <c r="F56">
-        <v>52664.54</v>
+        <v>51709.33</v>
       </c>
       <c r="G56">
-        <v>45149.85</v>
+        <v>44149.91</v>
       </c>
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.25">
@@ -2064,22 +2064,22 @@
         <v>58</v>
       </c>
       <c r="B57">
-        <v>221547.49</v>
+        <v>220385.02</v>
       </c>
       <c r="C57">
-        <v>119873.76</v>
+        <v>118894.18</v>
       </c>
       <c r="D57">
-        <v>86286.79</v>
+        <v>85344.6</v>
       </c>
       <c r="E57">
-        <v>69718.45</v>
+        <v>68777.73</v>
       </c>
       <c r="F57">
-        <v>53588.480000000003</v>
+        <v>52616.51</v>
       </c>
       <c r="G57">
-        <v>45941.95</v>
+        <v>44924.46</v>
       </c>
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.25">
@@ -2087,22 +2087,22 @@
         <v>59</v>
       </c>
       <c r="B58">
-        <v>225367.28</v>
+        <v>224184.76</v>
       </c>
       <c r="C58">
-        <v>121940.55</v>
+        <v>120944.08</v>
       </c>
       <c r="D58">
-        <v>87774.49</v>
+        <v>86816.06</v>
       </c>
       <c r="E58">
-        <v>70920.490000000005</v>
+        <v>69963.55</v>
       </c>
       <c r="F58">
-        <v>54512.42</v>
+        <v>53523.69</v>
       </c>
       <c r="G58">
-        <v>46734.05</v>
+        <v>45699.02</v>
       </c>
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.25">
@@ -2110,22 +2110,22 @@
         <v>60</v>
       </c>
       <c r="B59">
-        <v>229187.06</v>
+        <v>227984.5</v>
       </c>
       <c r="C59">
-        <v>124007.34</v>
+        <v>122993.98</v>
       </c>
       <c r="D59">
-        <v>89262.2</v>
+        <v>88287.52</v>
       </c>
       <c r="E59">
-        <v>72122.53</v>
+        <v>71149.38</v>
       </c>
       <c r="F59">
-        <v>55436.36</v>
+        <v>54430.87</v>
       </c>
       <c r="G59">
-        <v>47526.16</v>
+        <v>46473.58</v>
       </c>
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.25">
@@ -2133,22 +2133,22 @@
         <v>61</v>
       </c>
       <c r="B60">
-        <v>233006.84</v>
+        <v>231784.25</v>
       </c>
       <c r="C60">
-        <v>126074.13</v>
+        <v>125043.88</v>
       </c>
       <c r="D60">
-        <v>90749.9</v>
+        <v>89758.98</v>
       </c>
       <c r="E60">
-        <v>73324.58</v>
+        <v>72335.199999999997</v>
       </c>
       <c r="F60">
-        <v>56360.3</v>
+        <v>55338.05</v>
       </c>
       <c r="G60">
-        <v>48318.26</v>
+        <v>47248.14</v>
       </c>
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.25">
@@ -2156,22 +2156,22 @@
         <v>62</v>
       </c>
       <c r="B61">
-        <v>236826.63</v>
+        <v>235583.99</v>
       </c>
       <c r="C61">
-        <v>128140.92</v>
+        <v>127093.78</v>
       </c>
       <c r="D61">
-        <v>92237.6</v>
+        <v>91230.44</v>
       </c>
       <c r="E61">
-        <v>74526.62</v>
+        <v>73521.02</v>
       </c>
       <c r="F61">
-        <v>57284.24</v>
+        <v>56245.23</v>
       </c>
       <c r="G61">
-        <v>49110.36</v>
+        <v>48022.7</v>
       </c>
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.25">
@@ -2179,22 +2179,22 @@
         <v>63</v>
       </c>
       <c r="B62">
-        <v>240646.41</v>
+        <v>239383.73</v>
       </c>
       <c r="C62">
-        <v>130207.71</v>
+        <v>129143.67999999999</v>
       </c>
       <c r="D62">
-        <v>93725.31</v>
+        <v>92701.9</v>
       </c>
       <c r="E62">
-        <v>75728.66</v>
+        <v>74706.850000000006</v>
       </c>
       <c r="F62">
-        <v>58208.18</v>
+        <v>57152.41</v>
       </c>
       <c r="G62">
-        <v>49902.46</v>
+        <v>48797.26</v>
       </c>
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.25">
@@ -2202,22 +2202,22 @@
         <v>64</v>
       </c>
       <c r="B63">
-        <v>244466.2</v>
+        <v>243183.47</v>
       </c>
       <c r="C63">
-        <v>132274.5</v>
+        <v>131193.57999999999</v>
       </c>
       <c r="D63">
-        <v>95213.01</v>
+        <v>94173.36</v>
       </c>
       <c r="E63">
-        <v>76930.7</v>
+        <v>75892.67</v>
       </c>
       <c r="F63">
-        <v>59132.12</v>
+        <v>58059.6</v>
       </c>
       <c r="G63">
-        <v>50694.57</v>
+        <v>49571.82</v>
       </c>
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.25">
@@ -2225,22 +2225,22 @@
         <v>65</v>
       </c>
       <c r="B64">
-        <v>248285.9</v>
+        <v>246983.21</v>
       </c>
       <c r="C64">
-        <v>134341.29</v>
+        <v>133243.48000000001</v>
       </c>
       <c r="D64">
-        <v>96700.71</v>
+        <v>95644.81</v>
       </c>
       <c r="E64">
-        <v>78132.740000000005</v>
+        <v>77078.490000000005</v>
       </c>
       <c r="F64">
-        <v>60056.06</v>
+        <v>58966.78</v>
       </c>
       <c r="G64">
-        <v>51486.67</v>
+        <v>50346.38</v>
       </c>
     </row>
     <row r="65" spans="1:7" x14ac:dyDescent="0.25">
@@ -2248,22 +2248,22 @@
         <v>66</v>
       </c>
       <c r="B65">
-        <v>252105.77</v>
+        <v>250782.96</v>
       </c>
       <c r="C65">
-        <v>136408.07</v>
+        <v>135293.38</v>
       </c>
       <c r="D65">
-        <v>98188.42</v>
+        <v>97116.27</v>
       </c>
       <c r="E65">
-        <v>79334.789999999994</v>
+        <v>78264.31</v>
       </c>
       <c r="F65">
-        <v>60980</v>
+        <v>59873.96</v>
       </c>
       <c r="G65">
-        <v>52278.77</v>
+        <v>51120.94</v>
       </c>
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.25">
@@ -2271,22 +2271,22 @@
         <v>67</v>
       </c>
       <c r="B66">
-        <v>255925.55</v>
+        <v>254582.7</v>
       </c>
       <c r="C66">
-        <v>138474.85999999999</v>
+        <v>137343.28</v>
       </c>
       <c r="D66">
-        <v>99676.12</v>
+        <v>98587.73</v>
       </c>
       <c r="E66">
-        <v>80536.83</v>
+        <v>79450.14</v>
       </c>
       <c r="F66">
-        <v>61903.94</v>
+        <v>60781.14</v>
       </c>
       <c r="G66">
-        <v>53070.87</v>
+        <v>51895.5</v>
       </c>
     </row>
     <row r="67" spans="1:7" x14ac:dyDescent="0.25">
@@ -2294,22 +2294,22 @@
         <v>68</v>
       </c>
       <c r="B67">
-        <v>259745.33</v>
+        <v>258382.44</v>
       </c>
       <c r="C67">
-        <v>140541.65</v>
+        <v>139393.18</v>
       </c>
       <c r="D67">
-        <v>101163.82</v>
+        <v>100059.19</v>
       </c>
       <c r="E67">
-        <v>81738.87</v>
+        <v>80635.960000000006</v>
       </c>
       <c r="F67">
-        <v>62827.87</v>
+        <v>61688.32</v>
       </c>
       <c r="G67">
-        <v>53862.98</v>
+        <v>52670.06</v>
       </c>
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.25">
@@ -2317,22 +2317,22 @@
         <v>69</v>
       </c>
       <c r="B68">
-        <v>263565.12</v>
+        <v>262182.18</v>
       </c>
       <c r="C68">
-        <v>142608.44</v>
+        <v>141443.07999999999</v>
       </c>
       <c r="D68">
-        <v>102651.53</v>
+        <v>101530.65</v>
       </c>
       <c r="E68">
-        <v>82940.91</v>
+        <v>81821.78</v>
       </c>
       <c r="F68">
-        <v>63751.81</v>
+        <v>62595.5</v>
       </c>
       <c r="G68">
-        <v>54655.08</v>
+        <v>53444.62</v>
       </c>
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.25">
@@ -2340,22 +2340,22 @@
         <v>70</v>
       </c>
       <c r="B69">
-        <v>267384.90000000002</v>
+        <v>265981.92</v>
       </c>
       <c r="C69">
-        <v>144675.23000000001</v>
+        <v>143492.98000000001</v>
       </c>
       <c r="D69">
-        <v>104139.23</v>
+        <v>103002.11</v>
       </c>
       <c r="E69">
-        <v>84142.96</v>
+        <v>83007.61</v>
       </c>
       <c r="F69">
-        <v>64675.75</v>
+        <v>63502.68</v>
       </c>
       <c r="G69">
-        <v>55447.18</v>
+        <v>54219.18</v>
       </c>
     </row>
     <row r="70" spans="1:7" x14ac:dyDescent="0.25">
@@ -2363,22 +2363,22 @@
         <v>71</v>
       </c>
       <c r="B70">
-        <v>271204.69</v>
+        <v>269781.65999999997</v>
       </c>
       <c r="C70">
-        <v>146742.01999999999</v>
+        <v>145542.88</v>
       </c>
       <c r="D70">
-        <v>105626.93</v>
+        <v>104473.57</v>
       </c>
       <c r="E70">
-        <v>85345</v>
+        <v>84193.43</v>
       </c>
       <c r="F70">
-        <v>65599.69</v>
+        <v>64409.86</v>
       </c>
       <c r="G70">
-        <v>56239.28</v>
+        <v>54993.74</v>
       </c>
     </row>
     <row r="71" spans="1:7" x14ac:dyDescent="0.25">
@@ -2386,22 +2386,22 @@
         <v>72</v>
       </c>
       <c r="B71">
-        <v>275024.46999999997</v>
+        <v>273581.40999999997</v>
       </c>
       <c r="C71">
-        <v>148808.81</v>
+        <v>147592.78</v>
       </c>
       <c r="D71">
-        <v>107114.64</v>
+        <v>105945.03</v>
       </c>
       <c r="E71">
-        <v>86547.04</v>
+        <v>85379.25</v>
       </c>
       <c r="F71">
-        <v>66523.63</v>
+        <v>65317.05</v>
       </c>
       <c r="G71">
-        <v>57031.39</v>
+        <v>55768.3</v>
       </c>
     </row>
     <row r="72" spans="1:7" x14ac:dyDescent="0.25">
@@ -2409,22 +2409,22 @@
         <v>73</v>
       </c>
       <c r="B72">
-        <v>278844.26</v>
+        <v>277381.15000000002</v>
       </c>
       <c r="C72">
-        <v>150875.6</v>
+        <v>149642.68</v>
       </c>
       <c r="D72">
-        <v>108602.34</v>
+        <v>107416.48</v>
       </c>
       <c r="E72">
-        <v>87749.08</v>
+        <v>86565.08</v>
       </c>
       <c r="F72">
-        <v>67447.570000000007</v>
+        <v>66224.23</v>
       </c>
       <c r="G72">
-        <v>57823.49</v>
+        <v>56542.86</v>
       </c>
     </row>
     <row r="73" spans="1:7" x14ac:dyDescent="0.25">
@@ -2432,22 +2432,22 @@
         <v>74</v>
       </c>
       <c r="B73">
-        <v>282664.03999999998</v>
+        <v>281180.89</v>
       </c>
       <c r="C73">
-        <v>152942.39000000001</v>
+        <v>151692.57999999999</v>
       </c>
       <c r="D73">
-        <v>110090.04</v>
+        <v>108887.94</v>
       </c>
       <c r="E73">
-        <v>88951.12</v>
+        <v>87750.9</v>
       </c>
       <c r="F73">
-        <v>68371.509999999995</v>
+        <v>67131.41</v>
       </c>
       <c r="G73">
-        <v>58615.59</v>
+        <v>57317.42</v>
       </c>
     </row>
     <row r="74" spans="1:7" x14ac:dyDescent="0.25">
@@ -2455,22 +2455,22 @@
         <v>75</v>
       </c>
       <c r="B74">
-        <v>286483.82</v>
+        <v>284980.63</v>
       </c>
       <c r="C74">
-        <v>155009.18</v>
+        <v>153742.48000000001</v>
       </c>
       <c r="D74">
-        <v>111577.75</v>
+        <v>110359.4</v>
       </c>
       <c r="E74">
-        <v>90153.17</v>
+        <v>88936.72</v>
       </c>
       <c r="F74">
-        <v>69295.45</v>
+        <v>68038.59</v>
       </c>
       <c r="G74">
-        <v>59407.69</v>
+        <v>58091.98</v>
       </c>
     </row>
     <row r="75" spans="1:7" x14ac:dyDescent="0.25">
@@ -2478,22 +2478,22 @@
         <v>76</v>
       </c>
       <c r="B75">
-        <v>290303.61</v>
+        <v>288780.37</v>
       </c>
       <c r="C75">
-        <v>157075.96</v>
+        <v>155792.38</v>
       </c>
       <c r="D75">
-        <v>113065.45</v>
+        <v>111830.86</v>
       </c>
       <c r="E75">
-        <v>91355.21</v>
+        <v>90122.54</v>
       </c>
       <c r="F75">
-        <v>70219.39</v>
+        <v>68945.77</v>
       </c>
       <c r="G75">
-        <v>60199.8</v>
+        <v>58866.54</v>
       </c>
     </row>
     <row r="76" spans="1:7" x14ac:dyDescent="0.25">
@@ -2501,22 +2501,22 @@
         <v>77</v>
       </c>
       <c r="B76">
-        <v>294123.39</v>
+        <v>292580.11</v>
       </c>
       <c r="C76">
-        <v>159142.75</v>
+        <v>157842.28</v>
       </c>
       <c r="D76">
-        <v>114553.15</v>
+        <v>113302.32</v>
       </c>
       <c r="E76">
-        <v>92557.25</v>
+        <v>91308.37</v>
       </c>
       <c r="F76">
-        <v>71143.33</v>
+        <v>69852.95</v>
       </c>
       <c r="G76">
-        <v>60991.9</v>
+        <v>59641.1</v>
       </c>
     </row>
     <row r="77" spans="1:7" x14ac:dyDescent="0.25">
@@ -2524,22 +2524,22 @@
         <v>78</v>
       </c>
       <c r="B77">
-        <v>297943.18</v>
+        <v>296379.86</v>
       </c>
       <c r="C77">
-        <v>161209.54</v>
+        <v>159892.18</v>
       </c>
       <c r="D77">
-        <v>116040.86</v>
+        <v>114773.78</v>
       </c>
       <c r="E77">
-        <v>93759.29</v>
+        <v>92494.19</v>
       </c>
       <c r="F77">
-        <v>72067.27</v>
+        <v>70760.13</v>
       </c>
       <c r="G77">
-        <v>61784</v>
+        <v>60415.66</v>
       </c>
     </row>
     <row r="78" spans="1:7" x14ac:dyDescent="0.25">
@@ -2547,22 +2547,22 @@
         <v>79</v>
       </c>
       <c r="B78">
-        <v>301762.96000000002</v>
+        <v>300179.59999999998</v>
       </c>
       <c r="C78">
-        <v>163276.32999999999</v>
+        <v>161942.07999999999</v>
       </c>
       <c r="D78">
-        <v>117528.56</v>
+        <v>116245.24</v>
       </c>
       <c r="E78">
-        <v>94961.34</v>
+        <v>93680.01</v>
       </c>
       <c r="F78">
-        <v>72991.210000000006</v>
+        <v>71667.31</v>
       </c>
       <c r="G78">
-        <v>62576.1</v>
+        <v>61190.22</v>
       </c>
     </row>
     <row r="79" spans="1:7" x14ac:dyDescent="0.25">
@@ -2570,22 +2570,22 @@
         <v>80</v>
       </c>
       <c r="B79">
-        <v>305582.75</v>
+        <v>303979.34000000003</v>
       </c>
       <c r="C79">
-        <v>165343.12</v>
+        <v>163991.98000000001</v>
       </c>
       <c r="D79">
-        <v>119016.26</v>
+        <v>117716.7</v>
       </c>
       <c r="E79">
-        <v>96163.38</v>
+        <v>94865.84</v>
       </c>
       <c r="F79">
-        <v>73915.149999999994</v>
+        <v>72574.490000000005</v>
       </c>
       <c r="G79">
-        <v>63368.21</v>
+        <v>61964.78</v>
       </c>
     </row>
     <row r="80" spans="1:7" x14ac:dyDescent="0.25">
@@ -2593,22 +2593,22 @@
         <v>81</v>
       </c>
       <c r="B80">
-        <v>309402.53000000003</v>
+        <v>307779.08</v>
       </c>
       <c r="C80">
-        <v>167409.91</v>
+        <v>166041.88</v>
       </c>
       <c r="D80">
-        <v>120503.97</v>
+        <v>119188.15</v>
       </c>
       <c r="E80">
-        <v>97365.42</v>
+        <v>96051.66</v>
       </c>
       <c r="F80">
-        <v>74839.09</v>
+        <v>73481.679999999993</v>
       </c>
       <c r="G80">
-        <v>64160.31</v>
+        <v>62739.34</v>
       </c>
     </row>
     <row r="81" spans="1:7" x14ac:dyDescent="0.25">
@@ -2616,22 +2616,22 @@
         <v>82</v>
       </c>
       <c r="B81">
-        <v>313222.32</v>
+        <v>311578.82</v>
       </c>
       <c r="C81">
-        <v>169476.7</v>
+        <v>168091.78</v>
       </c>
       <c r="D81">
-        <v>121991.67</v>
+        <v>120659.61</v>
       </c>
       <c r="E81">
-        <v>98567.46</v>
+        <v>97237.48</v>
       </c>
       <c r="F81">
-        <v>75763.03</v>
+        <v>74388.86</v>
       </c>
       <c r="G81">
-        <v>64952.41</v>
+        <v>63513.9</v>
       </c>
     </row>
     <row r="82" spans="1:7" x14ac:dyDescent="0.25">
@@ -2639,22 +2639,22 @@
         <v>83</v>
       </c>
       <c r="B82">
-        <v>317042.09999999998</v>
+        <v>315378.57</v>
       </c>
       <c r="C82">
-        <v>171543.49</v>
+        <v>170141.68</v>
       </c>
       <c r="D82">
-        <v>123479.37</v>
+        <v>122131.07</v>
       </c>
       <c r="E82">
-        <v>99769.5</v>
+        <v>98423.3</v>
       </c>
       <c r="F82">
-        <v>76686.960000000006</v>
+        <v>75296.039999999994</v>
       </c>
       <c r="G82">
-        <v>65744.52</v>
+        <v>64288.46</v>
       </c>
     </row>
     <row r="83" spans="1:7" x14ac:dyDescent="0.25">
@@ -2662,22 +2662,22 @@
         <v>84</v>
       </c>
       <c r="B83">
-        <v>320861.88</v>
+        <v>319178.31</v>
       </c>
       <c r="C83">
-        <v>173610.28</v>
+        <v>172191.58</v>
       </c>
       <c r="D83">
-        <v>124967.08</v>
+        <v>123602.53</v>
       </c>
       <c r="E83">
-        <v>100971.55</v>
+        <v>99609.13</v>
       </c>
       <c r="F83">
-        <v>77610.899999999994</v>
+        <v>76203.22</v>
       </c>
       <c r="G83">
-        <v>66536.62</v>
+        <v>65063.02</v>
       </c>
     </row>
     <row r="84" spans="1:7" x14ac:dyDescent="0.25">
@@ -2685,22 +2685,22 @@
         <v>85</v>
       </c>
       <c r="B84">
-        <v>324681.67</v>
+        <v>322978.05</v>
       </c>
       <c r="C84">
-        <v>175677.07</v>
+        <v>174241.47</v>
       </c>
       <c r="D84">
-        <v>126454.78</v>
+        <v>125073.99</v>
       </c>
       <c r="E84">
-        <v>102173.59</v>
+        <v>100794.95</v>
       </c>
       <c r="F84">
-        <v>78534.84</v>
+        <v>77110.399999999994</v>
       </c>
       <c r="G84">
-        <v>67328.72</v>
+        <v>65837.58</v>
       </c>
     </row>
     <row r="85" spans="1:7" x14ac:dyDescent="0.25">
@@ -2708,22 +2708,22 @@
         <v>86</v>
       </c>
       <c r="B85">
-        <v>328501.45</v>
+        <v>326777.78999999998</v>
       </c>
       <c r="C85">
-        <v>177743.85</v>
+        <v>176291.37</v>
       </c>
       <c r="D85">
-        <v>127942.48</v>
+        <v>126545.45</v>
       </c>
       <c r="E85">
-        <v>103375.63</v>
+        <v>101980.77</v>
       </c>
       <c r="F85">
-        <v>79458.78</v>
+        <v>78017.58</v>
       </c>
       <c r="G85">
-        <v>68120.820000000007</v>
+        <v>66612.14</v>
       </c>
     </row>
     <row r="86" spans="1:7" x14ac:dyDescent="0.25">
@@ -2731,22 +2731,22 @@
         <v>87</v>
       </c>
       <c r="B86">
-        <v>332321.24</v>
+        <v>330577.53000000003</v>
       </c>
       <c r="C86">
-        <v>179810.64</v>
+        <v>178341.27</v>
       </c>
       <c r="D86">
-        <v>129430.19</v>
+        <v>128016.91</v>
       </c>
       <c r="E86">
-        <v>104577.67</v>
+        <v>103166.6</v>
       </c>
       <c r="F86">
-        <v>80382.720000000001</v>
+        <v>78924.759999999995</v>
       </c>
       <c r="G86">
-        <v>68912.929999999993</v>
+        <v>67386.7</v>
       </c>
     </row>
     <row r="87" spans="1:7" x14ac:dyDescent="0.25">
@@ -2754,22 +2754,22 @@
         <v>88</v>
       </c>
       <c r="B87">
-        <v>336141.02</v>
+        <v>334377.27</v>
       </c>
       <c r="C87">
-        <v>181877.43</v>
+        <v>180391.17</v>
       </c>
       <c r="D87">
-        <v>130917.89</v>
+        <v>129488.36</v>
       </c>
       <c r="E87">
-        <v>105779.72</v>
+        <v>104352.42</v>
       </c>
       <c r="F87">
-        <v>81306.66</v>
+        <v>79831.94</v>
       </c>
       <c r="G87">
-        <v>69705.03</v>
+        <v>68161.259999999995</v>
       </c>
     </row>
     <row r="88" spans="1:7" x14ac:dyDescent="0.25">
@@ -2777,22 +2777,22 @@
         <v>89</v>
       </c>
       <c r="B88">
-        <v>339960.81</v>
+        <v>338177.02</v>
       </c>
       <c r="C88">
-        <v>183944.22</v>
+        <v>182441.07</v>
       </c>
       <c r="D88">
-        <v>132405.59</v>
+        <v>130959.82</v>
       </c>
       <c r="E88">
-        <v>106981.75999999999</v>
+        <v>105538.24000000001</v>
       </c>
       <c r="F88">
-        <v>82230.600000000006</v>
+        <v>80739.13</v>
       </c>
       <c r="G88">
-        <v>70497.13</v>
+        <v>68935.820000000007</v>
       </c>
     </row>
     <row r="89" spans="1:7" x14ac:dyDescent="0.25">
@@ -2800,22 +2800,22 @@
         <v>90</v>
       </c>
       <c r="B89">
-        <v>343780.59</v>
+        <v>341976.76</v>
       </c>
       <c r="C89">
-        <v>186011.01</v>
+        <v>184490.97</v>
       </c>
       <c r="D89">
-        <v>133893.29999999999</v>
+        <v>132431.28</v>
       </c>
       <c r="E89">
-        <v>108183.8</v>
+        <v>106724.07</v>
       </c>
       <c r="F89">
-        <v>83154.539999999994</v>
+        <v>81646.31</v>
       </c>
       <c r="G89">
-        <v>71289.23</v>
+        <v>69710.38</v>
       </c>
     </row>
     <row r="90" spans="1:7" x14ac:dyDescent="0.25">
@@ -2823,22 +2823,22 @@
         <v>91</v>
       </c>
       <c r="B90">
-        <v>347600.37</v>
+        <v>345776.5</v>
       </c>
       <c r="C90">
-        <v>188077.8</v>
+        <v>186540.87</v>
       </c>
       <c r="D90">
-        <v>135381</v>
+        <v>133902.74</v>
       </c>
       <c r="E90">
-        <v>109385.84</v>
+        <v>107909.89</v>
       </c>
       <c r="F90">
-        <v>84078.48</v>
+        <v>82553.490000000005</v>
       </c>
       <c r="G90">
-        <v>72081.34</v>
+        <v>70484.94</v>
       </c>
     </row>
     <row r="91" spans="1:7" x14ac:dyDescent="0.25">
@@ -2846,22 +2846,22 @@
         <v>92</v>
       </c>
       <c r="B91">
-        <v>351420.15999999997</v>
+        <v>349576.24</v>
       </c>
       <c r="C91">
-        <v>190144.59</v>
+        <v>188590.77</v>
       </c>
       <c r="D91">
-        <v>136868.70000000001</v>
+        <v>135374.20000000001</v>
       </c>
       <c r="E91">
-        <v>110587.88</v>
+        <v>109095.71</v>
       </c>
       <c r="F91">
-        <v>85002.42</v>
+        <v>83460.67</v>
       </c>
       <c r="G91">
-        <v>72873.440000000002</v>
+        <v>71259.5</v>
       </c>
     </row>
     <row r="92" spans="1:7" x14ac:dyDescent="0.25">
@@ -2869,22 +2869,22 @@
         <v>93</v>
       </c>
       <c r="B92">
-        <v>355239.94</v>
+        <v>353375.98</v>
       </c>
       <c r="C92">
-        <v>192211.38</v>
+        <v>190640.67</v>
       </c>
       <c r="D92">
-        <v>138356.41</v>
+        <v>136845.66</v>
       </c>
       <c r="E92">
-        <v>111789.93</v>
+        <v>110281.53</v>
       </c>
       <c r="F92">
-        <v>85926.36</v>
+        <v>84367.85</v>
       </c>
       <c r="G92">
-        <v>73665.539999999994</v>
+        <v>72034.06</v>
       </c>
     </row>
     <row r="93" spans="1:7" x14ac:dyDescent="0.25">
@@ -2892,22 +2892,22 @@
         <v>94</v>
       </c>
       <c r="B93">
-        <v>359059.73</v>
+        <v>357175.72</v>
       </c>
       <c r="C93">
-        <v>194278.17</v>
+        <v>192690.57</v>
       </c>
       <c r="D93">
-        <v>139844.10999999999</v>
+        <v>138317.12</v>
       </c>
       <c r="E93">
-        <v>112991.97</v>
+        <v>111467.36</v>
       </c>
       <c r="F93">
-        <v>86850.3</v>
+        <v>85275.03</v>
       </c>
       <c r="G93">
-        <v>74457.64</v>
+        <v>72808.62</v>
       </c>
     </row>
     <row r="94" spans="1:7" x14ac:dyDescent="0.25">
@@ -2915,22 +2915,22 @@
         <v>95</v>
       </c>
       <c r="B94">
-        <v>362879.51</v>
+        <v>360975.47</v>
       </c>
       <c r="C94">
-        <v>196344.95999999999</v>
+        <v>194740.47</v>
       </c>
       <c r="D94">
-        <v>141331.81</v>
+        <v>139788.57999999999</v>
       </c>
       <c r="E94">
-        <v>114194.01</v>
+        <v>112653.18</v>
       </c>
       <c r="F94">
-        <v>87774.24</v>
+        <v>86182.21</v>
       </c>
       <c r="G94">
-        <v>75249.75</v>
+        <v>73583.179999999993</v>
       </c>
     </row>
     <row r="95" spans="1:7" x14ac:dyDescent="0.25">
@@ -2938,22 +2938,22 @@
         <v>96</v>
       </c>
       <c r="B95">
-        <v>366699.3</v>
+        <v>364775.21</v>
       </c>
       <c r="C95">
-        <v>198411.74</v>
+        <v>196790.37</v>
       </c>
       <c r="D95">
-        <v>142819.51999999999</v>
+        <v>141260.03</v>
       </c>
       <c r="E95">
-        <v>115396.05</v>
+        <v>113839</v>
       </c>
       <c r="F95">
-        <v>88698.18</v>
+        <v>87089.39</v>
       </c>
       <c r="G95">
-        <v>76041.850000000006</v>
+        <v>74357.73</v>
       </c>
     </row>
     <row r="96" spans="1:7" x14ac:dyDescent="0.25">
@@ -2961,22 +2961,22 @@
         <v>97</v>
       </c>
       <c r="B96">
-        <v>370519.08</v>
+        <v>368574.95</v>
       </c>
       <c r="C96">
-        <v>200478.53</v>
+        <v>198840.27</v>
       </c>
       <c r="D96">
-        <v>144307.22</v>
+        <v>142731.49</v>
       </c>
       <c r="E96">
-        <v>116598.1</v>
+        <v>115024.83</v>
       </c>
       <c r="F96">
-        <v>89622.12</v>
+        <v>87996.57</v>
       </c>
       <c r="G96">
-        <v>76833.95</v>
+        <v>75132.289999999994</v>
       </c>
     </row>
     <row r="97" spans="1:7" x14ac:dyDescent="0.25">
@@ -2984,22 +2984,22 @@
         <v>98</v>
       </c>
       <c r="B97">
-        <v>374338.86</v>
+        <v>372374.69</v>
       </c>
       <c r="C97">
-        <v>202545.32</v>
+        <v>200890.17</v>
       </c>
       <c r="D97">
-        <v>145794.92000000001</v>
+        <v>144202.95000000001</v>
       </c>
       <c r="E97">
-        <v>117800.14</v>
+        <v>116210.65</v>
       </c>
       <c r="F97">
-        <v>90546.05</v>
+        <v>88903.76</v>
       </c>
       <c r="G97">
-        <v>77626.05</v>
+        <v>75906.850000000006</v>
       </c>
     </row>
     <row r="98" spans="1:7" x14ac:dyDescent="0.25">
@@ -3007,22 +3007,22 @@
         <v>99</v>
       </c>
       <c r="B98">
-        <v>378158.65</v>
+        <v>376174.43</v>
       </c>
       <c r="C98">
-        <v>204612.11</v>
+        <v>202940.07</v>
       </c>
       <c r="D98">
-        <v>147282.63</v>
+        <v>145674.41</v>
       </c>
       <c r="E98">
-        <v>119002.18</v>
+        <v>117396.47</v>
       </c>
       <c r="F98">
-        <v>91469.99</v>
+        <v>89810.94</v>
       </c>
       <c r="G98">
-        <v>78418.16</v>
+        <v>76681.41</v>
       </c>
     </row>
     <row r="99" spans="1:7" x14ac:dyDescent="0.25">
@@ -3030,22 +3030,22 @@
         <v>100</v>
       </c>
       <c r="B99">
-        <v>381978.43</v>
+        <v>379974.17</v>
       </c>
       <c r="C99">
-        <v>206678.9</v>
+        <v>204989.97</v>
       </c>
       <c r="D99">
-        <v>148770.32999999999</v>
+        <v>147145.87</v>
       </c>
       <c r="E99">
-        <v>120204.22</v>
+        <v>118582.29</v>
       </c>
       <c r="F99">
-        <v>92393.93</v>
+        <v>90718.12</v>
       </c>
       <c r="G99">
-        <v>79210.259999999995</v>
+        <v>77455.97</v>
       </c>
     </row>
     <row r="100" spans="1:7" x14ac:dyDescent="0.25">
@@ -3053,22 +3053,22 @@
         <v>101</v>
       </c>
       <c r="B100">
-        <v>401077.35</v>
+        <v>398972.88</v>
       </c>
       <c r="C100">
-        <v>217012.85</v>
+        <v>215239.47</v>
       </c>
       <c r="D100">
-        <v>156208.84</v>
+        <v>154503.16</v>
       </c>
       <c r="E100">
-        <v>126214.43</v>
+        <v>124511.41</v>
       </c>
       <c r="F100">
-        <v>97013.63</v>
+        <v>95254.02</v>
       </c>
       <c r="G100">
-        <v>83170.77</v>
+        <v>81328.77</v>
       </c>
     </row>
     <row r="101" spans="1:7" x14ac:dyDescent="0.25">
@@ -3076,22 +3076,22 @@
         <v>102</v>
       </c>
       <c r="B101">
-        <v>420176.28</v>
+        <v>417971.59</v>
       </c>
       <c r="C101">
-        <v>227346.79</v>
+        <v>225488.97</v>
       </c>
       <c r="D101">
         <v>163647.35999999999</v>
       </c>
       <c r="E101">
-        <v>132224.64000000001</v>
+        <v>130440.52</v>
       </c>
       <c r="F101">
-        <v>101633.33</v>
+        <v>99789.93</v>
       </c>
       <c r="G101">
-        <v>87131.29</v>
+        <v>85201.57</v>
       </c>
     </row>
     <row r="102" spans="1:7" x14ac:dyDescent="0.25">
@@ -3099,22 +3099,22 @@
         <v>103</v>
       </c>
       <c r="B102">
-        <v>439275.2</v>
+        <v>436970.3</v>
       </c>
       <c r="C102">
-        <v>237680.74</v>
+        <v>235738.47</v>
       </c>
       <c r="D102">
-        <v>171085.88</v>
+        <v>169217.75</v>
       </c>
       <c r="E102">
-        <v>138234.85999999999</v>
+        <v>136369.64000000001</v>
       </c>
       <c r="F102">
-        <v>106253.02</v>
+        <v>104325.84</v>
       </c>
       <c r="G102">
-        <v>91091.8</v>
+        <v>89074.37</v>
       </c>
     </row>
     <row r="103" spans="1:7" x14ac:dyDescent="0.25">
@@ -3122,22 +3122,22 @@
         <v>104</v>
       </c>
       <c r="B103">
-        <v>458374.12</v>
+        <v>455969.01</v>
       </c>
       <c r="C103">
-        <v>248014.68</v>
+        <v>245987.96</v>
       </c>
       <c r="D103">
-        <v>178524.39</v>
+        <v>176575.04</v>
       </c>
       <c r="E103">
-        <v>144245.07</v>
+        <v>142298.75</v>
       </c>
       <c r="F103">
-        <v>110872.72</v>
+        <v>108861.74</v>
       </c>
       <c r="G103">
-        <v>95052.31</v>
+        <v>92947.17</v>
       </c>
     </row>
     <row r="104" spans="1:7" x14ac:dyDescent="0.25">
@@ -3145,22 +3145,22 @@
         <v>105</v>
       </c>
       <c r="B104">
-        <v>477473.04</v>
+        <v>474967.72</v>
       </c>
       <c r="C104">
-        <v>258348.63</v>
+        <v>256237.46</v>
       </c>
       <c r="D104">
-        <v>185962.91</v>
+        <v>183932.34</v>
       </c>
       <c r="E104">
-        <v>150255.28</v>
+        <v>148227.87</v>
       </c>
       <c r="F104">
-        <v>115492.42</v>
+        <v>113397.65</v>
       </c>
       <c r="G104">
-        <v>99012.82</v>
+        <v>96819.97</v>
       </c>
     </row>
     <row r="105" spans="1:7" x14ac:dyDescent="0.25">
@@ -3168,22 +3168,22 @@
         <v>106</v>
       </c>
       <c r="B105">
-        <v>496571.96</v>
+        <v>493966.43</v>
       </c>
       <c r="C105">
-        <v>268682.57</v>
+        <v>266486.96000000002</v>
       </c>
       <c r="D105">
-        <v>193401.43</v>
+        <v>191289.63</v>
       </c>
       <c r="E105">
-        <v>156265.49</v>
+        <v>154156.98000000001</v>
       </c>
       <c r="F105">
-        <v>120112.11</v>
+        <v>117933.55</v>
       </c>
       <c r="G105">
-        <v>102973.34</v>
+        <v>100692.77</v>
       </c>
     </row>
     <row r="106" spans="1:7" x14ac:dyDescent="0.25">
@@ -3191,22 +3191,22 @@
         <v>107</v>
       </c>
       <c r="B106">
-        <v>515670.88</v>
+        <v>512965.14</v>
       </c>
       <c r="C106">
-        <v>279016.52</v>
+        <v>276736.46000000002</v>
       </c>
       <c r="D106">
-        <v>200839.94</v>
+        <v>198646.92</v>
       </c>
       <c r="E106">
-        <v>162275.70000000001</v>
+        <v>160086.1</v>
       </c>
       <c r="F106">
-        <v>124731.81</v>
+        <v>122469.46</v>
       </c>
       <c r="G106">
-        <v>106933.85</v>
+        <v>104565.56</v>
       </c>
     </row>
     <row r="107" spans="1:7" x14ac:dyDescent="0.25">
@@ -3214,22 +3214,22 @@
         <v>108</v>
       </c>
       <c r="B107">
-        <v>534769.81000000006</v>
+        <v>531963.84</v>
       </c>
       <c r="C107">
-        <v>289350.46000000002</v>
+        <v>286985.96000000002</v>
       </c>
       <c r="D107">
-        <v>208278.46</v>
+        <v>206604.22</v>
       </c>
       <c r="E107">
-        <v>168285.91</v>
+        <v>166015.21</v>
       </c>
       <c r="F107">
-        <v>129351.51</v>
+        <v>127005.37</v>
       </c>
       <c r="G107">
-        <v>110894.36</v>
+        <v>108438.36</v>
       </c>
     </row>
     <row r="108" spans="1:7" x14ac:dyDescent="0.25">
@@ -3237,22 +3237,22 @@
         <v>109</v>
       </c>
       <c r="B108">
-        <v>553868.73</v>
+        <v>550962.55000000005</v>
       </c>
       <c r="C108">
-        <v>299684.40999999997</v>
+        <v>297235.46000000002</v>
       </c>
       <c r="D108">
-        <v>215716.98</v>
+        <v>213631.51</v>
       </c>
       <c r="E108">
-        <v>174296.12</v>
+        <v>171944.33</v>
       </c>
       <c r="F108">
-        <v>133971.20000000001</v>
+        <v>131541.26999999999</v>
       </c>
       <c r="G108">
-        <v>114854.88</v>
+        <v>112311.16</v>
       </c>
     </row>
     <row r="109" spans="1:7" x14ac:dyDescent="0.25">
@@ -3260,22 +3260,22 @@
         <v>110</v>
       </c>
       <c r="B109">
-        <v>572967.65</v>
+        <v>569961.26</v>
       </c>
       <c r="C109">
-        <v>310018.34999999998</v>
+        <v>307484.96000000002</v>
       </c>
       <c r="D109">
-        <v>223155.49</v>
+        <v>220718.8</v>
       </c>
       <c r="E109">
-        <v>180306.33</v>
+        <v>177873.44</v>
       </c>
       <c r="F109">
-        <v>138590.9</v>
+        <v>136077.18</v>
       </c>
       <c r="G109">
-        <v>118815.39</v>
+        <v>116183.96</v>
       </c>
     </row>
     <row r="110" spans="1:7" x14ac:dyDescent="0.25">
@@ -3283,13 +3283,13 @@
         <v>115</v>
       </c>
       <c r="B110" s="2">
-        <v>592066.56999999995</v>
+        <v>588959.97</v>
       </c>
       <c r="C110" s="2">
-        <v>320352.3</v>
+        <v>317734.45</v>
       </c>
       <c r="D110" s="2">
-        <v>230594.01</v>
+        <v>228076.1</v>
       </c>
       <c r="E110">
         <v>186316.54</v>
@@ -3306,13 +3306,13 @@
         <v>116</v>
       </c>
       <c r="B111" s="2">
-        <v>611165.49</v>
+        <v>607958.68000000005</v>
       </c>
       <c r="C111" s="2">
-        <v>330686.24</v>
+        <v>327983.95</v>
       </c>
       <c r="D111" s="2">
-        <v>238032.53</v>
+        <v>235433.39</v>
       </c>
       <c r="E111">
         <v>192326.76</v>
